--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="25440" windowHeight="18615"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>编号</t>
   </si>
@@ -83,6 +83,21 @@
   </si>
   <si>
     <t>已修正</t>
+  </si>
+  <si>
+    <t>开箱设置界面，勾选框会出现点击之后自己会马上消失的情况</t>
+  </si>
+  <si>
+    <t>问题图片\问题5_1.png</t>
+  </si>
+  <si>
+    <t>新手训练营地图，怪物没有掉落，挂机了15分钟，一个掉落物品都没看到，但是掉落文件是有的。</t>
+  </si>
+  <si>
+    <t>新手训练营，角色自动获取的经验值变成了积分，并且数值也不对，但是角色能升级，不知道原因在哪里。</t>
+  </si>
+  <si>
+    <t>问题图片\问题7-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -1156,17 +1171,27 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>18</v>
+      </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7" ht="16.5" spans="1:5">
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
@@ -1174,9 +1199,15 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9" ht="16.5" spans="1:5">
@@ -1541,6 +1572,8 @@
     <hyperlink ref="D3" r:id="rId2" display="问题图片\问题2_1.png"/>
     <hyperlink ref="D4" r:id="rId3" display="问题图片\问题3_1.png"/>
     <hyperlink ref="D5" r:id="rId4" display="问题图片\问题4_1.png"/>
+    <hyperlink ref="D6" r:id="rId5" display="问题图片\问题5_1.png"/>
+    <hyperlink ref="D8" r:id="rId6" display="问题图片\问题7-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="18615"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>编号</t>
   </si>
@@ -61,6 +61,9 @@
     <t>问题图片\问题1_1.png</t>
   </si>
   <si>
+    <t>已修正</t>
+  </si>
+  <si>
     <t>BUG</t>
   </si>
   <si>
@@ -82,9 +85,6 @@
     <t>问题图片\问题4_1.png</t>
   </si>
   <si>
-    <t>已修正</t>
-  </si>
-  <si>
     <t>开箱设置界面，勾选框会出现点击之后自己会马上消失的情况</t>
   </si>
   <si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>问题图片\问题7-1.jpg</t>
+  </si>
+  <si>
+    <t>已去掉积分的增加，经验不提示是因为小于2000经验</t>
+  </si>
+  <si>
+    <t>可以降低获得经验的频率，而提高经验值</t>
   </si>
 </sst>
 </file>
@@ -1076,12 +1082,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="101.625" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="6" max="6" width="35" customWidth="1"/>
+    <col min="6" max="6" width="46.25" customWidth="1"/>
+    <col min="7" max="7" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
@@ -1104,7 +1111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="66" spans="1:5">
+    <row r="2" ht="66" spans="1:6">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1118,19 +1125,22 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1142,10 +1152,10 @@
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1157,22 +1167,22 @@
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:6">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>17</v>
@@ -1181,26 +1191,32 @@
         <v>18</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:7">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -1209,6 +1225,12 @@
         <v>21</v>
       </c>
       <c r="E8" s="2"/>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" ht="16.5" spans="1:5">
       <c r="A9" s="2">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17490"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>编号</t>
   </si>
@@ -100,10 +100,16 @@
     <t>问题图片\问题7-1.jpg</t>
   </si>
   <si>
-    <t>已去掉积分的增加，经验不提示是因为小于2000经验</t>
-  </si>
-  <si>
-    <t>可以降低获得经验的频率，而提高经验值</t>
+    <t>积分目前还存在；如果经验值必须要超过2000才显示，那就把现在的经验计算间隔扩大到现在的4倍，然后我去改单位时间的经验值</t>
+  </si>
+  <si>
+    <t>任务跳转需求：
+1、需要达到一定等级的任务，点击之后跳转到对应等级的练级地图
+2、需要达到一定开箱次数的任务，点击之后帮玩家点击一次宝箱，如果宝箱数量不足，则按照通用提示处理。
+3、需要达到一定战力的任务，点击之后按照等级段来跳转：【1，40级】打开槽位强化界面；【41，60级】打开槽位升星界面；【61，80级】打开魂石镶嵌界面；【81，100级】打开灵玉界面；【100级以上】打开护卫界面。</t>
+  </si>
+  <si>
+    <t>战力的计算不正确，按照现在表格里面配置的系数，初始角色的面板属性计算出来不会有这么大。</t>
   </si>
 </sst>
 </file>
@@ -746,7 +752,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -770,6 +776,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1082,11 +1091,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="3" max="3" width="101.625" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="46.25" customWidth="1"/>
     <col min="7" max="7" width="36.25" customWidth="1"/>
   </cols>
@@ -1211,7 +1221,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:7">
+    <row r="8" ht="16.5" spans="1:5">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1224,20 +1234,20 @@
       <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
+    </row>
+    <row r="9" ht="82.5" spans="1:5">
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
@@ -1245,8 +1255,12 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17490"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>编号</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>战力的计算不正确，按照现在表格里面配置的系数，初始角色的面板属性计算出来不会有这么大。</t>
+  </si>
+  <si>
+    <t>开箱结果展示界面上，装备图标上的转光特效和其本身品质不匹配</t>
   </si>
 </sst>
 </file>
@@ -752,7 +755,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -776,9 +779,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1245,7 +1245,7 @@
       <c r="B9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="2"/>
@@ -1268,8 +1268,12 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
   <si>
     <t>编号</t>
   </si>
@@ -113,6 +113,12 @@
   </si>
   <si>
     <t>开箱结果展示界面上，装备图标上的转光特效和其本身品质不匹配</t>
+  </si>
+  <si>
+    <t>去除和刀魂相关的飘字显示和对应属性计算</t>
+  </si>
+  <si>
+    <t>问题图片\问题11-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -1281,9 +1287,15 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13" ht="16.5" spans="1:5">
@@ -1614,6 +1626,7 @@
     <hyperlink ref="D5" r:id="rId4" display="问题图片\问题4_1.png"/>
     <hyperlink ref="D6" r:id="rId5" display="问题图片\问题5_1.png"/>
     <hyperlink ref="D8" r:id="rId6" display="问题图片\问题7-1.jpg"/>
+    <hyperlink ref="D12" r:id="rId7" display="问题图片\问题11-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
   <si>
     <t>编号</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>问题图片\问题7-1.jpg</t>
-  </si>
-  <si>
-    <t>积分目前还存在；如果经验值必须要超过2000才显示，那就把现在的经验计算间隔扩大到现在的4倍，然后我去改单位时间的经验值</t>
   </si>
   <si>
     <t>任务跳转需求：
@@ -1227,7 +1224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" ht="16.5" spans="1:5">
+    <row r="8" ht="16.5" spans="1:6">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1240,8 +1237,9 @@
       <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>22</v>
+      <c r="E8" s="2"/>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:5">
@@ -1252,7 +1250,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
@@ -1265,7 +1263,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1278,7 +1276,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1291,10 +1289,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="E12" s="2"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>编号</t>
   </si>
@@ -1281,7 +1281,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" ht="16.5" spans="1:5">
+    <row r="12" ht="16.5" spans="1:6">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1295,6 +1295,9 @@
         <v>26</v>
       </c>
       <c r="E12" s="2"/>
+      <c r="F12" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" ht="16.5" spans="1:5">
       <c r="A13" s="2">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>编号</t>
   </si>
@@ -116,6 +116,12 @@
   </si>
   <si>
     <t>问题图片\问题11-1.jpg</t>
+  </si>
+  <si>
+    <t>给等级进入的挂机副本添加一个“离开”按钮，点击之后可以退出副本回到对应主城安全区</t>
+  </si>
+  <si>
+    <t>问题图片\问题12-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -1303,9 +1309,15 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14" ht="16.5" spans="1:5">
@@ -1628,6 +1640,7 @@
     <hyperlink ref="D6" r:id="rId5" display="问题图片\问题5_1.png"/>
     <hyperlink ref="D8" r:id="rId6" display="问题图片\问题7-1.jpg"/>
     <hyperlink ref="D12" r:id="rId7" display="问题图片\问题11-1.jpg"/>
+    <hyperlink ref="D13" r:id="rId8" display="问题图片\问题12-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>编号</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>开箱结果展示界面上，装备图标上的转光特效和其本身品质不匹配</t>
+  </si>
+  <si>
+    <t>道具品质展示是要改物品表的</t>
   </si>
   <si>
     <t>去除和刀魂相关的飘字显示和对应属性计算</t>
@@ -1274,7 +1277,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" ht="16.5" spans="1:5">
+    <row r="11" ht="16.5" spans="1:6">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1286,6 +1289,9 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
       <c r="A12" s="2">
@@ -1295,10 +1301,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="1" t="s">
@@ -1313,10 +1319,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>编号</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>战力的计算不正确，按照现在表格里面配置的系数，初始角色的面板属性计算出来不会有这么大。</t>
+  </si>
+  <si>
+    <t>已修正，属性id 200被占用</t>
   </si>
   <si>
     <t>开箱结果展示界面上，装备图标上的转光特效和其本身品质不匹配</t>
@@ -1264,7 +1267,7 @@
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" ht="16.5" spans="1:5">
+    <row r="10" ht="16.5" spans="1:6">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1276,6 +1279,9 @@
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
       <c r="A11" s="2">
@@ -1285,12 +1291,12 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
@@ -1301,10 +1307,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="1" t="s">
@@ -1319,10 +1325,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>编号</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>问题图片\问题2_1.png</t>
+  </si>
+  <si>
+    <t>已不需要</t>
   </si>
   <si>
     <t>开箱结果界面，不管有几个宝箱，始终保持弹框居中显示</t>
@@ -299,12 +302,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -646,7 +655,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -670,16 +679,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -688,93 +697,96 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -786,13 +798,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="6" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1117,19 +1135,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1137,506 +1155,515 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="1" t="s">
+      <c r="E2" s="3"/>
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="2">
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="9"/>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:6">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:6">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" ht="82.5" spans="1:6">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:6">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:6">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:6">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:6">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:5">
+      <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" ht="16.5" spans="1:5">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="6">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" ht="16.5" spans="1:5">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" ht="16.5" spans="1:5">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" ht="16.5" spans="1:5">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" ht="16.5" spans="1:5">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" ht="16.5" spans="1:5">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" ht="16.5" spans="1:5">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" ht="16.5" spans="1:5">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" ht="82.5" spans="1:5">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" ht="16.5" spans="1:5">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:5">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="1" t="s">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="25" ht="16.5" spans="1:5">
+      <c r="A25" s="3">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+    </row>
+    <row r="26" ht="16.5" spans="1:5">
+      <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" t="s">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" ht="16.5" spans="1:5">
+      <c r="A27" s="3">
         <v>26</v>
       </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" ht="16.5" spans="1:5">
+      <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" ht="16.5" spans="1:5">
+      <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:5">
+      <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:5">
+      <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
     </row>
     <row r="34" ht="16.5" spans="1:5">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
     </row>
     <row r="35" ht="16.5" spans="1:5">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
     </row>
     <row r="36" ht="16.5" spans="1:5">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
     </row>
     <row r="37" ht="16.5" spans="1:5">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
     </row>
     <row r="38" ht="16.5" spans="1:5">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
     </row>
     <row r="39" ht="16.5" spans="1:5">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
     </row>
     <row r="40" ht="16.5" spans="1:5">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
     </row>
     <row r="41" ht="16.5" spans="1:5">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
     </row>
     <row r="42" ht="16.5" spans="1:5">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
     </row>
     <row r="43" ht="16.5" spans="1:5">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
     </row>
     <row r="44" ht="16.5" spans="1:5">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
     </row>
     <row r="45" ht="16.5" spans="1:5">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
     </row>
     <row r="46" ht="16.5" spans="1:5">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>45</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
     </row>
     <row r="47" ht="16.5" spans="1:5">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>46</v>
       </c>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="19395" windowHeight="17475"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>编号</t>
   </si>
@@ -131,6 +131,24 @@
   </si>
   <si>
     <t>问题图片\问题12-1.jpg</t>
+  </si>
+  <si>
+    <t>等级19级，点击主线任务，跳转到秋林地图之后地图一片黑，过了5秒被传送到了铁匠铺地图。</t>
+  </si>
+  <si>
+    <t>问题图片\问题13-1.jpg</t>
+  </si>
+  <si>
+    <t>主界面的血球资源错乱</t>
+  </si>
+  <si>
+    <t>问题图片\问题14-1.png</t>
+  </si>
+  <si>
+    <t>铁匠铺地图中的NPC需要去掉</t>
+  </si>
+  <si>
+    <t>问题图片\问题15-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -1363,27 +1381,45 @@
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" ht="16.5" spans="1:5">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" ht="16.5" spans="1:5">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" ht="16.5" spans="1:5">
@@ -1680,6 +1716,9 @@
     <hyperlink ref="D8" r:id="rId6" display="问题图片\问题7-1.jpg"/>
     <hyperlink ref="D12" r:id="rId7" display="问题图片\问题11-1.jpg"/>
     <hyperlink ref="D13" r:id="rId8" display="问题图片\问题12-1.jpg"/>
+    <hyperlink ref="D14" r:id="rId9" display="问题图片\问题13-1.jpg"/>
+    <hyperlink ref="D15" r:id="rId10" display="问题图片\问题14-1.png"/>
+    <hyperlink ref="D16" r:id="rId11" display="问题图片\问题15-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19395" windowHeight="17475"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
   <si>
     <t>编号</t>
   </si>
@@ -149,6 +149,9 @@
   </si>
   <si>
     <t>问题图片\问题15-1.jpg</t>
+  </si>
+  <si>
+    <t>箱子按钮有时候会出现点击无响应的现象，初步怀疑和点击速度有关，但角色新上线第一次点会开不出来装备</t>
   </si>
 </sst>
 </file>
@@ -1426,8 +1429,12 @@
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
   <si>
     <t>编号</t>
   </si>
@@ -152,6 +152,12 @@
   </si>
   <si>
     <t>箱子按钮有时候会出现点击无响应的现象，初步怀疑和点击速度有关，但角色新上线第一次点会开不出来装备</t>
+  </si>
+  <si>
+    <t>土城安全区NPC整理如下：
+1、去掉：等级提升，（切割）神石，（战力）转生使者，（进阶）神器打造，游戏冠名，书页夺宝
+2、在NPC：（狂暴）不归路，（进阶）称号专属，（首充）死亡棺材，尸王，重装使者，蓝色庄园，所进入的地图中均添加“离开副本”按钮。
+3、目前：蓝色庄园的地图进入等级需要调整为100级，另外等级地图{秋风峡谷，奴隶山谷，水上城市，蚂蚁巢穴}的进入等级并没有调整</t>
   </si>
 </sst>
 </file>
@@ -800,7 +806,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -833,6 +839,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="6" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1438,12 +1447,16 @@
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
     </row>
-    <row r="18" ht="16.5" spans="1:5">
+    <row r="18" ht="99" spans="1:5">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>39</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="14745" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
   <si>
     <t>编号</t>
   </si>
@@ -158,6 +158,15 @@
 1、去掉：等级提升，（切割）神石，（战力）转生使者，（进阶）神器打造，游戏冠名，书页夺宝
 2、在NPC：（狂暴）不归路，（进阶）称号专属，（首充）死亡棺材，尸王，重装使者，蓝色庄园，所进入的地图中均添加“离开副本”按钮。
 3、目前：蓝色庄园的地图进入等级需要调整为100级，另外等级地图{秋风峡谷，奴隶山谷，水上城市，蚂蚁巢穴}的进入等级并没有调整</t>
+  </si>
+  <si>
+    <t>宝箱升级界面，缺少了升级的状态，也就是升级需要消耗元宝货币的状态，目前只有加速状态。</t>
+  </si>
+  <si>
+    <t>详见文档宝箱升级的定义部分</t>
+  </si>
+  <si>
+    <t>新手地图内：黄沙蚁，白沙蚁，虎斑蚁三个怪物的形象资源错乱或者缺失</t>
   </si>
 </sst>
 </file>
@@ -806,7 +815,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -839,9 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="6" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1454,7 +1460,7 @@
       <c r="B18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D18" s="3"/>
@@ -1464,17 +1470,27 @@
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>42</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14745" windowHeight="12360"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
   <si>
     <t>编号</t>
   </si>
@@ -133,12 +133,18 @@
     <t>问题图片\问题12-1.jpg</t>
   </si>
   <si>
+    <t>待确认</t>
+  </si>
+  <si>
     <t>等级19级，点击主线任务，跳转到秋林地图之后地图一片黑，过了5秒被传送到了铁匠铺地图。</t>
   </si>
   <si>
     <t>问题图片\问题13-1.jpg</t>
   </si>
   <si>
+    <t>固定了飞行点</t>
+  </si>
+  <si>
     <t>主界面的血球资源错乱</t>
   </si>
   <si>
@@ -152,6 +158,9 @@
   </si>
   <si>
     <t>箱子按钮有时候会出现点击无响应的现象，初步怀疑和点击速度有关，但角色新上线第一次点会开不出来装备</t>
+  </si>
+  <si>
+    <t>增加宝箱功能的几个按钮点击间隔，500ms</t>
   </si>
   <si>
     <t>土城安全区NPC整理如下：
@@ -164,6 +173,9 @@
   </si>
   <si>
     <t>详见文档宝箱升级的定义部分</t>
+  </si>
+  <si>
+    <t>有升级和加速两个状态</t>
   </si>
   <si>
     <t>新手地图内：黄沙蚁，白沙蚁，虎斑蚁三个怪物的形象资源错乱或者缺失</t>
@@ -1160,8 +1172,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="101.625" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
@@ -1377,7 +1389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" ht="16.5" spans="1:6">
+    <row r="13" ht="16.5" spans="1:7">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -1394,8 +1406,11 @@
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:7">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -1403,14 +1418,20 @@
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3"/>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
+      <c r="F14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="1:7">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -1418,14 +1439,20 @@
         <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
+      <c r="F15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:7">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -1433,14 +1460,20 @@
         <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E16" s="3"/>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
+      <c r="F16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:7">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -1448,12 +1481,18 @@
         <v>10</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" ht="99" spans="1:5">
+      <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" ht="99" spans="1:6">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1461,12 +1500,15 @@
         <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
+      <c r="F18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:6">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1474,12 +1516,15 @@
         <v>10</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3"/>
+      <c r="F19" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="20" ht="16.5" spans="1:5">
       <c r="A20" s="3">
@@ -1489,7 +1534,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
   <si>
     <t>编号</t>
   </si>
@@ -179,6 +179,15 @@
   </si>
   <si>
     <t>新手地图内：黄沙蚁，白沙蚁，虎斑蚁三个怪物的形象资源错乱或者缺失</t>
+  </si>
+  <si>
+    <t>若开箱次数达到今日上限，主线任务给的开箱次数奖励现在无法正常发放，正常的应该是奖励正常发放，点击开箱提示开箱已达上限</t>
+  </si>
+  <si>
+    <t>包裹界面，点击“回收”按钮，弹出的回收操作界面层级不对，正常的应该在上层，目前被包裹主界面给盖住了</t>
+  </si>
+  <si>
+    <t>副本中的“离开”按钮位置调整到主线任务区域旁边，目前的位置容易被属性增加的飘字提示遮盖</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1184,7 @@
   <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="101.625" customWidth="1"/>
+    <col min="3" max="3" width="121.25" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="46.25" customWidth="1"/>
@@ -1543,8 +1552,12 @@
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
@@ -1552,8 +1565,12 @@
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
     </row>
@@ -1561,8 +1578,12 @@
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="50">
   <si>
     <t>编号</t>
   </si>
@@ -1501,7 +1501,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="99" spans="1:6">
+    <row r="18" ht="66" spans="1:6">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1548,7 +1548,7 @@
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
     </row>
-    <row r="21" ht="16.5" spans="1:5">
+    <row r="21" ht="16.5" spans="1:6">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1560,8 +1560,11 @@
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:6">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1573,8 +1576,11 @@
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
+      <c r="F22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:6">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1586,6 +1592,9 @@
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
+      <c r="F23" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="24" ht="16.5" spans="1:5">
       <c r="A24" s="3">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
   <si>
     <t>编号</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>副本中的“离开”按钮位置调整到主线任务区域旁边，目前的位置容易被属性增加的飘字提示遮盖</t>
+  </si>
+  <si>
+    <t>新手地图，点击“离开地图”按钮，没有响应。</t>
+  </si>
+  <si>
+    <t>当前版本，需要有元宝和绑定元宝的数值拆分，能使用绑定元宝的地方，当绑定元宝不足时，使用元宝补足；只能使用元宝的地方，绑定元宝不可用</t>
   </si>
 </sst>
 </file>
@@ -1501,7 +1507,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="99" spans="1:6">
+    <row r="18" ht="66" spans="1:6">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -1591,8 +1597,12 @@
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
     </row>
@@ -1600,8 +1610,12 @@
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
   <si>
     <t>编号</t>
   </si>
@@ -181,6 +181,9 @@
     <t>新手地图内：黄沙蚁，白沙蚁，虎斑蚁三个怪物的形象资源错乱或者缺失</t>
   </si>
   <si>
+    <t>需要选择合适的怪物外显填monster表的appear中</t>
+  </si>
+  <si>
     <t>若开箱次数达到今日上限，主线任务给的开箱次数奖励现在无法正常发放，正常的应该是奖励正常发放，点击开箱提示开箱已达上限</t>
   </si>
   <si>
@@ -191,6 +194,9 @@
   </si>
   <si>
     <t>新手地图，点击“离开地图”按钮，没有响应。</t>
+  </si>
+  <si>
+    <t>未能复现该问题，请再确认；我是手机模拟器进的，是因为手机点不中按钮？？？</t>
   </si>
   <si>
     <t>当前版本，需要有元宝和绑定元宝的数值拆分，能使用绑定元宝的地方，当绑定元宝不足时，使用元宝补足；只能使用元宝的地方，绑定元宝不可用</t>
@@ -365,7 +371,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,6 +387,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -718,7 +730,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,16 +754,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -760,89 +772,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -850,6 +862,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -874,6 +889,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="6" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1198,19 +1216,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1218,206 +1236,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="4"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="6">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="10"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="3">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="3">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="3"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="3">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="3">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="3"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="3">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="3"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1426,19 +1444,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="3">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="3"/>
+      <c r="E14" s="4"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1447,19 +1465,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="3">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="3"/>
+      <c r="E15" s="4"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1468,19 +1486,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="3">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="3"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1489,17 +1507,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="3">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1508,314 +1526,329 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="3">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="3">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="3"/>
+      <c r="E19" s="4"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="3">
+    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A20" s="12">
         <v>19</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" ht="16.5" spans="1:5">
-      <c r="A21" s="3">
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:6">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-    </row>
-    <row r="22" ht="16.5" spans="1:5">
-      <c r="A22" s="3">
+      <c r="C21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:6">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" ht="16.5" spans="1:5">
-      <c r="A23" s="3">
+      <c r="C22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:6">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:5">
-      <c r="A24" s="3">
+      <c r="C23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:6">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="C24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="25" ht="16.5" spans="1:5">
-      <c r="A25" s="3">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="C25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
     </row>
     <row r="26" ht="16.5" spans="1:5">
-      <c r="A26" s="3">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
     </row>
     <row r="27" ht="16.5" spans="1:5">
-      <c r="A27" s="3">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="3">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="3">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="3">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="3">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="B31" s="4"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="3">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="3">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
     </row>
     <row r="34" ht="16.5" spans="1:5">
-      <c r="A34" s="3">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
     </row>
     <row r="35" ht="16.5" spans="1:5">
-      <c r="A35" s="3">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
     </row>
     <row r="36" ht="16.5" spans="1:5">
-      <c r="A36" s="3">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
     </row>
     <row r="37" ht="16.5" spans="1:5">
-      <c r="A37" s="3">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
     </row>
     <row r="38" ht="16.5" spans="1:5">
-      <c r="A38" s="3">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
     </row>
     <row r="39" ht="16.5" spans="1:5">
-      <c r="A39" s="3">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
     </row>
     <row r="40" ht="16.5" spans="1:5">
-      <c r="A40" s="3">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
     </row>
     <row r="41" ht="16.5" spans="1:5">
-      <c r="A41" s="3">
+      <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
     </row>
     <row r="42" ht="16.5" spans="1:5">
-      <c r="A42" s="3">
+      <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
     </row>
     <row r="43" ht="16.5" spans="1:5">
-      <c r="A43" s="3">
+      <c r="A43" s="4">
         <v>42</v>
       </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
     </row>
     <row r="44" ht="16.5" spans="1:5">
-      <c r="A44" s="3">
+      <c r="A44" s="4">
         <v>43</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
     </row>
     <row r="45" ht="16.5" spans="1:5">
-      <c r="A45" s="3">
+      <c r="A45" s="4">
         <v>44</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" ht="16.5" spans="1:5">
-      <c r="A46" s="3">
+      <c r="A46" s="4">
         <v>45</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" ht="16.5" spans="1:5">
-      <c r="A47" s="3">
+      <c r="A47" s="4">
         <v>46</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="54">
   <si>
     <t>编号</t>
   </si>
@@ -1495,7 +1495,7 @@
       <c r="C16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="6" t="s">
         <v>39</v>
       </c>
       <c r="E16" s="4"/>
@@ -1639,7 +1639,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" ht="16.5" spans="1:5">
+    <row r="25" ht="16.5" spans="1:6">
       <c r="A25" s="4">
         <v>24</v>
       </c>
@@ -1651,6 +1651,9 @@
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
+      <c r="F25" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="26" ht="16.5" spans="1:5">
       <c r="A26" s="4">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
   <si>
     <t>编号</t>
   </si>
@@ -200,6 +200,25 @@
   </si>
   <si>
     <t>当前版本，需要有元宝和绑定元宝的数值拆分，能使用绑定元宝的地方，当绑定元宝不足时，使用元宝补足；只能使用元宝的地方，绑定元宝不可用</t>
+  </si>
+  <si>
+    <t>需要迁移的界面功能罗列：
+1、首充三日活动，按钮位置同原版本
+2、充值返利活动，按钮位置同原版本
+3、开服狂欢活动，按钮位置同原版本
+4、进阶礼包活动，按钮位置同原版本
+5、免费VIP活动，需要用独立按钮取代NPC的点击打开，按钮位置与上述活动在一起，按钮资源可以直接用现版本的“会员”按钮</t>
+  </si>
+  <si>
+    <t>需要迁移的NPC功能罗列：
+1、战力首领NPC以及相应功能，位置在安全区上方边缘
+2、灵珠副本NPC以及相应功能，位置在安全区上方边缘
+3、个人首领NPC以及相应功能，位置在安全区右侧边缘
+4、野外首领NPC以及相应功能，位置在安全区右侧边缘
+5、运镖功能NPC，位置在安全区左侧边缘；交镖功能NPC，位置在原版位置</t>
+  </si>
+  <si>
+    <t>实现跨服玩法功能，详见对应策划文档</t>
   </si>
 </sst>
 </file>
@@ -854,7 +873,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -893,6 +912,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1655,21 +1677,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" ht="16.5" spans="1:5">
+    <row r="26" ht="99" spans="1:5">
       <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
+      <c r="B26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>54</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" ht="16.5" spans="1:5">
+    <row r="27" ht="99" spans="1:5">
       <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="B27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>55</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
@@ -1677,8 +1707,12 @@
       <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
+      <c r="B28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>56</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
   <si>
     <t>编号</t>
   </si>
@@ -208,6 +208,9 @@
 3、开服狂欢活动，按钮位置同原版本
 4、进阶礼包活动，按钮位置同原版本
 5、免费VIP活动，需要用独立按钮取代NPC的点击打开，按钮位置与上述活动在一起，按钮资源可以直接用现版本的“会员”按钮</t>
+  </si>
+  <si>
+    <t>已初步迁移</t>
   </si>
   <si>
     <t>需要迁移的NPC功能罗列：
@@ -873,7 +876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -912,9 +915,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1677,18 +1677,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" ht="99" spans="1:5">
+    <row r="26" ht="99" spans="1:6">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="5" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
+      <c r="F26" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="27" ht="99" spans="1:5">
       <c r="A27" s="4">
@@ -1697,8 +1700,8 @@
       <c r="B27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>55</v>
+      <c r="C27" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1711,7 +1714,7 @@
         <v>6</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
   <si>
     <t>编号</t>
   </si>
@@ -876,7 +876,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -915,6 +915,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1677,34 +1680,37 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" ht="99" spans="1:6">
-      <c r="A26" s="4">
+    <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
+      <c r="A26" s="12">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" t="s">
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" ht="99" spans="1:5">
-      <c r="A27" s="4">
+    <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
+      <c r="A27" s="12">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
       <c r="A28" s="4">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
   <si>
     <t>编号</t>
   </si>
@@ -222,6 +222,82 @@
   </si>
   <si>
     <t>实现跨服玩法功能，详见对应策划文档</t>
+  </si>
+  <si>
+    <t>技能的升级逻辑要调整为原来的需要书页进行升级，现在是会自动升级。</t>
+  </si>
+  <si>
+    <t>问题图片\问题28-1.jpg</t>
+  </si>
+  <si>
+    <t>将原来上线默认赠送的开会员用的元宝奖励去除。</t>
+  </si>
+  <si>
+    <t>问题图片\问题29-1.jpg</t>
+  </si>
+  <si>
+    <t>面板属性：生命：314；魔法：99；准确：14；敏捷：15；攻击：250-572；魔法：198-456；道术：198-456；防御：59-139；魔防：105-238；攻速：14；爆伤增加：30%；增加攻击伤害：6%；吸血：10%。游戏内显示战力：67990，按照当前配置的战力系数实际应该是：88916。</t>
+  </si>
+  <si>
+    <t>开箱结果界面，部分道具图标缺失，目前发现以戒指和头盔两个部位出现频率最高，其他部位也有发现。</t>
+  </si>
+  <si>
+    <t>问题图片\问题31-1.jpg</t>
+  </si>
+  <si>
+    <t>包裹中有很多道具的图标资源缺失，多次刷新以及上下线均无法正常加载出来，比如书页道具，技能书卷轴道具等。</t>
+  </si>
+  <si>
+    <t>问题图片\问题32-1.jpg</t>
+  </si>
+  <si>
+    <t>运镖功能异常：1是刷新镖车，实际刷新出来紫色的镖车，但是显示仍然是绿色的；2是点击运送镖车按钮，一直提示：系统繁忙，无法正常运镖，场景中也并未刷新出镖车。3是点击运送镖车之后角色开始自动寻路，但是寻路最终点并不是交镖处，而是盟重土城【628，302】坐标。</t>
+  </si>
+  <si>
+    <t>问题图片\33-1.jpg</t>
+  </si>
+  <si>
+    <t>免费VIP功能的任务问题与调整：
+1、新增任务种类：累计开箱XX次。
+2、点击累计开箱多少次的任务前往按钮后，关闭免费VIP界面，开始自动开箱，如果开箱次数不足，则给出通用提示：开箱次数不足。
+3、任务中的前往按钮功能目前失效了，需要按照原来设计进行实现，比如，槽位强化到XX级，文档定义是打开槽位强化界面；角色等级XX级则传送到对应挂机副本。
+4、特权中需要增加一类：任务泡点经验提升X倍。</t>
+  </si>
+  <si>
+    <t>绑定元宝的显示异常，目前主界面上绑定元宝的图标显示错误，且一直显示为0，但实际商城购买中会扣除绑定元宝</t>
+  </si>
+  <si>
+    <t>宝箱升级成功之后，需要将同时能开启的箱子数量自动帮玩家选定为当前的最大次数，如截图中红框中所示，目前宝箱升到2级了，但是开箱子的数量还是1，需要自己手动去调。</t>
+  </si>
+  <si>
+    <t>问题图片\问题36-1.png</t>
+  </si>
+  <si>
+    <t>魂石合成成功之后，每次都会自动弹出来五行效果的属性弹框，不知道为什么。</t>
+  </si>
+  <si>
+    <t>问题图片\问题37-1.jpg</t>
+  </si>
+  <si>
+    <t>升级技能时候，聊天框会显示：nil持久过低</t>
+  </si>
+  <si>
+    <t>问题图片\38-1.jpg</t>
+  </si>
+  <si>
+    <t>目前单职业的话，只有战士的技能，没有法师和道士的技能。</t>
+  </si>
+  <si>
+    <t>本服会员这个功能目前在主界面上还存在，需要去掉按钮以及对应的会员特权</t>
+  </si>
+  <si>
+    <t>问题图片\40-1.png</t>
+  </si>
+  <si>
+    <t>自动升星按钮，点击之后会提升文字：没有指定星级，系统默认选中了下一星级，但是并没有开始升星。自动升星功能未生效。</t>
+  </si>
+  <si>
+    <t>问题图片\41-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -876,7 +952,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -917,6 +993,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1729,26 +1808,42 @@
       <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="B29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>59</v>
+      </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+      <c r="B30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="E30" s="4"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
       <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
+      <c r="B31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>62</v>
+      </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
     </row>
@@ -1756,35 +1851,57 @@
       <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+      <c r="B32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
       <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
+      <c r="B33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>66</v>
+      </c>
       <c r="E33" s="4"/>
     </row>
     <row r="34" ht="16.5" spans="1:5">
       <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
+      <c r="B34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>68</v>
+      </c>
       <c r="E34" s="4"/>
     </row>
-    <row r="35" ht="16.5" spans="1:5">
+    <row r="35" ht="99" spans="1:5">
       <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
+      <c r="B35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>69</v>
+      </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
     </row>
@@ -1792,8 +1909,12 @@
       <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
+      <c r="B36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
     </row>
@@ -1801,35 +1922,57 @@
       <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>72</v>
+      </c>
       <c r="E37" s="4"/>
     </row>
     <row r="38" ht="16.5" spans="1:5">
       <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
+      <c r="B38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>74</v>
+      </c>
       <c r="E38" s="4"/>
     </row>
     <row r="39" ht="16.5" spans="1:5">
       <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
+      <c r="B39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="E39" s="4"/>
     </row>
     <row r="40" ht="16.5" spans="1:5">
       <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="B40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
     </row>
@@ -1837,18 +1980,30 @@
       <c r="A41" s="4">
         <v>40</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
+      <c r="B41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>79</v>
+      </c>
       <c r="E41" s="4"/>
     </row>
     <row r="42" ht="16.5" spans="1:5">
       <c r="A42" s="4">
         <v>41</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
+      <c r="B42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" ht="16.5" spans="1:5">
@@ -1914,6 +2069,16 @@
     <hyperlink ref="D14" r:id="rId9" display="问题图片\问题13-1.jpg"/>
     <hyperlink ref="D15" r:id="rId10" display="问题图片\问题14-1.png"/>
     <hyperlink ref="D16" r:id="rId11" display="问题图片\问题15-1.jpg"/>
+    <hyperlink ref="D29" r:id="rId12" display="问题图片\问题28-1.jpg"/>
+    <hyperlink ref="D30" r:id="rId13" display="问题图片\问题29-1.jpg"/>
+    <hyperlink ref="D32" r:id="rId14" display="问题图片\问题31-1.jpg"/>
+    <hyperlink ref="D33" r:id="rId15" display="问题图片\问题32-1.jpg"/>
+    <hyperlink ref="D34" r:id="rId16" display="问题图片\33-1.jpg"/>
+    <hyperlink ref="D37" r:id="rId17" display="问题图片\问题36-1.png"/>
+    <hyperlink ref="D38" r:id="rId18" display="问题图片\问题37-1.jpg"/>
+    <hyperlink ref="D39" r:id="rId19" display="问题图片\38-1.jpg"/>
+    <hyperlink ref="D41" r:id="rId20" display="问题图片\40-1.png"/>
+    <hyperlink ref="D42" r:id="rId21" display="问题图片\41-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="94">
   <si>
     <t>编号</t>
   </si>
@@ -230,31 +230,61 @@
     <t>问题图片\问题28-1.jpg</t>
   </si>
   <si>
+    <t>已修正   这个是技能熟练度导致的，技能升级的熟练度设置为0就可以了</t>
+  </si>
+  <si>
     <t>将原来上线默认赠送的开会员用的元宝奖励去除。</t>
   </si>
   <si>
     <t>问题图片\问题29-1.jpg</t>
   </si>
   <si>
+    <t>已修改</t>
+  </si>
+  <si>
     <t>面板属性：生命：314；魔法：99；准确：14；敏捷：15；攻击：250-572；魔法：198-456；道术：198-456；防御：59-139；魔防：105-238；攻速：14；爆伤增加：30%；增加攻击伤害：6%；吸血：10%。游戏内显示战力：67990，按照当前配置的战力系数实际应该是：88916。</t>
   </si>
   <si>
+    <t>我看的自己的数据，算下来基本上是对的。。。这个要再确认下</t>
+  </si>
+  <si>
     <t>开箱结果界面，部分道具图标缺失，目前发现以戒指和头盔两个部位出现频率最高，其他部位也有发现。</t>
   </si>
   <si>
     <t>问题图片\问题31-1.jpg</t>
   </si>
   <si>
+    <t>本地没出现这个情况。。。回头再确认下手机，看是不是资源问题，和包裹中资源的问题应该是一个事情</t>
+  </si>
+  <si>
     <t>包裹中有很多道具的图标资源缺失，多次刷新以及上下线均无法正常加载出来，比如书页道具，技能书卷轴道具等。</t>
   </si>
   <si>
     <t>问题图片\问题32-1.jpg</t>
   </si>
   <si>
+    <t>本地没出现这个情况。。。回头再确认下手机，看是不是资源问题，和上面的问题应该是一个事情</t>
+  </si>
+  <si>
     <t>运镖功能异常：1是刷新镖车，实际刷新出来紫色的镖车，但是显示仍然是绿色的；2是点击运送镖车按钮，一直提示：系统繁忙，无法正常运镖，场景中也并未刷新出镖车。3是点击运送镖车之后角色开始自动寻路，但是寻路最终点并不是交镖处，而是盟重土城【628，302】坐标。</t>
   </si>
   <si>
     <t>问题图片\33-1.jpg</t>
+  </si>
+  <si>
+    <r>
+      <t>已修改  前面是镖车怪物没配置，应该刷不出来的。。。。现在已修正，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>但镖车宝宝的名字颜色无法修改</t>
+    </r>
   </si>
   <si>
     <t>免费VIP功能的任务问题与调整：
@@ -264,9 +294,15 @@
 4、特权中需要增加一类：任务泡点经验提升X倍。</t>
   </si>
   <si>
+    <t>1.增加（需要配置，任务类型14）   2.已完成   3.已修改    4.已完成</t>
+  </si>
+  <si>
     <t>绑定元宝的显示异常，目前主界面上绑定元宝的图标显示错误，且一直显示为0，但实际商城购买中会扣除绑定元宝</t>
   </si>
   <si>
+    <t>已修正，之前那里显示的金刚石</t>
+  </si>
+  <si>
     <t>宝箱升级成功之后，需要将同时能开启的箱子数量自动帮玩家选定为当前的最大次数，如截图中红框中所示，目前宝箱升到2级了，但是开箱子的数量还是1，需要自己手动去调。</t>
   </si>
   <si>
@@ -285,19 +321,31 @@
     <t>问题图片\38-1.jpg</t>
   </si>
   <si>
+    <t>这个应该不是升级技能时候的提示，本服没看到，待到模拟器上再测试下。。。也可能是其它状况下发出的</t>
+  </si>
+  <si>
     <t>目前单职业的话，只有战士的技能，没有法师和道士的技能。</t>
   </si>
   <si>
+    <t>待配置，脚本中的</t>
+  </si>
+  <si>
     <t>本服会员这个功能目前在主界面上还存在，需要去掉按钮以及对应的会员特权</t>
   </si>
   <si>
     <t>问题图片\40-1.png</t>
   </si>
   <si>
+    <t>已删除</t>
+  </si>
+  <si>
     <t>自动升星按钮，点击之后会提升文字：没有指定星级，系统默认选中了下一星级，但是并没有开始升星。自动升星功能未生效。</t>
   </si>
   <si>
     <t>问题图片\41-1.jpg</t>
+  </si>
+  <si>
+    <t>因为没有指定星级，自动升星是先帮你设置下一级作为目标星级，你确认后，再点一次自动升级就好了！（如觉得不合适，再调整）</t>
   </si>
 </sst>
 </file>
@@ -310,7 +358,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,8 +516,15 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,6 +546,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -828,7 +895,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -852,16 +919,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -870,89 +937,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -963,6 +1030,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -995,8 +1068,23 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="6" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1309,30 +1397,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.25" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="46.25" customWidth="1"/>
+    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="104.25" customWidth="1"/>
     <col min="7" max="7" width="36.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1340,206 +1428,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="6"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="7">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="9"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="10">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="12"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="4">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="4">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1548,19 +1636,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="4">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="6"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1569,19 +1657,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="4">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1590,19 +1678,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="4">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="6"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1611,17 +1699,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="4">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1630,426 +1718,501 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="4">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="4">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="6"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="12">
+      <c r="A20" s="14">
         <v>19</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="4">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="4">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="4">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="4">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="4">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="12">
+      <c r="A26" s="14">
         <v>25</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="12">
+      <c r="A27" s="14">
         <v>26</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="4">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="4">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:5">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+    </row>
+    <row r="31" ht="16.5" spans="1:5">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:5">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" ht="16.5" spans="1:5">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A34" s="14">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="B34" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D34" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="4"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="4">
+      <c r="F34" s="14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A35" s="14">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B35" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="C35" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="4"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="4">
+      <c r="D35" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A36" s="17">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-    </row>
-    <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="4">
+      <c r="B36" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A37" s="18">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E32" s="4"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="4">
+      <c r="B37" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="18"/>
+      <c r="F37" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A38" s="18">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E33" s="4"/>
-    </row>
-    <row r="34" ht="16.5" spans="1:5">
-      <c r="A34" s="4">
+      <c r="B38" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="E38" s="18"/>
+      <c r="F38" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A39" s="14">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="4"/>
-    </row>
-    <row r="35" ht="99" spans="1:5">
-      <c r="A35" s="4">
+      <c r="B39" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
+      <c r="A40" s="14">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B40" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-    </row>
-    <row r="36" ht="16.5" spans="1:5">
-      <c r="A36" s="4">
+      <c r="C40" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A41" s="14">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-    </row>
-    <row r="37" ht="16.5" spans="1:5">
-      <c r="A37" s="4">
+      <c r="B41" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A42" s="14">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B42" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="4"/>
-    </row>
-    <row r="38" ht="16.5" spans="1:5">
-      <c r="A38" s="4">
+      <c r="C42" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A43" s="14">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38" s="4"/>
-    </row>
-    <row r="39" ht="16.5" spans="1:5">
-      <c r="A39" s="4">
+      <c r="B43" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="1:6">
+      <c r="A44" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="E39" s="4"/>
-    </row>
-    <row r="40" ht="16.5" spans="1:5">
-      <c r="A40" s="4">
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="F44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A45" s="18">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-    </row>
-    <row r="41" ht="16.5" spans="1:5">
-      <c r="A41" s="4">
+      <c r="B45" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A46" s="14">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E41" s="4"/>
-    </row>
-    <row r="42" ht="16.5" spans="1:5">
-      <c r="A42" s="4">
+      <c r="B46" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A47" s="14">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" s="4"/>
-    </row>
-    <row r="43" ht="16.5" spans="1:5">
-      <c r="A43" s="4">
+      <c r="B47" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E47" s="14"/>
+      <c r="F47" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:5">
+      <c r="A48" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-    </row>
-    <row r="44" ht="16.5" spans="1:5">
-      <c r="A44" s="4">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+    </row>
+    <row r="49" ht="16.5" spans="1:5">
+      <c r="A49" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-    </row>
-    <row r="45" ht="16.5" spans="1:5">
-      <c r="A45" s="4">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+    </row>
+    <row r="50" ht="16.5" spans="1:5">
+      <c r="A50" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-    </row>
-    <row r="46" ht="16.5" spans="1:5">
-      <c r="A46" s="4">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+    </row>
+    <row r="51" ht="16.5" spans="1:5">
+      <c r="A51" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-    </row>
-    <row r="47" ht="16.5" spans="1:5">
-      <c r="A47" s="4">
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+    </row>
+    <row r="52" ht="16.5" spans="1:5">
+      <c r="A52" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2069,16 +2232,16 @@
     <hyperlink ref="D14" r:id="rId9" display="问题图片\问题13-1.jpg"/>
     <hyperlink ref="D15" r:id="rId10" display="问题图片\问题14-1.png"/>
     <hyperlink ref="D16" r:id="rId11" display="问题图片\问题15-1.jpg"/>
-    <hyperlink ref="D29" r:id="rId12" display="问题图片\问题28-1.jpg"/>
-    <hyperlink ref="D30" r:id="rId13" display="问题图片\问题29-1.jpg"/>
-    <hyperlink ref="D32" r:id="rId14" display="问题图片\问题31-1.jpg"/>
-    <hyperlink ref="D33" r:id="rId15" display="问题图片\问题32-1.jpg"/>
-    <hyperlink ref="D34" r:id="rId16" display="问题图片\33-1.jpg"/>
-    <hyperlink ref="D37" r:id="rId17" display="问题图片\问题36-1.png"/>
-    <hyperlink ref="D38" r:id="rId18" display="问题图片\问题37-1.jpg"/>
-    <hyperlink ref="D39" r:id="rId19" display="问题图片\38-1.jpg"/>
-    <hyperlink ref="D41" r:id="rId20" display="问题图片\40-1.png"/>
-    <hyperlink ref="D42" r:id="rId21" display="问题图片\41-1.jpg"/>
+    <hyperlink ref="D34" r:id="rId12" display="问题图片\问题28-1.jpg"/>
+    <hyperlink ref="D35" r:id="rId13" display="问题图片\问题29-1.jpg"/>
+    <hyperlink ref="D37" r:id="rId14" display="问题图片\问题31-1.jpg"/>
+    <hyperlink ref="D38" r:id="rId15" display="问题图片\问题32-1.jpg"/>
+    <hyperlink ref="D39" r:id="rId16" display="问题图片\33-1.jpg"/>
+    <hyperlink ref="D42" r:id="rId17" display="问题图片\问题36-1.png"/>
+    <hyperlink ref="D43" r:id="rId18" display="问题图片\问题37-1.jpg"/>
+    <hyperlink ref="D44" r:id="rId19" display="问题图片\38-1.jpg"/>
+    <hyperlink ref="D46" r:id="rId20" display="问题图片\40-1.png"/>
+    <hyperlink ref="D47" r:id="rId21" display="问题图片\41-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -254,7 +254,7 @@
     <t>问题图片\问题31-1.jpg</t>
   </si>
   <si>
-    <t>本地没出现这个情况。。。回头再确认下手机，看是不是资源问题，和包裹中资源的问题应该是一个事情</t>
+    <t>装备都是屏蔽字的问题 良 XXX  中间的点的问题</t>
   </si>
   <si>
     <t>包裹中有很多道具的图标资源缺失，多次刷新以及上下线均无法正常加载出来，比如书页道具，技能书卷轴道具等。</t>
@@ -263,7 +263,7 @@
     <t>问题图片\问题32-1.jpg</t>
   </si>
   <si>
-    <t>本地没出现这个情况。。。回头再确认下手机，看是不是资源问题，和上面的问题应该是一个事情</t>
+    <t>和装备情况类似，道具中部分新道具名字被屏蔽了</t>
   </si>
   <si>
     <t>运镖功能异常：1是刷新镖车，实际刷新出来紫色的镖车，但是显示仍然是绿色的；2是点击运送镖车按钮，一直提示：系统繁忙，无法正常运镖，场景中也并未刷新出镖车。3是点击运送镖车之后角色开始自动寻路，但是寻路最终点并不是交镖处，而是盟重土城【628，302】坐标。</t>
@@ -273,6 +273,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>已修改  前面是镖车怪物没配置，应该刷不出来的。。。。现在已修正，</t>
     </r>
     <r>
@@ -524,7 +531,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -552,6 +559,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,7 +908,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -919,16 +932,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -937,89 +950,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1036,6 +1049,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1084,6 +1100,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1408,19 +1427,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1428,206 +1447,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="9">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="12"/>
+      <c r="E5" s="13"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="6">
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1636,19 +1655,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1657,19 +1676,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="6">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1678,19 +1697,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="6">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1699,17 +1718,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="6">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="B17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1718,501 +1737,501 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="6">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="6">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="7"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>19</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="6">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="6">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="B22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="6">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="6">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="6">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="6">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="14">
+      <c r="A34" s="15">
         <v>28</v>
       </c>
-      <c r="B34" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="14" t="s">
+      <c r="B34" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="D34" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="14">
+      <c r="A35" s="15">
         <v>29</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="15" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="17">
+      <c r="A36" s="18">
         <v>30</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="17" t="s">
+      <c r="B36" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="18">
+      <c r="A37" s="19">
         <v>31</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="18" t="s">
+      <c r="B37" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="18"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="18">
+      <c r="A38" s="19">
         <v>32</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="18" t="s">
+      <c r="B38" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="18"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="14">
+      <c r="A39" s="15">
         <v>33</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="21" t="s">
+      <c r="E39" s="15"/>
+      <c r="F39" s="22" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="14">
+      <c r="A40" s="15">
         <v>34</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="14">
+      <c r="A41" s="15">
         <v>35</v>
       </c>
-      <c r="B41" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="14" t="s">
+      <c r="B41" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="14">
+      <c r="A42" s="15">
         <v>36</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="14"/>
+      <c r="E42" s="15"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="14">
+      <c r="A43" s="15">
         <v>37</v>
       </c>
-      <c r="B43" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="14"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="6">
+      <c r="A44" s="7">
         <v>38</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6" t="s">
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="6"/>
+      <c r="E44" s="7"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="18">
+    <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A45" s="23">
         <v>39</v>
       </c>
-      <c r="B45" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="18" t="s">
+      <c r="B45" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="5" t="s">
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="14">
+      <c r="A46" s="15">
         <v>40</v>
       </c>
-      <c r="B46" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="14" t="s">
+      <c r="B46" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="14"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="14">
+      <c r="A47" s="15">
         <v>41</v>
       </c>
-      <c r="B47" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="14" t="s">
+      <c r="B47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="14"/>
+      <c r="E47" s="15"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:5">
-      <c r="A48" s="6">
+      <c r="A48" s="7">
         <v>42</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
     </row>
     <row r="49" ht="16.5" spans="1:5">
-      <c r="A49" s="6">
+      <c r="A49" s="7">
         <v>43</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="6"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
     </row>
     <row r="50" ht="16.5" spans="1:5">
-      <c r="A50" s="6">
+      <c r="A50" s="7">
         <v>44</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="6">
+      <c r="A51" s="7">
         <v>45</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="6"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" ht="16.5" spans="1:5">
-      <c r="A52" s="6">
+      <c r="A52" s="7">
         <v>46</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="98">
   <si>
     <t>编号</t>
   </si>
@@ -353,6 +353,18 @@
   </si>
   <si>
     <t>因为没有指定星级，自动升星是先帮你设置下一级作为目标星级，你确认后，再点一次自动升级就好了！（如觉得不合适，再调整）</t>
+  </si>
+  <si>
+    <t>新创建角色进入游戏之后会被禁言然后还有新手地图禁用刺杀，这个应该去掉</t>
+  </si>
+  <si>
+    <t>问题图片\42-1.jpg</t>
+  </si>
+  <si>
+    <t>开箱碰到开箱结果界面为空的情况</t>
+  </si>
+  <si>
+    <t>问题图片\43-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -2192,18 +2204,30 @@
       <c r="A48" s="7">
         <v>42</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
+      <c r="B48" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="E48" s="7"/>
     </row>
     <row r="49" ht="16.5" spans="1:5">
       <c r="A49" s="7">
         <v>43</v>
       </c>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
+      <c r="B49" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="E49" s="7"/>
     </row>
     <row r="50" ht="16.5" spans="1:5">
@@ -2261,6 +2285,8 @@
     <hyperlink ref="D44" r:id="rId19" display="问题图片\38-1.jpg"/>
     <hyperlink ref="D46" r:id="rId20" display="问题图片\40-1.png"/>
     <hyperlink ref="D47" r:id="rId21" display="问题图片\41-1.jpg"/>
+    <hyperlink ref="D48" r:id="rId22" display="问题图片\42-1.jpg"/>
+    <hyperlink ref="D49" r:id="rId23" display="问题图片\43-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1428,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.25" customWidth="1"/>
@@ -2200,66 +2200,87 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" ht="16.5" spans="1:5">
-      <c r="A48" s="7">
-        <v>42</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E48" s="7"/>
-    </row>
-    <row r="49" ht="16.5" spans="1:5">
-      <c r="A49" s="7">
-        <v>43</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" ht="16.5" spans="1:5">
-      <c r="A50" s="7">
-        <v>44</v>
-      </c>
-      <c r="B50" s="7"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
+    <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="15"/>
+    </row>
+    <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="15"/>
+    </row>
+    <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A50" s="15"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="15"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
       <c r="A51" s="7">
-        <v>45</v>
-      </c>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
+        <v>42</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>95</v>
+      </c>
       <c r="E51" s="7"/>
     </row>
     <row r="52" ht="16.5" spans="1:5">
       <c r="A52" s="7">
+        <v>43</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" ht="16.5" spans="1:5">
+      <c r="A53" s="7">
+        <v>44</v>
+      </c>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54" ht="16.5" spans="1:5">
+      <c r="A54" s="7">
+        <v>45</v>
+      </c>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55" ht="16.5" spans="1:5">
+      <c r="A55" s="7">
         <v>46</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B47 B48:B50 B51:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2285,8 +2306,8 @@
     <hyperlink ref="D44" r:id="rId19" display="问题图片\38-1.jpg"/>
     <hyperlink ref="D46" r:id="rId20" display="问题图片\40-1.png"/>
     <hyperlink ref="D47" r:id="rId21" display="问题图片\41-1.jpg"/>
-    <hyperlink ref="D48" r:id="rId22" display="问题图片\42-1.jpg"/>
-    <hyperlink ref="D49" r:id="rId23" display="问题图片\43-1.jpg"/>
+    <hyperlink ref="D51" r:id="rId22" display="问题图片\42-1.jpg"/>
+    <hyperlink ref="D52" r:id="rId23" display="问题图片\43-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="100">
   <si>
     <t>编号</t>
   </si>
@@ -365,6 +365,12 @@
   </si>
   <si>
     <t>问题图片\43-1.jpg</t>
+  </si>
+  <si>
+    <t>首次进入兽人古战场地图，点击“离开地图”按钮没有响应，无法离开地图。</t>
+  </si>
+  <si>
+    <t>背包中有可以使用的筛子道具时，需要在提示按钮中增加一个“获得箱子”，点击之后打开包裹并自动选中筛子道具弹出道具详情页</t>
   </si>
 </sst>
 </file>
@@ -2255,8 +2261,12 @@
       <c r="A53" s="7">
         <v>44</v>
       </c>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
+      <c r="B53" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>98</v>
+      </c>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
     </row>
@@ -2264,8 +2274,12 @@
       <c r="A54" s="7">
         <v>45</v>
       </c>
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
+      <c r="B54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>99</v>
+      </c>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
     </row>
@@ -2273,14 +2287,16 @@
       <c r="A55" s="7">
         <v>46</v>
       </c>
-      <c r="B55" s="7"/>
+      <c r="B55" s="7" t="s">
+        <v>6</v>
+      </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B47 B48:B50 B51:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="104">
   <si>
     <t>编号</t>
   </si>
@@ -371,6 +371,18 @@
   </si>
   <si>
     <t>背包中有可以使用的筛子道具时，需要在提示按钮中增加一个“获得箱子”，点击之后打开包裹并自动选中筛子道具弹出道具详情页</t>
+  </si>
+  <si>
+    <t>免费VIP任务中的开箱次数达到XX个没有实现功能；另外就是VIP解锁对应会员地图的特权描述缺失</t>
+  </si>
+  <si>
+    <t>去除合成功能中的“角色装备”功能，去掉对应的功能页签，只保留魂石合成，升星宝石合成</t>
+  </si>
+  <si>
+    <t>在挂机地图挂机，击杀小怪之后会一直产出元宝，但是掉落里面并没有配置元宝，怀疑是把金币和元宝搞混了</t>
+  </si>
+  <si>
+    <t>挂机地图挂机了1个多小时，没有触发过战力首领，表格里面配置的几率是1/100</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1062,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1121,6 +1133,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1434,7 +1452,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.25" customWidth="1"/>
@@ -2288,11 +2306,57 @@
         <v>46</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>100</v>
+      </c>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
+    </row>
+    <row r="56" ht="16.5" spans="1:5">
+      <c r="A56" s="7">
+        <v>47</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57" ht="16.5" spans="1:5">
+      <c r="A57" s="7">
+        <v>48</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58" ht="16.5" spans="1:5">
+      <c r="A58" s="7">
+        <v>49</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+    </row>
+    <row r="59" ht="16.5" spans="1:1">
+      <c r="A59" s="7">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="107">
   <si>
     <t>编号</t>
   </si>
@@ -370,9 +370,15 @@
     <t>首次进入兽人古战场地图，点击“离开地图”按钮没有响应，无法离开地图。</t>
   </si>
   <si>
+    <t>切手机应用后会断线重连，断线重连后产生的问题，暂时没有好的方案</t>
+  </si>
+  <si>
     <t>背包中有可以使用的筛子道具时，需要在提示按钮中增加一个“获得箱子”，点击之后打开包裹并自动选中筛子道具弹出道具详情页</t>
   </si>
   <si>
+    <t>待增加</t>
+  </si>
+  <si>
     <t>免费VIP任务中的开箱次数达到XX个没有实现功能；另外就是VIP解锁对应会员地图的特权描述缺失</t>
   </si>
   <si>
@@ -383,6 +389,9 @@
   </si>
   <si>
     <t>挂机地图挂机了1个多小时，没有触发过战力首领，表格里面配置的几率是1/100</t>
+  </si>
+  <si>
+    <t>对应地图需要配置，已增加</t>
   </si>
 </sst>
 </file>
@@ -561,7 +570,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,6 +610,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -938,7 +953,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -962,16 +977,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -980,85 +995,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1084,6 +1099,9 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1135,10 +1153,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1463,19 +1478,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1483,206 +1498,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="10">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="14"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="7">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="7">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="7">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="7">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1691,19 +1706,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="7">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1712,19 +1727,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="7">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1733,19 +1748,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="7">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1754,17 +1769,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1773,588 +1788,600 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="7">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="7">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="8"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="15">
+      <c r="A20" s="16">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="7">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="7">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="7">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="7">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="7">
+      <c r="A25" s="8">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="15">
+      <c r="A26" s="16">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="15">
+      <c r="A27" s="16">
         <v>26</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="7">
+      <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="15">
+      <c r="A34" s="16">
         <v>28</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="15" t="s">
+      <c r="B34" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="15">
+      <c r="A35" s="16">
         <v>29</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="16" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="18">
+      <c r="A36" s="19">
         <v>30</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="18" t="s">
+      <c r="B36" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="19">
+      <c r="A37" s="20">
         <v>31</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="19" t="s">
+      <c r="B37" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="19"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="19">
+      <c r="A38" s="20">
         <v>32</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="19"/>
+      <c r="E38" s="20"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="15">
+      <c r="A39" s="16">
         <v>33</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="16"/>
+      <c r="F39" s="23" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="15">
+      <c r="A40" s="16">
         <v>34</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="15">
+      <c r="A41" s="16">
         <v>35</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="15">
+      <c r="A42" s="16">
         <v>36</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="15"/>
+      <c r="E42" s="16"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="15">
+      <c r="A43" s="16">
         <v>37</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="15"/>
+      <c r="E43" s="16"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="7">
+      <c r="A44" s="8">
         <v>38</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="B44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="7"/>
+      <c r="E44" s="8"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="23">
+      <c r="A45" s="24">
         <v>39</v>
       </c>
-      <c r="B45" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="23" t="s">
+      <c r="B45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="15">
+      <c r="A46" s="16">
         <v>40</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="15" t="s">
+      <c r="B46" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="15"/>
+      <c r="E46" s="16"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="15">
+      <c r="A47" s="16">
         <v>41</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="15" t="s">
+      <c r="B47" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="15"/>
+      <c r="E47" s="16"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="15"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="16"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="15"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="16"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="15"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="16"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="7">
+      <c r="A51" s="8">
         <v>42</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="7" t="s">
+      <c r="B51" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="7"/>
-    </row>
-    <row r="52" ht="16.5" spans="1:5">
-      <c r="A52" s="7">
+      <c r="E51" s="8"/>
+    </row>
+    <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A52" s="16">
         <v>43</v>
       </c>
-      <c r="B52" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="7" t="s">
+      <c r="B52" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="7"/>
-    </row>
-    <row r="53" ht="16.5" spans="1:5">
-      <c r="A53" s="7">
+      <c r="E52" s="16"/>
+      <c r="F52" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" s="7" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A53" s="25">
         <v>44</v>
       </c>
-      <c r="B53" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="7" t="s">
+      <c r="B53" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-    </row>
-    <row r="54" ht="16.5" spans="1:5">
-      <c r="A54" s="7">
+      <c r="D53" s="25"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" s="7" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A54" s="25">
         <v>45</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-    </row>
-    <row r="55" ht="16.5" spans="1:5">
-      <c r="A55" s="7">
+      <c r="C54" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A55" s="16">
         <v>46</v>
       </c>
-      <c r="B55" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-    </row>
-    <row r="56" ht="16.5" spans="1:5">
-      <c r="A56" s="7">
+      <c r="B55" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+    </row>
+    <row r="56" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A56" s="16">
         <v>47</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="B56" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="C56" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
     </row>
     <row r="57" ht="16.5" spans="1:5">
-      <c r="A57" s="7">
+      <c r="A57" s="8">
         <v>48</v>
       </c>
-      <c r="B57" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-    </row>
-    <row r="58" ht="16.5" spans="1:5">
-      <c r="A58" s="7">
+      <c r="B57" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+    </row>
+    <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A58" s="16">
         <v>49</v>
       </c>
-      <c r="B58" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D58" s="25"/>
-      <c r="E58" s="25"/>
+      <c r="B58" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="3" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="59" ht="16.5" spans="1:1">
-      <c r="A59" s="7">
+      <c r="A59" s="8">
         <v>50</v>
       </c>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="108">
   <si>
     <t>编号</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>在挂机地图挂机，击杀小怪之后会一直产出元宝，但是掉落里面并没有配置元宝，怀疑是把金币和元宝搞混了</t>
+  </si>
+  <si>
+    <t>可能是因为道具表1表示的是金币，修改item表</t>
   </si>
   <si>
     <t>挂机地图挂机了1个多小时，没有触发过战力首领，表格里面配置的几率是1/100</t>
@@ -1209,6 +1212,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FFFF00"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2351,18 +2359,21 @@
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
     </row>
-    <row r="57" ht="16.5" spans="1:5">
-      <c r="A57" s="8">
+    <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A57" s="16">
         <v>48</v>
       </c>
-      <c r="B57" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="8" t="s">
+      <c r="B57" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="3" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
       <c r="A58" s="16">
@@ -2372,12 +2383,12 @@
         <v>10</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
       <c r="F58" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:1">

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -2317,19 +2317,19 @@
         <v>99</v>
       </c>
     </row>
-    <row r="54" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="25">
+    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A54" s="16">
         <v>45</v>
       </c>
-      <c r="B54" s="25" t="s">
+      <c r="B54" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="7" t="s">
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="3" t="s">
         <v>101</v>
       </c>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="104">
   <si>
     <t>编号</t>
   </si>
@@ -370,15 +370,9 @@
     <t>首次进入兽人古战场地图，点击“离开地图”按钮没有响应，无法离开地图。</t>
   </si>
   <si>
-    <t>切手机应用后会断线重连，断线重连后产生的问题，暂时没有好的方案</t>
-  </si>
-  <si>
     <t>背包中有可以使用的筛子道具时，需要在提示按钮中增加一个“获得箱子”，点击之后打开包裹并自动选中筛子道具弹出道具详情页</t>
   </si>
   <si>
-    <t>待增加</t>
-  </si>
-  <si>
     <t>免费VIP任务中的开箱次数达到XX个没有实现功能；另外就是VIP解锁对应会员地图的特权描述缺失</t>
   </si>
   <si>
@@ -388,13 +382,7 @@
     <t>在挂机地图挂机，击杀小怪之后会一直产出元宝，但是掉落里面并没有配置元宝，怀疑是把金币和元宝搞混了</t>
   </si>
   <si>
-    <t>可能是因为道具表1表示的是金币，修改item表</t>
-  </si>
-  <si>
     <t>挂机地图挂机了1个多小时，没有触发过战力首领，表格里面配置的几率是1/100</t>
-  </si>
-  <si>
-    <t>对应地图需要配置，已增加</t>
   </si>
 </sst>
 </file>
@@ -573,7 +561,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,12 +601,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -956,7 +938,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -980,16 +962,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -998,89 +980,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1100,9 +1082,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1154,9 +1133,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1486,19 +1462,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1506,206 +1482,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" s="7"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="11">
+      <c r="A3" s="10">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="10"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="14">
+      <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="13"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="8">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="8">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1714,19 +1690,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1735,19 +1711,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1756,19 +1732,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1777,17 +1753,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1796,603 +1772,609 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="7"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="16">
+      <c r="A20" s="15">
         <v>19</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="8">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="8">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="8">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="8">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="16">
+      <c r="A26" s="15">
         <v>25</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="16">
+      <c r="A27" s="15">
         <v>26</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="8">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="16">
+      <c r="A34" s="15">
         <v>28</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B34" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="16">
+      <c r="A35" s="15">
         <v>29</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="15" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="19">
+      <c r="A36" s="18">
         <v>30</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="19" t="s">
+      <c r="B36" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="20">
+      <c r="A37" s="19">
         <v>31</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="20"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="20">
+      <c r="A38" s="19">
         <v>32</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="20" t="s">
+      <c r="B38" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="20"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="16">
+      <c r="A39" s="15">
         <v>33</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="23" t="s">
+      <c r="E39" s="15"/>
+      <c r="F39" s="22" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="16">
+      <c r="A40" s="15">
         <v>34</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="16">
+      <c r="A41" s="15">
         <v>35</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="16">
+      <c r="A42" s="15">
         <v>36</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="16"/>
+      <c r="E42" s="15"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="16">
+      <c r="A43" s="15">
         <v>37</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="16"/>
+      <c r="E43" s="15"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="8">
+      <c r="A44" s="7">
         <v>38</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="8"/>
+      <c r="E44" s="7"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="24">
+      <c r="A45" s="23">
         <v>39</v>
       </c>
-      <c r="B45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="24" t="s">
+      <c r="B45" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="16">
+      <c r="A46" s="15">
         <v>40</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="16" t="s">
+      <c r="B46" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="16"/>
+      <c r="E46" s="15"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="16">
+      <c r="A47" s="15">
         <v>41</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="16"/>
+      <c r="E47" s="15"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="16"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="15"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="16"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="15"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="16"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="15"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="15"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="8">
+      <c r="A51" s="7">
         <v>42</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="8" t="s">
+      <c r="B51" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="8"/>
+      <c r="E51" s="7"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="16">
+      <c r="A52" s="15">
         <v>43</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="B52" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="16"/>
+      <c r="E52" s="15"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="53" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="25">
+    <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A53" s="15">
         <v>44</v>
       </c>
-      <c r="B53" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="25" t="s">
+      <c r="B53" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="7" t="s">
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A54" s="15">
+        <v>45</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="16">
-        <v>45</v>
-      </c>
-      <c r="B54" s="16" t="s">
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A55" s="15">
+        <v>46</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A56" s="15">
+        <v>47</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="3" t="s">
+      <c r="C56" s="15" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="55" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A55" s="16">
-        <v>46</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="16" t="s">
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A57" s="15">
+        <v>48</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-    </row>
-    <row r="56" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A56" s="16">
-        <v>47</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="16" t="s">
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A58" s="15">
+        <v>49</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-    </row>
-    <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="16">
-        <v>48</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="16">
-        <v>49</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
       <c r="F58" s="3" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:1">
-      <c r="A59" s="8">
+      <c r="A59" s="7">
         <v>50</v>
       </c>
     </row>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="18350" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="121">
   <si>
     <t>编号</t>
   </si>
@@ -383,6 +383,57 @@
   </si>
   <si>
     <t>挂机地图挂机了1个多小时，没有触发过战力首领，表格里面配置的几率是1/100</t>
+  </si>
+  <si>
+    <t>VIP全身穿戴装备的任务点前往没反应，应该跳转到角色界面</t>
+  </si>
+  <si>
+    <t>问题图片\50.jpg</t>
+  </si>
+  <si>
+    <t>商城购买货币错乱，怀疑和你改怪物掉落元宝的bug相关，表格里面我配置的加速卷轴是元宝购买，结果现在好多道具都变成了金币购买</t>
+  </si>
+  <si>
+    <t>问题图片\51.jpg</t>
+  </si>
+  <si>
+    <t>会员之家地图，角色达到对应VIP等级之后也无法进入</t>
+  </si>
+  <si>
+    <t>问题图片\52.jpg</t>
+  </si>
+  <si>
+    <t>回馈大使功能，用模拟充值测试，达到对应充值条件也无法领取奖励，另外需要告知奖励配置的位置来调整内容</t>
+  </si>
+  <si>
+    <t>问题图片\53.jpg</t>
+  </si>
+  <si>
+    <t>充值界面文字错乱</t>
+  </si>
+  <si>
+    <t>问题图片\54.jpg</t>
+  </si>
+  <si>
+    <t>仍然没有添加法师和道士的技能，详见超链接文档</t>
+  </si>
+  <si>
+    <t>问题图片\技能等级.txt</t>
+  </si>
+  <si>
+    <t>用GM命令给角色加了8万攻击，但是打40级野外首领，只能打出2000多的伤害，数值严重不符合。</t>
+  </si>
+  <si>
+    <t>断线重连成功之后，感叹号按钮打开的弹框无法关闭。</t>
+  </si>
+  <si>
+    <t>问题图片\57.jpg</t>
+  </si>
+  <si>
+    <t>宝箱升级界面：1是没有显示当前等级和下一等级的数字；2是对应品质装备的开启几率与配置几率不符合</t>
+  </si>
+  <si>
+    <t>问题图片\58.jpg</t>
   </si>
 </sst>
 </file>
@@ -1062,7 +1113,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1133,6 +1184,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1451,14 +1505,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="121.25" customWidth="1"/>
+    <col min="3" max="3" width="121.254545454545" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="15.125" customWidth="1"/>
-    <col min="6" max="6" width="104.25" customWidth="1"/>
-    <col min="7" max="7" width="36.25" customWidth="1"/>
+    <col min="5" max="5" width="15.1272727272727" customWidth="1"/>
+    <col min="6" max="6" width="104.254545454545" customWidth="1"/>
+    <col min="7" max="7" width="36.2545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
@@ -1771,7 +1825,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="66" spans="1:6">
+    <row r="18" ht="82.5" spans="1:6">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2373,9 +2427,127 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:1">
+    <row r="59" ht="16.5" spans="1:4">
       <c r="A59" s="7">
         <v>50</v>
+      </c>
+      <c r="B59" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:4">
+      <c r="A60" s="15">
+        <v>51</v>
+      </c>
+      <c r="B60" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" t="s">
+        <v>106</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:4">
+      <c r="A61" s="7">
+        <v>52</v>
+      </c>
+      <c r="B61" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" t="s">
+        <v>108</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="1:4">
+      <c r="A62" s="15">
+        <v>53</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>110</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:4">
+      <c r="A63" s="7">
+        <v>54</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" s="24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="1:4">
+      <c r="A64" s="15">
+        <v>55</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:3">
+      <c r="A65" s="7">
+        <v>56</v>
+      </c>
+      <c r="B65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="1:4">
+      <c r="A66" s="15">
+        <v>57</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>117</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:4">
+      <c r="A67" s="7">
+        <v>58</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>119</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2408,6 +2580,14 @@
     <hyperlink ref="D47" r:id="rId21" display="问题图片\41-1.jpg"/>
     <hyperlink ref="D51" r:id="rId22" display="问题图片\42-1.jpg"/>
     <hyperlink ref="D52" r:id="rId23" display="问题图片\43-1.jpg"/>
+    <hyperlink ref="D59" r:id="rId24" display="问题图片\50.jpg"/>
+    <hyperlink ref="D60" r:id="rId25" display="问题图片\51.jpg"/>
+    <hyperlink ref="D61" r:id="rId26" display="问题图片\52.jpg"/>
+    <hyperlink ref="D62" r:id="rId27" display="问题图片\53.jpg"/>
+    <hyperlink ref="D63" r:id="rId28" display="问题图片\54.jpg"/>
+    <hyperlink ref="D64" r:id="rId29" display="问题图片\技能等级.txt"/>
+    <hyperlink ref="D66" r:id="rId30" display="问题图片\57.jpg"/>
+    <hyperlink ref="D67" r:id="rId31" display="问题图片\58.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2422,7 +2602,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2434,7 +2614,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="123">
   <si>
     <t>编号</t>
   </si>
@@ -434,6 +434,12 @@
   </si>
   <si>
     <t>问题图片\58.jpg</t>
+  </si>
+  <si>
+    <t>技能无法进阶，点击进阶提示：技能进阶失败</t>
+  </si>
+  <si>
+    <t>问题图片\59.jpg</t>
   </si>
 </sst>
 </file>
@@ -1505,7 +1511,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.254545454545" customWidth="1"/>
@@ -2548,6 +2554,20 @@
       </c>
       <c r="D67" s="24" t="s">
         <v>120</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:4">
+      <c r="A68" s="15">
+        <v>59</v>
+      </c>
+      <c r="B68" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" t="s">
+        <v>121</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2588,6 +2608,7 @@
     <hyperlink ref="D64" r:id="rId29" display="问题图片\技能等级.txt"/>
     <hyperlink ref="D66" r:id="rId30" display="问题图片\57.jpg"/>
     <hyperlink ref="D67" r:id="rId31" display="问题图片\58.jpg"/>
+    <hyperlink ref="D68" r:id="rId32" display="问题图片\59.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7590"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="129">
   <si>
     <t>编号</t>
   </si>
@@ -391,18 +391,27 @@
     <t>问题图片\50.jpg</t>
   </si>
   <si>
+    <t>以前没加</t>
+  </si>
+  <si>
     <t>商城购买货币错乱，怀疑和你改怪物掉落元宝的bug相关，表格里面我配置的加速卷轴是元宝购买，结果现在好多道具都变成了金币购买</t>
   </si>
   <si>
     <t>问题图片\51.jpg</t>
   </si>
   <si>
+    <t>商城的金币和元宝itemid换过</t>
+  </si>
+  <si>
     <t>会员之家地图，角色达到对应VIP等级之后也无法进入</t>
   </si>
   <si>
     <t>问题图片\52.jpg</t>
   </si>
   <si>
+    <t>写错写成3级了，其它对的，2，4,6,8</t>
+  </si>
+  <si>
     <t>回馈大使功能，用模拟充值测试，达到对应充值条件也无法领取奖励，另外需要告知奖励配置的位置来调整内容</t>
   </si>
   <si>
@@ -415,13 +424,22 @@
     <t>问题图片\54.jpg</t>
   </si>
   <si>
+    <t>去掉老的充值里面添加的内容</t>
+  </si>
+  <si>
     <t>仍然没有添加法师和道士的技能，详见超链接文档</t>
   </si>
   <si>
     <t>问题图片\技能等级.txt</t>
   </si>
   <si>
+    <t>技能都已添加，但技能效果需逐个测试</t>
+  </si>
+  <si>
     <t>用GM命令给角色加了8万攻击，但是打40级野外首领，只能打出2000多的伤害，数值严重不符合。</t>
+  </si>
+  <si>
+    <t>重新登录加的攻击就没有的，我打怪都是十来万的攻击，可以再截图看看</t>
   </si>
   <si>
     <t>断线重连成功之后，感叹号按钮打开的弹框无法关闭。</t>
@@ -618,7 +636,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -658,6 +676,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -995,7 +1019,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1019,16 +1043,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1037,89 +1061,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1139,6 +1163,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1192,7 +1219,25 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1511,30 +1556,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="121.254545454545" customWidth="1"/>
+    <col min="3" max="3" width="121.258333333333" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="15.1272727272727" customWidth="1"/>
-    <col min="6" max="6" width="104.254545454545" customWidth="1"/>
-    <col min="7" max="7" width="36.2545454545455" customWidth="1"/>
+    <col min="5" max="5" width="31.875" customWidth="1"/>
+    <col min="6" max="6" width="104.258333333333" customWidth="1"/>
+    <col min="7" max="7" width="36.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1542,206 +1587,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="7">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="10">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="13"/>
+      <c r="E5" s="14"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="7">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="7">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="7">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1750,19 +1795,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="7">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1771,19 +1816,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="7">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1792,19 +1837,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="7">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1813,17 +1858,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1831,748 +1876,822 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="82.5" spans="1:6">
-      <c r="A18" s="7">
+    <row r="18" ht="66" spans="1:6">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="7">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="8"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="15">
+      <c r="A20" s="16">
         <v>19</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="B20" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="7">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="7">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="7">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="7">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="7">
+      <c r="A25" s="8">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="15">
+      <c r="A26" s="16">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="15">
+      <c r="A27" s="16">
         <v>26</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="7">
+      <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="15">
+      <c r="A34" s="16">
         <v>28</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="15" t="s">
+      <c r="B34" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="16" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="15">
+      <c r="A35" s="16">
         <v>29</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="16" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="18">
+      <c r="A36" s="19">
         <v>30</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="18" t="s">
+      <c r="B36" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="19">
+      <c r="A37" s="20">
         <v>31</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="19" t="s">
+      <c r="B37" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="19"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="19">
+      <c r="A38" s="20">
         <v>32</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="B38" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="19"/>
+      <c r="E38" s="20"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="15">
+      <c r="A39" s="16">
         <v>33</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="15" t="s">
+      <c r="B39" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="22" t="s">
+      <c r="E39" s="16"/>
+      <c r="F39" s="23" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="15">
+      <c r="A40" s="16">
         <v>34</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="15">
+      <c r="A41" s="16">
         <v>35</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="15" t="s">
+      <c r="B41" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="15">
+      <c r="A42" s="16">
         <v>36</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="15"/>
+      <c r="E42" s="16"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="15">
+      <c r="A43" s="16">
         <v>37</v>
       </c>
-      <c r="B43" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="15" t="s">
+      <c r="B43" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="15"/>
+      <c r="E43" s="16"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="7">
+      <c r="A44" s="8">
         <v>38</v>
       </c>
-      <c r="B44" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="7" t="s">
+      <c r="B44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="7"/>
+      <c r="E44" s="8"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="23">
+      <c r="A45" s="24">
         <v>39</v>
       </c>
-      <c r="B45" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="23" t="s">
+      <c r="B45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="15">
+      <c r="A46" s="16">
         <v>40</v>
       </c>
-      <c r="B46" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="15" t="s">
+      <c r="B46" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="15"/>
+      <c r="E46" s="16"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="15">
+      <c r="A47" s="16">
         <v>41</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="15" t="s">
+      <c r="B47" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="15"/>
+      <c r="E47" s="16"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="15"/>
+      <c r="A48" s="16"/>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="16"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="15"/>
+      <c r="A49" s="16"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="16"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="15"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="15"/>
+      <c r="A50" s="16"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="16"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="7">
+      <c r="A51" s="8">
         <v>42</v>
       </c>
-      <c r="B51" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="7" t="s">
+      <c r="B51" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="7"/>
+      <c r="E51" s="8"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="15">
+      <c r="A52" s="16">
         <v>43</v>
       </c>
-      <c r="B52" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="15" t="s">
+      <c r="B52" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="15"/>
+      <c r="E52" s="16"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="15">
+      <c r="A53" s="16">
         <v>44</v>
       </c>
-      <c r="B53" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="15" t="s">
+      <c r="B53" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="15">
+      <c r="A54" s="16">
         <v>45</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="15"/>
-      <c r="E54" s="15"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="15">
+      <c r="A55" s="16">
         <v>46</v>
       </c>
-      <c r="B55" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="15" t="s">
+      <c r="B55" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="15">
+      <c r="A56" s="16">
         <v>47</v>
       </c>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="15" t="s">
+      <c r="C56" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="15"/>
-      <c r="E56" s="15"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="15">
+      <c r="A57" s="16">
         <v>48</v>
       </c>
-      <c r="B57" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="15" t="s">
+      <c r="B57" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="15"/>
-      <c r="E57" s="15"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="15">
+      <c r="A58" s="16">
         <v>49</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="15" t="s">
+      <c r="B58" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" ht="16.5" spans="1:4">
-      <c r="A59" s="7">
+    <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A59" s="16"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="25"/>
+    </row>
+    <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A60" s="16"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+    </row>
+    <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A61" s="16"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+    </row>
+    <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A62" s="16"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="25"/>
+    </row>
+    <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A63" s="16"/>
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+    </row>
+    <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A64" s="16">
         <v>50</v>
       </c>
-      <c r="B59" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="B64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D59" s="24" t="s">
+      <c r="D64" s="26" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:4">
-      <c r="A60" s="15">
+      <c r="E64" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" s="7" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A65" s="16">
         <v>51</v>
       </c>
-      <c r="B60" t="s">
-        <v>10</v>
-      </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" s="24" t="s">
+      <c r="B65" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:4">
-      <c r="A61" s="7">
+      <c r="D65" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A66" s="16">
         <v>52</v>
       </c>
-      <c r="B61" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>108</v>
-      </c>
-      <c r="D61" s="24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" ht="16.5" spans="1:4">
-      <c r="A62" s="15">
+      <c r="B66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:4">
+      <c r="A67" s="16">
         <v>53</v>
       </c>
-      <c r="B62" t="s">
-        <v>10</v>
-      </c>
-      <c r="C62" t="s">
-        <v>110</v>
-      </c>
-      <c r="D62" s="24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:4">
-      <c r="A63" s="7">
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A68" s="16">
         <v>54</v>
       </c>
-      <c r="B63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C63" t="s">
-        <v>112</v>
-      </c>
-      <c r="D63" s="24" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" ht="16.5" spans="1:4">
-      <c r="A64" s="15">
+      <c r="B68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D68" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A69" s="16">
         <v>55</v>
       </c>
-      <c r="B64" t="s">
-        <v>10</v>
-      </c>
-      <c r="C64" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:3">
-      <c r="A65" s="7">
+      <c r="B69" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A70" s="14">
         <v>56</v>
       </c>
-      <c r="B65" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="66" ht="16.5" spans="1:4">
-      <c r="A66" s="15">
+      <c r="B70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="1:4">
+      <c r="A71" s="16">
         <v>57</v>
       </c>
-      <c r="B66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:4">
-      <c r="A67" s="7">
+      <c r="B71" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" t="s">
+        <v>123</v>
+      </c>
+      <c r="D71" s="31" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A72" s="16">
         <v>58</v>
       </c>
-      <c r="B67" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:4">
-      <c r="A68" s="15">
+      <c r="B72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A73" s="16">
         <v>59</v>
       </c>
-      <c r="B68" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" t="s">
-        <v>121</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>122</v>
+      <c r="B73" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B58 B59:B63 B64:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2600,15 +2719,15 @@
     <hyperlink ref="D47" r:id="rId21" display="问题图片\41-1.jpg"/>
     <hyperlink ref="D51" r:id="rId22" display="问题图片\42-1.jpg"/>
     <hyperlink ref="D52" r:id="rId23" display="问题图片\43-1.jpg"/>
-    <hyperlink ref="D59" r:id="rId24" display="问题图片\50.jpg"/>
-    <hyperlink ref="D60" r:id="rId25" display="问题图片\51.jpg"/>
-    <hyperlink ref="D61" r:id="rId26" display="问题图片\52.jpg"/>
-    <hyperlink ref="D62" r:id="rId27" display="问题图片\53.jpg"/>
-    <hyperlink ref="D63" r:id="rId28" display="问题图片\54.jpg"/>
-    <hyperlink ref="D64" r:id="rId29" display="问题图片\技能等级.txt"/>
-    <hyperlink ref="D66" r:id="rId30" display="问题图片\57.jpg"/>
-    <hyperlink ref="D67" r:id="rId31" display="问题图片\58.jpg"/>
-    <hyperlink ref="D68" r:id="rId32" display="问题图片\59.jpg"/>
+    <hyperlink ref="D64" r:id="rId24" display="问题图片\50.jpg"/>
+    <hyperlink ref="D65" r:id="rId25" display="问题图片\51.jpg"/>
+    <hyperlink ref="D66" r:id="rId26" display="问题图片\52.jpg"/>
+    <hyperlink ref="D67" r:id="rId27" display="问题图片\53.jpg"/>
+    <hyperlink ref="D68" r:id="rId28" display="问题图片\54.jpg"/>
+    <hyperlink ref="D69" r:id="rId29" display="问题图片\技能等级.txt"/>
+    <hyperlink ref="D71" r:id="rId30" display="问题图片\57.jpg"/>
+    <hyperlink ref="D72" r:id="rId31" display="问题图片\58.jpg"/>
+    <hyperlink ref="D73" r:id="rId32" display="问题图片\59.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2623,7 +2742,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2635,7 +2754,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
   <si>
     <t>编号</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>问题图片\53.jpg</t>
+  </si>
+  <si>
+    <t>屏蔽该功能</t>
   </si>
   <si>
     <t>充值界面文字错乱</t>
@@ -636,7 +639,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -676,6 +679,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1019,7 +1028,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1043,16 +1052,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1061,85 +1070,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1168,6 +1177,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1225,19 +1237,16 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="6" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1567,19 +1576,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1587,206 +1596,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="8">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="11">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="12"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="8">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="9"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="8">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="8">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="8">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1795,19 +1804,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="8">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1816,19 +1825,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="8">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="9"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1837,19 +1846,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="8">
+      <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="9"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1858,17 +1867,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="8">
+      <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1877,644 +1886,644 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="8">
+      <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="8">
+      <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="9"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="16">
+      <c r="A20" s="17">
         <v>19</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="8">
+      <c r="A21" s="9">
         <v>20</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="8">
+      <c r="A22" s="9">
         <v>21</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="8">
+      <c r="A23" s="9">
         <v>22</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="8">
+      <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="8">
+      <c r="A25" s="9">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="16">
+      <c r="A26" s="17">
         <v>25</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="16">
+      <c r="A27" s="17">
         <v>26</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="8">
+      <c r="A28" s="9">
         <v>27</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="16">
+      <c r="A34" s="17">
         <v>28</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="16" t="s">
+      <c r="B34" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="F34" s="17" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="16">
+      <c r="A35" s="17">
         <v>29</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="17" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="19">
+      <c r="A36" s="20">
         <v>30</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="19" t="s">
+      <c r="B36" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="20">
+      <c r="A37" s="21">
         <v>31</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="20"/>
+      <c r="E37" s="21"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="20">
+      <c r="A38" s="21">
         <v>32</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="20" t="s">
+      <c r="B38" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="20"/>
+      <c r="E38" s="21"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="16">
+      <c r="A39" s="17">
         <v>33</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="23" t="s">
+      <c r="E39" s="17"/>
+      <c r="F39" s="24" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="16">
+      <c r="A40" s="17">
         <v>34</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="16">
+      <c r="A41" s="17">
         <v>35</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="16">
+      <c r="A42" s="17">
         <v>36</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="16"/>
+      <c r="E42" s="17"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="16">
+      <c r="A43" s="17">
         <v>37</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="16"/>
+      <c r="E43" s="17"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="8">
+      <c r="A44" s="9">
         <v>38</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="8" t="s">
+      <c r="B44" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="8"/>
+      <c r="E44" s="9"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="24">
+      <c r="A45" s="25">
         <v>39</v>
       </c>
-      <c r="B45" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="24" t="s">
+      <c r="B45" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="25"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="16">
+      <c r="A46" s="17">
         <v>40</v>
       </c>
-      <c r="B46" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="16" t="s">
+      <c r="B46" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="16"/>
+      <c r="E46" s="17"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="16">
+      <c r="A47" s="17">
         <v>41</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="16"/>
+      <c r="E47" s="17"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="16"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="17"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="16"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="17"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="16"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="17"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="8">
+      <c r="A51" s="9">
         <v>42</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="8" t="s">
+      <c r="B51" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="8"/>
+      <c r="E51" s="9"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="16">
+      <c r="A52" s="17">
         <v>43</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="B52" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="16"/>
+      <c r="E52" s="17"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="16">
+      <c r="A53" s="17">
         <v>44</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="B53" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="16">
+      <c r="A54" s="17">
         <v>45</v>
       </c>
-      <c r="B54" s="16" t="s">
+      <c r="B54" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="16">
+      <c r="A55" s="17">
         <v>46</v>
       </c>
-      <c r="B55" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="16" t="s">
+      <c r="B55" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
+      <c r="D55" s="17"/>
+      <c r="E55" s="17"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="16">
+      <c r="A56" s="17">
         <v>47</v>
       </c>
-      <c r="B56" s="16" t="s">
+      <c r="B56" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="16" t="s">
+      <c r="C56" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="17"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="16">
+      <c r="A57" s="17">
         <v>48</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="16" t="s">
+      <c r="B57" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
+      <c r="D57" s="17"/>
+      <c r="E57" s="17"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="16">
+      <c r="A58" s="17">
         <v>49</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="16" t="s">
+      <c r="B58" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A59" s="16"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25"/>
-      <c r="E59" s="25"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A60" s="16"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25"/>
-      <c r="E60" s="25"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A61" s="16"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A62" s="16"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25"/>
-      <c r="E62" s="25"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A63" s="16"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A64" s="16">
+      <c r="A64" s="17">
         <v>50</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -2523,7 +2532,7 @@
       <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D64" s="26" t="s">
+      <c r="D64" s="27" t="s">
         <v>105</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -2533,20 +2542,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A65" s="16">
+    <row r="65" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A65" s="17">
         <v>51</v>
       </c>
-      <c r="B65" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C65" s="7" t="s">
+      <c r="B65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="27" t="s">
+      <c r="D65" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="E65" s="7" t="s">
+      <c r="E65" s="3" t="s">
         <v>109</v>
       </c>
       <c r="F65" s="3" t="s">
@@ -2554,7 +2563,7 @@
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A66" s="16">
+      <c r="A66" s="17">
         <v>52</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -2573,125 +2582,131 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" ht="16.5" spans="1:4">
-      <c r="A67" s="16">
+    <row r="67" s="7" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A67" s="29">
         <v>53</v>
       </c>
-      <c r="B67" t="s">
-        <v>10</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="B67" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="30" t="s">
         <v>114</v>
       </c>
+      <c r="F67" s="7" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A68" s="16">
+      <c r="A68" s="17">
         <v>54</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D68" s="26" t="s">
         <v>116</v>
       </c>
+      <c r="D68" s="27" t="s">
+        <v>117</v>
+      </c>
       <c r="E68" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="69" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A69" s="16">
+    <row r="69" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A69" s="17">
         <v>55</v>
       </c>
-      <c r="B69" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" s="30" t="s">
+      <c r="B69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="D69" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="F69" s="7" t="s">
+      <c r="E69" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="70" s="2" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A70" s="14">
+      <c r="A70" s="15">
         <v>56</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="71" ht="16.5" spans="1:4">
-      <c r="A71" s="16">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" s="8" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A71" s="17">
         <v>57</v>
       </c>
-      <c r="B71" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" t="s">
-        <v>123</v>
+      <c r="B71" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>124</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A72" s="16">
+      <c r="A72" s="17">
         <v>58</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D72" s="26" t="s">
         <v>126</v>
       </c>
+      <c r="D72" s="27" t="s">
+        <v>127</v>
+      </c>
       <c r="F72" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A73" s="16">
+    <row r="73" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A73" s="17">
         <v>59</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D73" s="27" t="s">
+      <c r="B73" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="D73" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B58 B59:B63 B64:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="18350" windowHeight="7590"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="151">
   <si>
     <t>编号</t>
   </si>
@@ -430,7 +430,7 @@
     <t>去掉老的充值里面添加的内容</t>
   </si>
   <si>
-    <t>仍然没有添加法师和道士的技能，详见超链接文档</t>
+    <t>仍然没有添加法师和道士的技能，详见超链接文档，技能仍然没有看到，按照设定技能均为等级开启</t>
   </si>
   <si>
     <t>问题图片\技能等级.txt</t>
@@ -442,7 +442,10 @@
     <t>用GM命令给角色加了8万攻击，但是打40级野外首领，只能打出2000多的伤害，数值严重不符合。</t>
   </si>
   <si>
-    <t>重新登录加的攻击就没有的，我打怪都是十来万的攻击，可以再截图看看</t>
+    <t>问题图片\56-1.jpg</t>
+  </si>
+  <si>
+    <t>仍然不生效，没有重新登陆也没有断线重连</t>
   </si>
   <si>
     <t>断线重连成功之后，感叹号按钮打开的弹框无法关闭。</t>
@@ -461,6 +464,66 @@
   </si>
   <si>
     <t>问题图片\59.jpg</t>
+  </si>
+  <si>
+    <t>个人首领、野外首领击杀之后，掉落配置中的强化石、书页等道具没有在地面显示</t>
+  </si>
+  <si>
+    <t>灵玉副本，如果角色没有行会，点击“行会求助”按钮没有任何提示，应该提示：当前没有行会！</t>
+  </si>
+  <si>
+    <t>包裹已满的状态下，自动开箱异常，会快速的自动开箱，开出的装备无法获取，也没有分解，直接消失了，然后开箱次数也会一直扣除</t>
+  </si>
+  <si>
+    <t>灵玉副本内的离开按钮和行会求助按钮会被带出副本之外，详见截图，行会求助按钮还会带到野外boss和个人boss副本中</t>
+  </si>
+  <si>
+    <t>问题图片\63.jpg</t>
+  </si>
+  <si>
+    <t>行会求助按钮还会带到野外boss和个人boss副本中</t>
+  </si>
+  <si>
+    <t>问题图片\63-1.jpg</t>
+  </si>
+  <si>
+    <t>首充三日奖励，昨天已经领了首充第一日的奖励，但今天第二天了，第二天的奖励状态没有刷新，还是处于未解锁状态</t>
+  </si>
+  <si>
+    <t>问题图片\65.jpg</t>
+  </si>
+  <si>
+    <t>免费VIP任务中的开箱任务，点击前往按钮之后应该和主线任务的引导逻辑相同，即帮玩家开启一次箱子</t>
+  </si>
+  <si>
+    <t>宝箱升级界面，加速卷轴的消耗显示区域需要改成道具图标的方式，另外需要显示出来当前持有的数量，按照：道具图标+需要数量/持有数量   的方式显示</t>
+  </si>
+  <si>
+    <t>会员地图没有添加离开地图的按钮，需要添加一下</t>
+  </si>
+  <si>
+    <t>问题图片\69.jpg</t>
+  </si>
+  <si>
+    <t>战力首领触发之后，点击确定按钮无法进入战力首领副本，点击取消和确定按钮都没有响应，另外弹框中的按钮位置有偏移</t>
+  </si>
+  <si>
+    <t>问题图片\70.jpg</t>
+  </si>
+  <si>
+    <t>VIP2泡点经验加成是40%，但是实际上每秒增加的经验值是2100，和计算的不符合。基础是500.</t>
+  </si>
+  <si>
+    <t>几个挂机地图的进入等级限定现在没有生效，我一个18级的角色还是可以进入40级的兽人战场地图</t>
+  </si>
+  <si>
+    <t>问题图片\71.jpg</t>
+  </si>
+  <si>
+    <t>宝箱升级的界面层级还是不对，现在还是会被箱子挡住</t>
+  </si>
+  <si>
+    <t>问题图片\72.jpg</t>
   </si>
 </sst>
 </file>
@@ -639,7 +702,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -690,7 +753,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,7 +1097,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1052,16 +1121,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1070,89 +1139,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1178,6 +1247,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1246,7 +1318,16 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1565,30 +1646,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G73"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G86"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="121.258333333333" customWidth="1"/>
+    <col min="3" max="3" width="121.254545454545" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="31.875" customWidth="1"/>
-    <col min="6" max="6" width="104.258333333333" customWidth="1"/>
-    <col min="7" max="7" width="36.2583333333333" customWidth="1"/>
+    <col min="5" max="5" width="31.8727272727273" customWidth="1"/>
+    <col min="6" max="6" width="104.254545454545" customWidth="1"/>
+    <col min="7" max="7" width="36.2545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1596,206 +1677,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="9">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
+      <c r="E2" s="10"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="12">
+      <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="12"/>
+      <c r="E3" s="13"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="9">
+      <c r="A4" s="10">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="16"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="10"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="9">
+      <c r="A8" s="10">
         <v>7</v>
       </c>
-      <c r="B8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="9">
+      <c r="A9" s="10">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="9">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="9" t="s">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="9">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="9" t="s">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="9">
+      <c r="A12" s="10">
         <v>11</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="10"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="9">
+      <c r="A13" s="10">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="10"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1804,19 +1885,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="9">
+      <c r="A14" s="10">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="10"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1825,19 +1906,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="9">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="10"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1846,19 +1927,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="9">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="10"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1867,17 +1948,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="9">
+      <c r="A17" s="10">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1885,645 +1966,645 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="9">
+    <row r="18" ht="82.5" spans="1:6">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="9">
+      <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="9"/>
+      <c r="E19" s="10"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="17">
+      <c r="A20" s="18">
         <v>19</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="B20" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="9">
+      <c r="A21" s="10">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="9">
+      <c r="A22" s="10">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="9">
+      <c r="A23" s="10">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="9">
+      <c r="A24" s="10">
         <v>23</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="9">
+      <c r="A25" s="10">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="17">
+      <c r="A26" s="18">
         <v>25</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="17">
+      <c r="A27" s="18">
         <v>26</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="9">
+      <c r="A28" s="10">
         <v>27</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="17">
+      <c r="A34" s="18">
         <v>28</v>
       </c>
-      <c r="B34" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="17" t="s">
+      <c r="B34" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="18" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="17">
+      <c r="A35" s="18">
         <v>29</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="18" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="20">
+      <c r="A36" s="21">
         <v>30</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="21">
+      <c r="A37" s="22">
         <v>31</v>
       </c>
-      <c r="B37" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="21" t="s">
+      <c r="B37" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="21"/>
+      <c r="E37" s="22"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="21">
+      <c r="A38" s="22">
         <v>32</v>
       </c>
-      <c r="B38" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="21" t="s">
+      <c r="B38" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="21"/>
+      <c r="E38" s="22"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="17">
+      <c r="A39" s="18">
         <v>33</v>
       </c>
-      <c r="B39" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="B39" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="17"/>
-      <c r="F39" s="24" t="s">
+      <c r="E39" s="18"/>
+      <c r="F39" s="25" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="17">
+      <c r="A40" s="18">
         <v>34</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="17"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="17">
+      <c r="A41" s="18">
         <v>35</v>
       </c>
-      <c r="B41" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="17" t="s">
+      <c r="B41" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="17">
+      <c r="A42" s="18">
         <v>36</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="17"/>
+      <c r="E42" s="18"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="17">
+      <c r="A43" s="18">
         <v>37</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="B43" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="17"/>
+      <c r="E43" s="18"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="9">
+      <c r="A44" s="10">
         <v>38</v>
       </c>
-      <c r="B44" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="9" t="s">
+      <c r="B44" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="9"/>
+      <c r="E44" s="10"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="25">
+      <c r="A45" s="26">
         <v>39</v>
       </c>
-      <c r="B45" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="25" t="s">
+      <c r="B45" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="17">
+      <c r="A46" s="18">
         <v>40</v>
       </c>
-      <c r="B46" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="17" t="s">
+      <c r="B46" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="17"/>
+      <c r="E46" s="18"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="17">
+      <c r="A47" s="18">
         <v>41</v>
       </c>
-      <c r="B47" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="17" t="s">
+      <c r="B47" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="17"/>
+      <c r="E47" s="18"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="17"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="18"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="17"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="18"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="17"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="18"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="9">
+      <c r="A51" s="10">
         <v>42</v>
       </c>
-      <c r="B51" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="9" t="s">
+      <c r="B51" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="9"/>
+      <c r="E51" s="10"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="17">
+      <c r="A52" s="18">
         <v>43</v>
       </c>
-      <c r="B52" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="17" t="s">
+      <c r="B52" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="D52" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="17"/>
+      <c r="E52" s="18"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="17">
+      <c r="A53" s="18">
         <v>44</v>
       </c>
-      <c r="B53" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="17" t="s">
+      <c r="B53" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="17">
+      <c r="A54" s="18">
         <v>45</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="17">
+      <c r="A55" s="18">
         <v>46</v>
       </c>
-      <c r="B55" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="17" t="s">
+      <c r="B55" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="17">
+      <c r="A56" s="18">
         <v>47</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="17"/>
-      <c r="E56" s="17"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="17">
+      <c r="A57" s="18">
         <v>48</v>
       </c>
-      <c r="B57" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="17" t="s">
+      <c r="B57" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="17"/>
-      <c r="E57" s="17"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="17">
+      <c r="A58" s="18">
         <v>49</v>
       </c>
-      <c r="B58" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="17" t="s">
+      <c r="B58" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A59" s="17"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A60" s="17"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A61" s="17"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A62" s="17"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="27"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A63" s="17"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="27"/>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A64" s="17">
+      <c r="A64" s="18">
         <v>50</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -2532,7 +2613,7 @@
       <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="D64" s="28" t="s">
         <v>105</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -2543,7 +2624,7 @@
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A65" s="17">
+      <c r="A65" s="18">
         <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -2552,7 +2633,7 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D65" s="29" t="s">
         <v>108</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -2563,7 +2644,7 @@
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A66" s="17">
+      <c r="A66" s="18">
         <v>52</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -2572,7 +2653,7 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D66" s="29" t="s">
         <v>111</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -2583,7 +2664,7 @@
       </c>
     </row>
     <row r="67" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A67" s="29">
+      <c r="A67" s="30">
         <v>53</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -2592,7 +2673,7 @@
       <c r="C67" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D67" s="30" t="s">
+      <c r="D67" s="31" t="s">
         <v>114</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -2600,7 +2681,7 @@
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A68" s="17">
+      <c r="A68" s="18">
         <v>54</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -2609,7 +2690,7 @@
       <c r="C68" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D68" s="27" t="s">
+      <c r="D68" s="28" t="s">
         <v>117</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -2620,7 +2701,7 @@
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A69" s="17">
+      <c r="A69" s="18">
         <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -2629,7 +2710,7 @@
       <c r="C69" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D69" s="27" t="s">
+      <c r="D69" s="28" t="s">
         <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -2639,74 +2720,241 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A70" s="15">
+    <row r="70" s="8" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A70" s="32">
         <v>56</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="B70" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="D70" s="33" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="71" s="8" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A71" s="17">
+      <c r="E70" s="8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="71" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A71" s="18">
         <v>57</v>
       </c>
-      <c r="B71" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D71" s="31" t="s">
+      <c r="B71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F71" s="8" t="s">
+      <c r="D71" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A72" s="17">
+      <c r="A72" s="18">
         <v>58</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D72" s="27" t="s">
         <v>127</v>
       </c>
+      <c r="D72" s="28" t="s">
+        <v>128</v>
+      </c>
       <c r="F72" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A73" s="17">
+      <c r="A73" s="18">
         <v>59</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D73" s="28" t="s">
         <v>129</v>
       </c>
+      <c r="D73" s="29" t="s">
+        <v>130</v>
+      </c>
       <c r="F73" s="3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="74" s="9" customFormat="1" ht="16.5" spans="1:3">
+      <c r="A74" s="32">
+        <v>60</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="75" s="9" customFormat="1" ht="16.5" spans="1:3">
+      <c r="A75" s="32">
+        <v>61</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" s="9" customFormat="1" ht="16.5" spans="1:3">
+      <c r="A76" s="32">
+        <v>62</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" s="9" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A77" s="32">
+        <v>63</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="D77" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" s="9" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A78" s="32">
+        <v>64</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D78" s="34" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="79" s="9" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A79" s="32">
+        <v>65</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="80" ht="16.5" spans="1:3">
+      <c r="A80" s="32">
+        <v>66</v>
+      </c>
+      <c r="B80" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:3">
+      <c r="A81" s="32">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="82" ht="16.5" spans="1:4">
+      <c r="A82" s="32">
+        <v>68</v>
+      </c>
+      <c r="B82" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" t="s">
+        <v>142</v>
+      </c>
+      <c r="D82" s="35" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" ht="16.5" spans="1:4">
+      <c r="A83" s="32">
+        <v>69</v>
+      </c>
+      <c r="B83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" t="s">
+        <v>144</v>
+      </c>
+      <c r="D83" s="35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="84" ht="16.5" spans="1:3">
+      <c r="A84" s="32">
+        <v>70</v>
+      </c>
+      <c r="B84" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:4">
+      <c r="A85" s="32">
+        <v>71</v>
+      </c>
+      <c r="B85" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" t="s">
+        <v>147</v>
+      </c>
+      <c r="D85" s="35" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:4">
+      <c r="A86" s="32">
+        <v>72</v>
+      </c>
+      <c r="B86" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" t="s">
+        <v>149</v>
+      </c>
+      <c r="D86" s="35" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B79 B80:B83 B84:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2743,6 +2991,14 @@
     <hyperlink ref="D71" r:id="rId30" display="问题图片\57.jpg"/>
     <hyperlink ref="D72" r:id="rId31" display="问题图片\58.jpg"/>
     <hyperlink ref="D73" r:id="rId32" display="问题图片\59.jpg"/>
+    <hyperlink ref="D70" r:id="rId33" display="问题图片\56-1.jpg"/>
+    <hyperlink ref="D77" r:id="rId34" display="问题图片\63.jpg"/>
+    <hyperlink ref="D78" r:id="rId35" display="问题图片\63-1.jpg"/>
+    <hyperlink ref="D79" r:id="rId36" display="问题图片\65.jpg"/>
+    <hyperlink ref="D82" r:id="rId37" display="问题图片\69.jpg"/>
+    <hyperlink ref="D83" r:id="rId38" display="问题图片\70.jpg"/>
+    <hyperlink ref="D85" r:id="rId39" display="问题图片\71.jpg"/>
+    <hyperlink ref="D86" r:id="rId40" display="问题图片\72.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2757,7 +3013,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2769,7 +3025,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7590"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="159">
   <si>
     <t>编号</t>
   </si>
@@ -481,6 +481,9 @@
     <t>问题图片\63.jpg</t>
   </si>
   <si>
+    <t>这是断线重连导致的</t>
+  </si>
+  <si>
     <t>行会求助按钮还会带到野外boss和个人boss副本中</t>
   </si>
   <si>
@@ -493,9 +496,15 @@
     <t>问题图片\65.jpg</t>
   </si>
   <si>
+    <t>我这边调时间看过没有问题的，服务器上状态可能不太对</t>
+  </si>
+  <si>
     <t>免费VIP任务中的开箱任务，点击前往按钮之后应该和主线任务的引导逻辑相同，即帮玩家开启一次箱子</t>
   </si>
   <si>
+    <t>这个正常逻辑是和主线任务一样，看是不是包裹满后的异常情况，暂时没有复现</t>
+  </si>
+  <si>
     <t>宝箱升级界面，加速卷轴的消耗显示区域需要改成道具图标的方式，另外需要显示出来当前持有的数量，按照：道具图标+需要数量/持有数量   的方式显示</t>
   </si>
   <si>
@@ -505,15 +514,27 @@
     <t>问题图片\69.jpg</t>
   </si>
   <si>
+    <t>已添加</t>
+  </si>
+  <si>
     <t>战力首领触发之后，点击确定按钮无法进入战力首领副本，点击取消和确定按钮都没有响应，另外弹框中的按钮位置有偏移</t>
   </si>
   <si>
     <t>问题图片\70.jpg</t>
   </si>
   <si>
+    <t>复活相关的都有问题</t>
+  </si>
+  <si>
     <t>VIP2泡点经验加成是40%，但是实际上每秒增加的经验值是2100，和计算的不符合。基础是500.</t>
   </si>
   <si>
+    <t>我计算的是对的</t>
+  </si>
+  <si>
+    <t>待确认下</t>
+  </si>
+  <si>
     <t>几个挂机地图的进入等级限定现在没有生效，我一个18级的角色还是可以进入40级的兽人战场地图</t>
   </si>
   <si>
@@ -524,6 +545,9 @@
   </si>
   <si>
     <t>问题图片\72.jpg</t>
+  </si>
+  <si>
+    <t>暂时无复现</t>
   </si>
 </sst>
 </file>
@@ -702,7 +726,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="42">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -759,7 +783,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1097,7 +1145,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1121,16 +1169,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1139,25 +1187,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1220,8 +1256,20 @@
     <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1250,6 +1298,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1324,10 +1381,22 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1646,30 +1715,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G86"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:G91"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="121.254545454545" customWidth="1"/>
+    <col min="3" max="3" width="121.258333333333" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="31.8727272727273" customWidth="1"/>
-    <col min="6" max="6" width="104.254545454545" customWidth="1"/>
-    <col min="7" max="7" width="36.2545454545455" customWidth="1"/>
+    <col min="5" max="5" width="31.875" customWidth="1"/>
+    <col min="6" max="6" width="104.258333333333" customWidth="1"/>
+    <col min="7" max="7" width="36.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1677,206 +1746,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="10">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="13"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="13">
+      <c r="A3" s="16">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="13"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="10">
+      <c r="A4" s="13">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="16">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="19"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="10">
+      <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="13"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="10">
+      <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="10">
+      <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="10">
+      <c r="A9" s="13">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="A10" s="13">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="A11" s="13">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="10">
+      <c r="A12" s="13">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="B12" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="13"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="10">
+      <c r="A13" s="13">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="10"/>
+      <c r="E13" s="13"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1885,19 +1954,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="10">
+      <c r="A14" s="13">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="10"/>
+      <c r="E14" s="13"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1906,19 +1975,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="10">
+      <c r="A15" s="13">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="10" t="s">
+      <c r="B15" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="10"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1927,19 +1996,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="10">
+      <c r="A16" s="13">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="10"/>
+      <c r="E16" s="13"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -1948,17 +2017,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="10">
+      <c r="A17" s="13">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -1966,645 +2035,645 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="82.5" spans="1:6">
-      <c r="A18" s="10">
+    <row r="18" ht="66" spans="1:6">
+      <c r="A18" s="13">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="10">
+      <c r="A19" s="13">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="10"/>
+      <c r="E19" s="13"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="18">
+      <c r="A20" s="21">
         <v>19</v>
       </c>
-      <c r="B20" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="18" t="s">
+      <c r="B20" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="10">
+      <c r="A21" s="13">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="10">
+      <c r="A22" s="13">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="10">
+      <c r="A23" s="13">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="10">
+      <c r="A24" s="13">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="10">
+      <c r="A25" s="13">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="18">
+      <c r="A26" s="21">
         <v>25</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="18">
+      <c r="A27" s="21">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="10">
+      <c r="A28" s="13">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="18">
+      <c r="A34" s="21">
         <v>28</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="18" t="s">
+      <c r="B34" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="18" t="s">
+      <c r="F34" s="21" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="18">
+      <c r="A35" s="21">
         <v>29</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="21">
+      <c r="A36" s="24">
         <v>30</v>
       </c>
-      <c r="B36" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="21" t="s">
+      <c r="B36" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="22">
+      <c r="A37" s="25">
         <v>31</v>
       </c>
-      <c r="B37" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="22" t="s">
+      <c r="B37" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="22"/>
+      <c r="E37" s="25"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="22">
+      <c r="A38" s="25">
         <v>32</v>
       </c>
-      <c r="B38" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="22" t="s">
+      <c r="B38" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="24" t="s">
+      <c r="D38" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="22"/>
+      <c r="E38" s="25"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="18">
+      <c r="A39" s="21">
         <v>33</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="18" t="s">
+      <c r="B39" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="25" t="s">
+      <c r="E39" s="21"/>
+      <c r="F39" s="28" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="18">
+      <c r="A40" s="21">
         <v>34</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="18">
+      <c r="A41" s="21">
         <v>35</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="18" t="s">
+      <c r="B41" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="18">
+      <c r="A42" s="21">
         <v>36</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="18"/>
+      <c r="E42" s="21"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="18">
+      <c r="A43" s="21">
         <v>37</v>
       </c>
-      <c r="B43" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="18" t="s">
+      <c r="B43" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="18"/>
+      <c r="E43" s="21"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="10">
+      <c r="A44" s="13">
         <v>38</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="10" t="s">
+      <c r="B44" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="10"/>
+      <c r="E44" s="13"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="26">
+      <c r="A45" s="29">
         <v>39</v>
       </c>
-      <c r="B45" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="26" t="s">
+      <c r="B45" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="18">
+      <c r="A46" s="21">
         <v>40</v>
       </c>
-      <c r="B46" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="18" t="s">
+      <c r="B46" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="18"/>
+      <c r="E46" s="21"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="18">
+      <c r="A47" s="21">
         <v>41</v>
       </c>
-      <c r="B47" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="18" t="s">
+      <c r="B47" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="20" t="s">
+      <c r="D47" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="18"/>
+      <c r="E47" s="21"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="18"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="18"/>
-      <c r="B49" s="18"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="18"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="21"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="18"/>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="18"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="10">
+      <c r="A51" s="13">
         <v>42</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="10" t="s">
+      <c r="B51" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="10"/>
+      <c r="E51" s="13"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="18">
+      <c r="A52" s="21">
         <v>43</v>
       </c>
-      <c r="B52" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="18" t="s">
+      <c r="B52" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="18"/>
+      <c r="E52" s="21"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="18">
+      <c r="A53" s="21">
         <v>44</v>
       </c>
-      <c r="B53" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="18" t="s">
+      <c r="B53" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="18"/>
-      <c r="E53" s="18"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="18">
+      <c r="A54" s="21">
         <v>45</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="18">
+      <c r="A55" s="21">
         <v>46</v>
       </c>
-      <c r="B55" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="18" t="s">
+      <c r="B55" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="18">
+      <c r="A56" s="21">
         <v>47</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="18">
+      <c r="A57" s="21">
         <v>48</v>
       </c>
-      <c r="B57" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="18" t="s">
+      <c r="B57" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="18">
+      <c r="A58" s="21">
         <v>49</v>
       </c>
-      <c r="B58" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="18" t="s">
+      <c r="B58" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A59" s="18"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A60" s="18"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
+      <c r="A60" s="21"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A61" s="18"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
+      <c r="A61" s="21"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A62" s="18"/>
-      <c r="B62" s="27"/>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-      <c r="E62" s="27"/>
+      <c r="A62" s="21"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A63" s="18"/>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
+      <c r="A63" s="21"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A64" s="18">
+      <c r="A64" s="21">
         <v>50</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -2613,7 +2682,7 @@
       <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D64" s="31" t="s">
         <v>105</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -2624,7 +2693,7 @@
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A65" s="18">
+      <c r="A65" s="21">
         <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -2633,7 +2702,7 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="32" t="s">
         <v>108</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -2644,7 +2713,7 @@
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A66" s="18">
+      <c r="A66" s="21">
         <v>52</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -2653,7 +2722,7 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="32" t="s">
         <v>111</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -2664,7 +2733,7 @@
       </c>
     </row>
     <row r="67" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A67" s="30">
+      <c r="A67" s="33">
         <v>53</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -2673,7 +2742,7 @@
       <c r="C67" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D67" s="31" t="s">
+      <c r="D67" s="34" t="s">
         <v>114</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -2681,7 +2750,7 @@
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A68" s="18">
+      <c r="A68" s="21">
         <v>54</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -2690,7 +2759,7 @@
       <c r="C68" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" s="31" t="s">
         <v>117</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -2701,7 +2770,7 @@
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A69" s="18">
+      <c r="A69" s="21">
         <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -2710,7 +2779,7 @@
       <c r="C69" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D69" s="31" t="s">
         <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -2721,7 +2790,7 @@
       </c>
     </row>
     <row r="70" s="8" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A70" s="32">
+      <c r="A70" s="35">
         <v>56</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -2730,7 +2799,7 @@
       <c r="C70" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="33" t="s">
+      <c r="D70" s="36" t="s">
         <v>123</v>
       </c>
       <c r="E70" s="8" t="s">
@@ -2738,7 +2807,7 @@
       </c>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A71" s="18">
+      <c r="A71" s="21">
         <v>57</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -2747,7 +2816,7 @@
       <c r="C71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" s="31" t="s">
         <v>126</v>
       </c>
       <c r="F71" s="3" t="s">
@@ -2755,7 +2824,7 @@
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A72" s="18">
+      <c r="A72" s="21">
         <v>58</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -2764,7 +2833,7 @@
       <c r="C72" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="D72" s="31" t="s">
         <v>128</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -2772,7 +2841,7 @@
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A73" s="18">
+      <c r="A73" s="21">
         <v>59</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -2781,180 +2850,245 @@
       <c r="C73" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D73" s="29" t="s">
+      <c r="D73" s="32" t="s">
         <v>130</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" s="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A74" s="32">
+    <row r="74" s="3" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A74" s="21"/>
+      <c r="D74" s="32"/>
+    </row>
+    <row r="75" s="3" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A75" s="21"/>
+      <c r="D75" s="32"/>
+    </row>
+    <row r="76" s="3" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A76" s="21"/>
+      <c r="D76" s="32"/>
+    </row>
+    <row r="77" s="3" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A77" s="21"/>
+      <c r="D77" s="32"/>
+    </row>
+    <row r="78" s="3" customFormat="1" ht="16.5" spans="1:4">
+      <c r="A78" s="21"/>
+      <c r="D78" s="32"/>
+    </row>
+    <row r="79" s="8" customFormat="1" ht="16.5" spans="1:3">
+      <c r="A79" s="35">
         <v>60</v>
       </c>
-      <c r="B74" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C74" s="9" t="s">
+      <c r="B79" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="75" s="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A75" s="32">
+    <row r="80" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A80" s="21">
         <v>61</v>
       </c>
-      <c r="B75" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="9" t="s">
+      <c r="B80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="76" s="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A76" s="32">
+      <c r="F80" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" s="8" customFormat="1" ht="16.5" spans="1:3">
+      <c r="A81" s="35">
         <v>62</v>
       </c>
-      <c r="B76" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="9" t="s">
+      <c r="B81" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="77" s="9" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A77" s="32">
+    <row r="82" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A82" s="21">
         <v>63</v>
       </c>
-      <c r="B77" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C77" s="9" t="s">
+      <c r="B82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D77" s="34" t="s">
+      <c r="D82" s="32" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="78" s="9" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A78" s="32">
+      <c r="E82" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A83" s="21">
         <v>64</v>
       </c>
-      <c r="B78" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="9" t="s">
+      <c r="B83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D83" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="34" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="79" s="9" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A79" s="32">
+      <c r="F83" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" s="9" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A84" s="37">
         <v>65</v>
       </c>
-      <c r="B79" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="D79" s="34" t="s">
+      <c r="B84" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="9" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="80" ht="16.5" spans="1:3">
-      <c r="A80" s="32">
+      <c r="D84" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" s="10" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A85" s="37">
         <v>66</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B85" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C80" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="81" ht="16.5" spans="1:3">
-      <c r="A81" s="32">
+      <c r="C85" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="86" s="11" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A86" s="21">
         <v>67</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B86" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C81" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="82" ht="16.5" spans="1:4">
-      <c r="A82" s="32">
+      <c r="C86" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F86" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" s="11" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A87" s="21">
         <v>68</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B87" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C82" t="s">
-        <v>142</v>
-      </c>
-      <c r="D82" s="35" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="83" ht="16.5" spans="1:4">
-      <c r="A83" s="32">
+      <c r="C87" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D87" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="F87" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="88" s="11" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A88" s="21">
         <v>69</v>
       </c>
-      <c r="B83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C83" t="s">
-        <v>144</v>
-      </c>
-      <c r="D83" s="35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="84" ht="16.5" spans="1:3">
-      <c r="A84" s="32">
+      <c r="B88" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F88" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" s="11" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A89" s="21">
         <v>70</v>
       </c>
-      <c r="B84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="85" ht="16.5" spans="1:4">
-      <c r="A85" s="32">
+      <c r="B89" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E89" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F89" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90" s="11" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A90" s="21">
         <v>71</v>
       </c>
-      <c r="B85" t="s">
-        <v>10</v>
-      </c>
-      <c r="C85" t="s">
-        <v>147</v>
-      </c>
-      <c r="D85" s="35" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="86" ht="16.5" spans="1:4">
-      <c r="A86" s="32">
+      <c r="B90" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="F90" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" s="12" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A91" s="41">
         <v>72</v>
       </c>
-      <c r="B86" t="s">
-        <v>10</v>
-      </c>
-      <c r="C86" t="s">
-        <v>149</v>
-      </c>
-      <c r="D86" s="35" t="s">
-        <v>150</v>
+      <c r="B91" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D91" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B79 B80:B83 B84:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B73 B74:B78 B79:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2992,13 +3126,13 @@
     <hyperlink ref="D72" r:id="rId31" display="问题图片\58.jpg"/>
     <hyperlink ref="D73" r:id="rId32" display="问题图片\59.jpg"/>
     <hyperlink ref="D70" r:id="rId33" display="问题图片\56-1.jpg"/>
-    <hyperlink ref="D77" r:id="rId34" display="问题图片\63.jpg"/>
-    <hyperlink ref="D78" r:id="rId35" display="问题图片\63-1.jpg"/>
-    <hyperlink ref="D79" r:id="rId36" display="问题图片\65.jpg"/>
-    <hyperlink ref="D82" r:id="rId37" display="问题图片\69.jpg"/>
-    <hyperlink ref="D83" r:id="rId38" display="问题图片\70.jpg"/>
-    <hyperlink ref="D85" r:id="rId39" display="问题图片\71.jpg"/>
-    <hyperlink ref="D86" r:id="rId40" display="问题图片\72.jpg"/>
+    <hyperlink ref="D82" r:id="rId34" display="问题图片\63.jpg"/>
+    <hyperlink ref="D83" r:id="rId35" display="问题图片\63-1.jpg"/>
+    <hyperlink ref="D84" r:id="rId36" display="问题图片\65.jpg"/>
+    <hyperlink ref="D87" r:id="rId37" display="问题图片\69.jpg"/>
+    <hyperlink ref="D88" r:id="rId38" display="问题图片\70.jpg"/>
+    <hyperlink ref="D90" r:id="rId39" display="问题图片\71.jpg"/>
+    <hyperlink ref="D91" r:id="rId40" display="问题图片\72.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3013,7 +3147,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3025,7 +3159,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="160">
   <si>
     <t>编号</t>
   </si>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>包裹已满的状态下，自动开箱异常，会快速的自动开箱，开出的装备无法获取，也没有分解，直接消失了，然后开箱次数也会一直扣除</t>
+  </si>
+  <si>
+    <t>包裹已满的时候开不了箱，具体再看看如何复现</t>
   </si>
   <si>
     <t>灵玉副本内的离开按钮和行会求助按钮会被带出副本之外，详见截图，行会求助按钮还会带到野外boss和个人boss副本中</t>
@@ -726,7 +729,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -783,31 +786,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1145,7 +1130,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1169,16 +1154,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1187,89 +1172,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1297,16 +1282,13 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1384,19 +1366,16 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="6" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="6" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1726,19 +1705,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1746,206 +1725,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13"/>
+      <c r="E2" s="12"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="16">
+      <c r="A3" s="15">
         <v>2</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="16"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="19"/>
+      <c r="E5" s="18"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="13"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="13">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="13" t="s">
+      <c r="B8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="13">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="13" t="s">
+      <c r="A10" s="12">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="13">
-        <v>10</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="A11" s="12">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="13">
+      <c r="A12" s="12">
         <v>11</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="13"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <v>12</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="13"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -1954,19 +1933,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="13">
+      <c r="A14" s="12">
         <v>13</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="12"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -1975,19 +1954,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="13">
+      <c r="A15" s="12">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="13" t="s">
+      <c r="B15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="13"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1996,19 +1975,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="13">
+      <c r="A16" s="12">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="13"/>
+      <c r="E16" s="12"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -2017,17 +1996,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="13">
+      <c r="A17" s="12">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="B17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -2036,644 +2015,644 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="13" t="s">
+      <c r="B19" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="13"/>
+      <c r="E19" s="12"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="21">
+      <c r="A20" s="20">
         <v>19</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="21" t="s">
+      <c r="B20" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <v>20</v>
       </c>
-      <c r="B21" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="13" t="s">
+      <c r="B21" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <v>21</v>
       </c>
-      <c r="B22" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="13" t="s">
+      <c r="B22" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="13">
+      <c r="A23" s="12">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="13">
+      <c r="A24" s="12">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="13" t="s">
+      <c r="B24" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="13">
+      <c r="A25" s="12">
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="21">
+      <c r="A26" s="20">
         <v>25</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="21">
+      <c r="A27" s="20">
         <v>26</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="13">
+      <c r="A28" s="12">
         <v>27</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="21">
+      <c r="A34" s="20">
         <v>28</v>
       </c>
-      <c r="B34" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="21" t="s">
+      <c r="B34" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="20" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="21">
+      <c r="A35" s="20">
         <v>29</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="21" t="s">
+      <c r="C35" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="20" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="24">
+      <c r="A36" s="23">
         <v>30</v>
       </c>
-      <c r="B36" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="24" t="s">
+      <c r="B36" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="25">
+      <c r="A37" s="24">
         <v>31</v>
       </c>
-      <c r="B37" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="25" t="s">
+      <c r="B37" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="26" t="s">
+      <c r="D37" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="25"/>
+      <c r="E37" s="24"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="25">
+      <c r="A38" s="24">
         <v>32</v>
       </c>
-      <c r="B38" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="25" t="s">
+      <c r="B38" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="25"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="21">
+      <c r="A39" s="20">
         <v>33</v>
       </c>
-      <c r="B39" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="21" t="s">
+      <c r="B39" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="21"/>
-      <c r="F39" s="28" t="s">
+      <c r="E39" s="20"/>
+      <c r="F39" s="27" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="21">
+      <c r="A40" s="20">
         <v>34</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="21">
+      <c r="A41" s="20">
         <v>35</v>
       </c>
-      <c r="B41" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="21" t="s">
+      <c r="B41" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="21">
+      <c r="A42" s="20">
         <v>36</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="21"/>
+      <c r="E42" s="20"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="21">
+      <c r="A43" s="20">
         <v>37</v>
       </c>
-      <c r="B43" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="21" t="s">
+      <c r="B43" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="23" t="s">
+      <c r="D43" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="21"/>
+      <c r="E43" s="20"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="13">
+      <c r="A44" s="12">
         <v>38</v>
       </c>
-      <c r="B44" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="13" t="s">
+      <c r="B44" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="13"/>
+      <c r="E44" s="12"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="29">
+      <c r="A45" s="28">
         <v>39</v>
       </c>
-      <c r="B45" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="29" t="s">
+      <c r="B45" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="21">
+      <c r="A46" s="20">
         <v>40</v>
       </c>
-      <c r="B46" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="21" t="s">
+      <c r="B46" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="21"/>
+      <c r="E46" s="20"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="21">
+      <c r="A47" s="20">
         <v>41</v>
       </c>
-      <c r="B47" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="21" t="s">
+      <c r="B47" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="21"/>
+      <c r="E47" s="20"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="21"/>
-      <c r="B48" s="21"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="21"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="20"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="21"/>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="21"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="20"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="21"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="21"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="20"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="13">
+      <c r="A51" s="12">
         <v>42</v>
       </c>
-      <c r="B51" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="13" t="s">
+      <c r="B51" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="13"/>
+      <c r="E51" s="12"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="21">
+      <c r="A52" s="20">
         <v>43</v>
       </c>
-      <c r="B52" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="21" t="s">
+      <c r="B52" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="23" t="s">
+      <c r="D52" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="21"/>
+      <c r="E52" s="20"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="21">
+      <c r="A53" s="20">
         <v>44</v>
       </c>
-      <c r="B53" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="21" t="s">
+      <c r="B53" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="21">
+      <c r="A54" s="20">
         <v>45</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B54" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="21">
+      <c r="A55" s="20">
         <v>46</v>
       </c>
-      <c r="B55" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="21" t="s">
+      <c r="B55" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="21">
+      <c r="A56" s="20">
         <v>47</v>
       </c>
-      <c r="B56" s="21" t="s">
+      <c r="B56" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="21" t="s">
+      <c r="C56" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="21"/>
-      <c r="E56" s="21"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="21">
+      <c r="A57" s="20">
         <v>48</v>
       </c>
-      <c r="B57" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="21" t="s">
+      <c r="B57" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="21">
+      <c r="A58" s="20">
         <v>49</v>
       </c>
-      <c r="B58" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="21" t="s">
+      <c r="B58" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A59" s="21"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
+      <c r="A59" s="20"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="29"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A60" s="21"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="29"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A61" s="21"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
+      <c r="A61" s="20"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A62" s="21"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
+      <c r="A62" s="20"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="29"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A63" s="21"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
+      <c r="A63" s="20"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A64" s="21">
+      <c r="A64" s="20">
         <v>50</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -2682,7 +2661,7 @@
       <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D64" s="31" t="s">
+      <c r="D64" s="30" t="s">
         <v>105</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -2693,7 +2672,7 @@
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A65" s="21">
+      <c r="A65" s="20">
         <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -2702,7 +2681,7 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="32" t="s">
+      <c r="D65" s="31" t="s">
         <v>108</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -2713,7 +2692,7 @@
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A66" s="21">
+      <c r="A66" s="20">
         <v>52</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -2722,7 +2701,7 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="32" t="s">
+      <c r="D66" s="31" t="s">
         <v>111</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -2733,7 +2712,7 @@
       </c>
     </row>
     <row r="67" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A67" s="33">
+      <c r="A67" s="32">
         <v>53</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -2742,7 +2721,7 @@
       <c r="C67" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="33" t="s">
         <v>114</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -2750,7 +2729,7 @@
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A68" s="21">
+      <c r="A68" s="20">
         <v>54</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -2759,7 +2738,7 @@
       <c r="C68" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D68" s="31" t="s">
+      <c r="D68" s="30" t="s">
         <v>117</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -2770,7 +2749,7 @@
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A69" s="21">
+      <c r="A69" s="20">
         <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -2779,7 +2758,7 @@
       <c r="C69" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D69" s="31" t="s">
+      <c r="D69" s="30" t="s">
         <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -2790,7 +2769,7 @@
       </c>
     </row>
     <row r="70" s="8" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A70" s="35">
+      <c r="A70" s="34">
         <v>56</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -2799,7 +2778,7 @@
       <c r="C70" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="36" t="s">
+      <c r="D70" s="35" t="s">
         <v>123</v>
       </c>
       <c r="E70" s="8" t="s">
@@ -2807,7 +2786,7 @@
       </c>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A71" s="21">
+      <c r="A71" s="20">
         <v>57</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -2816,7 +2795,7 @@
       <c r="C71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D71" s="31" t="s">
+      <c r="D71" s="30" t="s">
         <v>126</v>
       </c>
       <c r="F71" s="3" t="s">
@@ -2824,7 +2803,7 @@
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A72" s="21">
+      <c r="A72" s="20">
         <v>58</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -2833,7 +2812,7 @@
       <c r="C72" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="31" t="s">
+      <c r="D72" s="30" t="s">
         <v>128</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -2841,7 +2820,7 @@
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A73" s="21">
+      <c r="A73" s="20">
         <v>59</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -2850,7 +2829,7 @@
       <c r="C73" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D73" s="32" t="s">
+      <c r="D73" s="31" t="s">
         <v>130</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -2858,27 +2837,27 @@
       </c>
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A74" s="21"/>
-      <c r="D74" s="32"/>
+      <c r="A74" s="20"/>
+      <c r="D74" s="31"/>
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A75" s="21"/>
-      <c r="D75" s="32"/>
+      <c r="A75" s="20"/>
+      <c r="D75" s="31"/>
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A76" s="21"/>
-      <c r="D76" s="32"/>
+      <c r="A76" s="20"/>
+      <c r="D76" s="31"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A77" s="21"/>
-      <c r="D77" s="32"/>
+      <c r="A77" s="20"/>
+      <c r="D77" s="31"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A78" s="21"/>
-      <c r="D78" s="32"/>
+      <c r="A78" s="20"/>
+      <c r="D78" s="31"/>
     </row>
     <row r="79" s="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A79" s="35">
+      <c r="A79" s="34">
         <v>60</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -2889,7 +2868,7 @@
       </c>
     </row>
     <row r="80" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A80" s="21">
+      <c r="A80" s="20">
         <v>61</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -2902,193 +2881,196 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" s="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A81" s="35">
+    <row r="81" s="9" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A81" s="36">
         <v>62</v>
       </c>
-      <c r="B81" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="8" t="s">
+      <c r="B81" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="37" t="s">
         <v>133</v>
       </c>
+      <c r="E81" s="37" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="82" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A82" s="21">
+      <c r="A82" s="20">
         <v>63</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="D82" s="32" t="s">
         <v>135</v>
       </c>
+      <c r="D82" s="31" t="s">
+        <v>136</v>
+      </c>
       <c r="E82" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="83" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A83" s="21">
+      <c r="A83" s="20">
         <v>64</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D83" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D83" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" s="9" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A84" s="37">
+    <row r="84" s="10" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A84" s="38">
         <v>65</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D84" s="38" t="s">
+      <c r="B84" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="E84" s="9" t="s">
+      <c r="D84" s="39" t="s">
         <v>141</v>
       </c>
+      <c r="E84" s="10" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="85" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A85" s="37">
+      <c r="A85" s="38">
         <v>66</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="86" s="11" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A86" s="21">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="86" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A86" s="20">
         <v>67</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C86" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F86" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" s="11" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A87" s="21">
+      <c r="C86" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A87" s="20">
         <v>68</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D87" s="39" t="s">
+      <c r="C87" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="F87" s="11" t="s">
+      <c r="D87" s="31" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="88" s="11" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A88" s="21">
+      <c r="F87" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="88" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A88" s="20">
         <v>69</v>
       </c>
-      <c r="B88" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D88" s="40" t="s">
+      <c r="B88" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E88" s="11" t="s">
+      <c r="D88" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="F88" s="11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" s="11" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A89" s="21">
+      <c r="E88" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="89" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A89" s="20">
         <v>70</v>
       </c>
-      <c r="B89" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E89" s="11" t="s">
+      <c r="B89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F89" s="11" t="s">
+      <c r="E89" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="90" s="11" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A90" s="21">
+      <c r="F89" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="90" s="3" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A90" s="20">
         <v>71</v>
       </c>
-      <c r="B90" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="D90" s="39" t="s">
+      <c r="B90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F90" s="11" t="s">
+      <c r="D90" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="91" s="12" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A91" s="41">
+    <row r="91" s="11" customFormat="1" ht="16.5" spans="1:5">
+      <c r="A91" s="36">
         <v>72</v>
       </c>
-      <c r="B91" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D91" s="42" t="s">
+      <c r="B91" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="E91" s="12" t="s">
+      <c r="D91" s="40" t="s">
         <v>158</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B73 B74:B78 B79:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="166">
   <si>
     <t>编号</t>
   </si>
@@ -551,6 +551,24 @@
   </si>
   <si>
     <t>暂时无复现</t>
+  </si>
+  <si>
+    <t>宝石合成界面刷新问题，魂石界面放上魂石，不合成直接关界面，打开后，默认界面宝石页签出现了魂石</t>
+  </si>
+  <si>
+    <t>问题图片\73.jpg</t>
+  </si>
+  <si>
+    <t>技能升级和进阶界面没有技能图标</t>
+  </si>
+  <si>
+    <t>问题图片\74.jpg</t>
+  </si>
+  <si>
+    <t>强化和升星界面装备名称如果超出了页签，可以再多截掉一个字，这样不会出现字的超框。然后页签列表滑动到下一页的时候会出现选中之后回弹的情况</t>
+  </si>
+  <si>
+    <t>问题图片\75.jpg</t>
   </si>
 </sst>
 </file>
@@ -983,7 +1001,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1004,6 +1022,19 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1130,7 +1161,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1142,34 +1173,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1254,7 +1285,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1366,16 +1397,22 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1442,6 +1479,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1694,7 +1738,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.258333333333" customWidth="1"/>
@@ -2885,13 +2929,13 @@
       <c r="A81" s="36">
         <v>62</v>
       </c>
-      <c r="B81" s="37" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="37" t="s">
+      <c r="B81" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E81" s="37" t="s">
+      <c r="E81" s="9" t="s">
         <v>134</v>
       </c>
     </row>
@@ -2936,7 +2980,7 @@
       </c>
     </row>
     <row r="84" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A84" s="38">
+      <c r="A84" s="37">
         <v>65</v>
       </c>
       <c r="B84" s="10" t="s">
@@ -2945,7 +2989,7 @@
       <c r="C84" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="39" t="s">
+      <c r="D84" s="38" t="s">
         <v>141</v>
       </c>
       <c r="E84" s="10" t="s">
@@ -2953,7 +2997,7 @@
       </c>
     </row>
     <row r="85" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A85" s="38">
+      <c r="A85" s="37">
         <v>66</v>
       </c>
       <c r="B85" s="10" t="s">
@@ -3052,7 +3096,7 @@
       </c>
     </row>
     <row r="91" s="11" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A91" s="36">
+      <c r="A91" s="39">
         <v>72</v>
       </c>
       <c r="B91" s="11" t="s">
@@ -3068,9 +3112,54 @@
         <v>159</v>
       </c>
     </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="41">
+        <v>73</v>
+      </c>
+      <c r="B92" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="D92" s="42" t="s">
+        <v>161</v>
+      </c>
+      <c r="E92" s="41"/>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="41">
+        <v>74</v>
+      </c>
+      <c r="B93" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="41" t="s">
+        <v>162</v>
+      </c>
+      <c r="D93" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="E93" s="41"/>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="41">
+        <v>75</v>
+      </c>
+      <c r="B94" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="E94" s="41"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B91 B92:B94 B95:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3115,6 +3204,9 @@
     <hyperlink ref="D88" r:id="rId38" display="问题图片\70.jpg"/>
     <hyperlink ref="D90" r:id="rId39" display="问题图片\71.jpg"/>
     <hyperlink ref="D91" r:id="rId40" display="问题图片\72.jpg"/>
+    <hyperlink ref="D92" r:id="rId41" display="问题图片\73.jpg"/>
+    <hyperlink ref="D93" r:id="rId42" display="问题图片\74.jpg"/>
+    <hyperlink ref="D94" r:id="rId43" display="问题图片\75.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="166">
   <si>
     <t>编号</t>
   </si>
@@ -1409,10 +1409,10 @@
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3112,7 +3112,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" s="3" customFormat="1" spans="1:6">
       <c r="A92" s="41">
         <v>73</v>
       </c>
@@ -3126,8 +3126,11 @@
         <v>161</v>
       </c>
       <c r="E92" s="41"/>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" s="3" customFormat="1" spans="1:6">
       <c r="A93" s="41">
         <v>74</v>
       </c>
@@ -3137,12 +3140,15 @@
       <c r="C93" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="D93" s="42" t="s">
+      <c r="D93" s="22" t="s">
         <v>163</v>
       </c>
       <c r="E93" s="41"/>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" s="3" customFormat="1" spans="1:6">
       <c r="A94" s="41">
         <v>75</v>
       </c>
@@ -3152,14 +3158,17 @@
       <c r="C94" s="41" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="42" t="s">
+      <c r="D94" s="22" t="s">
         <v>165</v>
       </c>
       <c r="E94" s="41"/>
+      <c r="F94" s="3" t="s">
+        <v>63</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B91 B92:B94 B95:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="174">
   <si>
     <t>编号</t>
   </si>
@@ -569,6 +569,33 @@
   </si>
   <si>
     <t>问题图片\75.jpg</t>
+  </si>
+  <si>
+    <t>开箱按钮快速点击时会穿透点击到地面，导致自动战斗中断，需要调整为点击开箱按钮区域不会穿透</t>
+  </si>
+  <si>
+    <t>问题图片\76.png</t>
+  </si>
+  <si>
+    <t>商城中点击购买物品之后弹出的数量选择弹出框中，加减按钮点击之后没有效果，正常应该是可以进行数量的加一或者减一</t>
+  </si>
+  <si>
+    <t>问题图片\77.png</t>
+  </si>
+  <si>
+    <t>宝箱升级界面，点击加速按钮之后所弹出的加速卷轴不足的提示框调整为如图片所示状态：
+1、点击一键补足，判断元宝数量是否满足，是，则扣除元宝直接加速（按照所需加速券进行折算）；否，则提示元宝不足；
+2、点击商城购买，则跳转到商城对应的加速卷轴位置
+3、点击关闭按钮，则直接关闭弹出框</t>
+  </si>
+  <si>
+    <t>问题图片\78.jpg</t>
+  </si>
+  <si>
+    <t>免费VIP界面，去掉每个任务前面的：任务内容：，防止文字超框</t>
+  </si>
+  <si>
+    <t>问题图片\79-1.jpg</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1312,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1413,6 +1440,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1479,13 +1524,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1738,7 +1776,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.258333333333" customWidth="1"/>
@@ -3149,22 +3187,86 @@
       </c>
     </row>
     <row r="94" s="3" customFormat="1" spans="1:6">
-      <c r="A94" s="41">
+      <c r="A94" s="43">
         <v>75</v>
       </c>
-      <c r="B94" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="41" t="s">
+      <c r="B94" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="43" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="22" t="s">
+      <c r="D94" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="E94" s="41"/>
+      <c r="E94" s="43"/>
       <c r="F94" s="3" t="s">
         <v>63</v>
       </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" s="45">
+        <v>76</v>
+      </c>
+      <c r="B95" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="45">
+        <v>77</v>
+      </c>
+      <c r="B96" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="D96" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="E96" s="45"/>
+      <c r="F96" s="45"/>
+    </row>
+    <row r="97" ht="54" spans="1:6">
+      <c r="A97" s="45">
+        <v>78</v>
+      </c>
+      <c r="B97" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D97" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="E97" s="45"/>
+      <c r="F97" s="45"/>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" s="45">
+        <v>79</v>
+      </c>
+      <c r="B98" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="D98" s="48" t="s">
+        <v>173</v>
+      </c>
+      <c r="E98" s="47"/>
+      <c r="F98" s="47"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3216,6 +3318,10 @@
     <hyperlink ref="D92" r:id="rId41" display="问题图片\73.jpg"/>
     <hyperlink ref="D93" r:id="rId42" display="问题图片\74.jpg"/>
     <hyperlink ref="D94" r:id="rId43" display="问题图片\75.jpg"/>
+    <hyperlink ref="D95" r:id="rId44" display="问题图片\76.png"/>
+    <hyperlink ref="D96" r:id="rId45" display="问题图片\77.png"/>
+    <hyperlink ref="D97" r:id="rId46" display="问题图片\78.jpg"/>
+    <hyperlink ref="D98" r:id="rId47" display="问题图片\79-1.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="177">
   <si>
     <t>编号</t>
   </si>
@@ -596,6 +596,21 @@
   </si>
   <si>
     <t>问题图片\79-1.jpg</t>
+  </si>
+  <si>
+    <t>红点的界面层级不对，包括强化、升星等带有侧页签的界面</t>
+  </si>
+  <si>
+    <t>问题图片\80.png</t>
+  </si>
+  <si>
+    <t>添加游戏内的走马灯公告：
+1、当有玩家从开箱中获取了带有自然属性的装备时，给出走马灯公告：玩家XXXXX开箱获得了XXXXXX【风】！
+2、当有玩家运镖刷到了橙品镖车时，给出走马灯公告：玩家XXXXX幸运的接到了一辆XXX镖车！
+3、当有玩家触发了战力首领时，给出走马灯公告：玩家XXXX偶然发现了战力首领XXXX！
+4、当有玩家任一槽位升星到：10星、15星、20星、25星、30星时，给出走马灯公告：玩家XXXXX将XXXX槽位升至了XXX星，傲视群雄！
+5、当有玩家护卫升级到：3级、6级、9级、10级时，给出走马灯公告：玩家XXXX将XXX护卫提升至XX级，海量资源坐享其成！
+6、当有玩家合成魂石除了带有自然属性的魂石时，给出走马灯公告：玩家XXX幸运的合成出了XXXX【金】！</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1327,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1459,6 +1474,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1524,6 +1542,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1776,7 +1801,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.258333333333" customWidth="1"/>
@@ -3256,17 +3281,47 @@
       <c r="A98" s="45">
         <v>79</v>
       </c>
-      <c r="B98" s="47" t="s">
+      <c r="B98" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="47" t="s">
+      <c r="C98" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="D98" s="48" t="s">
+      <c r="D98" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="E98" s="47"/>
-      <c r="F98" s="47"/>
+      <c r="E98" s="45"/>
+      <c r="F98" s="45"/>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="45">
+        <v>80</v>
+      </c>
+      <c r="B99" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="D99" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="E99" s="47"/>
+      <c r="F99" s="47"/>
+    </row>
+    <row r="100" ht="94.5" spans="1:6">
+      <c r="A100" s="45">
+        <v>81</v>
+      </c>
+      <c r="B100" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="D100" s="47"/>
+      <c r="E100" s="47"/>
+      <c r="F100" s="47"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3322,6 +3377,7 @@
     <hyperlink ref="D96" r:id="rId45" display="问题图片\77.png"/>
     <hyperlink ref="D97" r:id="rId46" display="问题图片\78.jpg"/>
     <hyperlink ref="D98" r:id="rId47" display="问题图片\79-1.jpg"/>
+    <hyperlink ref="D99" r:id="rId48" display="问题图片\80.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="182">
   <si>
     <t>编号</t>
   </si>
@@ -577,10 +577,16 @@
     <t>问题图片\76.png</t>
   </si>
   <si>
+    <t>解决了</t>
+  </si>
+  <si>
     <t>商城中点击购买物品之后弹出的数量选择弹出框中，加减按钮点击之后没有效果，正常应该是可以进行数量的加一或者减一</t>
   </si>
   <si>
     <t>问题图片\77.png</t>
+  </si>
+  <si>
+    <t>商城配置待修改</t>
   </si>
   <si>
     <t>宝箱升级界面，点击加速按钮之后所弹出的加速卷轴不足的提示框调整为如图片所示状态：
@@ -592,6 +598,9 @@
     <t>问题图片\78.jpg</t>
   </si>
   <si>
+    <t>已修正，暂时加速卷轴对600元宝是固定脚本定义死的</t>
+  </si>
+  <si>
     <t>免费VIP界面，去掉每个任务前面的：任务内容：，防止文字超框</t>
   </si>
   <si>
@@ -602,6 +611,9 @@
   </si>
   <si>
     <t>问题图片\80.png</t>
+  </si>
+  <si>
+    <t>升星界面现在没有红点，之前版本就没要升星的红点，好像是因为随机概率；强化和技能升级已修正。。。其他还有界面你再提</t>
   </si>
   <si>
     <t>添加游戏内的走马灯公告：
@@ -611,6 +623,9 @@
 4、当有玩家任一槽位升星到：10星、15星、20星、25星、30星时，给出走马灯公告：玩家XXXXX将XXXX槽位升至了XXX星，傲视群雄！
 5、当有玩家护卫升级到：3级、6级、9级、10级时，给出走马灯公告：玩家XXXX将XXX护卫提升至XX级，海量资源坐享其成！
 6、当有玩家合成魂石除了带有自然属性的魂石时，给出走马灯公告：玩家XXX幸运的合成出了XXXX【金】！</t>
+  </si>
+  <si>
+    <t>合成的属性检测不太好加，其他都加了</t>
   </si>
 </sst>
 </file>
@@ -789,7 +804,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="43">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -853,6 +868,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1203,7 +1230,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1227,16 +1254,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1245,89 +1272,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1362,6 +1389,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1463,20 +1496,20 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="6" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1801,7 +1834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="121.258333333333" customWidth="1"/>
@@ -1812,19 +1845,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -1832,206 +1865,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="12">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="12"/>
+      <c r="E2" s="14"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="15">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="15"/>
+      <c r="E3" s="17"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="12">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="12"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="18">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="18"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="12">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="14"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="12">
+      <c r="A7" s="14">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B7" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="12">
+      <c r="A8" s="14">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="14"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="12">
+      <c r="A9" s="14">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="12">
-        <v>9</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="12" t="s">
+      <c r="A11" s="14">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="12">
+      <c r="A12" s="14">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="12"/>
+      <c r="E12" s="14"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="12">
+      <c r="A13" s="14">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="12"/>
+      <c r="E13" s="14"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -2040,19 +2073,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="12">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="B14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="12"/>
+      <c r="E14" s="14"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2061,19 +2094,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="12">
+      <c r="A15" s="14">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="12"/>
+      <c r="E15" s="14"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -2082,19 +2115,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="12">
+      <c r="A16" s="14">
         <v>15</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="14"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -2103,17 +2136,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="12">
+      <c r="A17" s="14">
         <v>16</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="12" t="s">
+      <c r="B17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -2122,644 +2155,644 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="12">
+      <c r="A18" s="14">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="12">
+      <c r="A19" s="14">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="12" t="s">
+      <c r="B19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="12"/>
+      <c r="E19" s="14"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="20">
+      <c r="A20" s="22">
         <v>19</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="12">
+      <c r="A21" s="14">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="12" t="s">
+      <c r="B21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="12">
+      <c r="A22" s="14">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="B22" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="12">
+      <c r="A23" s="14">
         <v>22</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="12">
+      <c r="A24" s="14">
         <v>23</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="12" t="s">
+      <c r="B24" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="12">
+      <c r="A25" s="14">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="20">
+      <c r="A26" s="22">
         <v>25</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="20">
+      <c r="A27" s="22">
         <v>26</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="12">
+      <c r="A28" s="14">
         <v>27</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="A29" s="14"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="12"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="A30" s="14"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
+      <c r="A32" s="14"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
+      <c r="A33" s="14"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="20">
+      <c r="A34" s="22">
         <v>28</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="20" t="s">
+      <c r="B34" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D34" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="22" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="20">
+      <c r="A35" s="22">
         <v>29</v>
       </c>
-      <c r="B35" s="20" t="s">
+      <c r="B35" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="22" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="23">
+      <c r="A36" s="25">
         <v>30</v>
       </c>
-      <c r="B36" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="23" t="s">
+      <c r="B36" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="24">
+      <c r="A37" s="26">
         <v>31</v>
       </c>
-      <c r="B37" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="24" t="s">
+      <c r="B37" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="25" t="s">
+      <c r="D37" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="24"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="24">
+      <c r="A38" s="26">
         <v>32</v>
       </c>
-      <c r="B38" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="24" t="s">
+      <c r="B38" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D38" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="24"/>
+      <c r="E38" s="26"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="20">
+      <c r="A39" s="22">
         <v>33</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="20"/>
-      <c r="F39" s="27" t="s">
+      <c r="E39" s="22"/>
+      <c r="F39" s="29" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="20">
+      <c r="A40" s="22">
         <v>34</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="20">
+      <c r="A41" s="22">
         <v>35</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="20" t="s">
+      <c r="B41" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="20">
+      <c r="A42" s="22">
         <v>36</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="22" t="s">
+      <c r="D42" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="20"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="20">
+      <c r="A43" s="22">
         <v>37</v>
       </c>
-      <c r="B43" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="20" t="s">
+      <c r="B43" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="22" t="s">
+      <c r="D43" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="20"/>
+      <c r="E43" s="22"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="12">
+      <c r="A44" s="14">
         <v>38</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="12" t="s">
+      <c r="B44" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="12"/>
+      <c r="E44" s="14"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="28">
+      <c r="A45" s="30">
         <v>39</v>
       </c>
-      <c r="B45" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="28" t="s">
+      <c r="B45" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="20">
+      <c r="A46" s="22">
         <v>40</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="20" t="s">
+      <c r="B46" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="D46" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="20"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="20">
+      <c r="A47" s="22">
         <v>41</v>
       </c>
-      <c r="B47" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="20" t="s">
+      <c r="B47" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="22" t="s">
+      <c r="D47" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="20"/>
+      <c r="E47" s="22"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="20"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="22"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="20"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="22"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="20"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="22"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="12">
+      <c r="A51" s="14">
         <v>42</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="12" t="s">
+      <c r="B51" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="12"/>
+      <c r="E51" s="14"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="20">
+      <c r="A52" s="22">
         <v>43</v>
       </c>
-      <c r="B52" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="20" t="s">
+      <c r="B52" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="22" t="s">
+      <c r="D52" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="20"/>
+      <c r="E52" s="22"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="20">
+      <c r="A53" s="22">
         <v>44</v>
       </c>
-      <c r="B53" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="20" t="s">
+      <c r="B53" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="20">
+      <c r="A54" s="22">
         <v>45</v>
       </c>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="20">
+      <c r="A55" s="22">
         <v>46</v>
       </c>
-      <c r="B55" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="20" t="s">
+      <c r="B55" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="20">
+      <c r="A56" s="22">
         <v>47</v>
       </c>
-      <c r="B56" s="20" t="s">
+      <c r="B56" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="20" t="s">
+      <c r="C56" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="20">
+      <c r="A57" s="22">
         <v>48</v>
       </c>
-      <c r="B57" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="20" t="s">
+      <c r="B57" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="20">
+      <c r="A58" s="22">
         <v>49</v>
       </c>
-      <c r="B58" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="20" t="s">
+      <c r="B58" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A59" s="20"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A60" s="20"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A61" s="20"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A62" s="20"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
+      <c r="A62" s="22"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A63" s="20"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A64" s="20">
+      <c r="A64" s="22">
         <v>50</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -2768,7 +2801,7 @@
       <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D64" s="30" t="s">
+      <c r="D64" s="32" t="s">
         <v>105</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -2779,7 +2812,7 @@
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A65" s="20">
+      <c r="A65" s="22">
         <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -2788,7 +2821,7 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="D65" s="33" t="s">
         <v>108</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -2799,7 +2832,7 @@
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A66" s="20">
+      <c r="A66" s="22">
         <v>52</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -2808,7 +2841,7 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="31" t="s">
+      <c r="D66" s="33" t="s">
         <v>111</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -2819,7 +2852,7 @@
       </c>
     </row>
     <row r="67" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A67" s="32">
+      <c r="A67" s="34">
         <v>53</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -2828,7 +2861,7 @@
       <c r="C67" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D67" s="33" t="s">
+      <c r="D67" s="35" t="s">
         <v>114</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -2836,7 +2869,7 @@
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A68" s="20">
+      <c r="A68" s="22">
         <v>54</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -2845,7 +2878,7 @@
       <c r="C68" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D68" s="30" t="s">
+      <c r="D68" s="32" t="s">
         <v>117</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -2856,7 +2889,7 @@
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A69" s="20">
+      <c r="A69" s="22">
         <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -2865,7 +2898,7 @@
       <c r="C69" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D69" s="30" t="s">
+      <c r="D69" s="32" t="s">
         <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -2876,7 +2909,7 @@
       </c>
     </row>
     <row r="70" s="8" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A70" s="34">
+      <c r="A70" s="36">
         <v>56</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -2885,7 +2918,7 @@
       <c r="C70" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="35" t="s">
+      <c r="D70" s="37" t="s">
         <v>123</v>
       </c>
       <c r="E70" s="8" t="s">
@@ -2893,7 +2926,7 @@
       </c>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A71" s="20">
+      <c r="A71" s="22">
         <v>57</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -2902,7 +2935,7 @@
       <c r="C71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D71" s="30" t="s">
+      <c r="D71" s="32" t="s">
         <v>126</v>
       </c>
       <c r="F71" s="3" t="s">
@@ -2910,7 +2943,7 @@
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A72" s="20">
+      <c r="A72" s="22">
         <v>58</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -2919,7 +2952,7 @@
       <c r="C72" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="30" t="s">
+      <c r="D72" s="32" t="s">
         <v>128</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -2927,7 +2960,7 @@
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A73" s="20">
+      <c r="A73" s="22">
         <v>59</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -2936,7 +2969,7 @@
       <c r="C73" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="D73" s="33" t="s">
         <v>130</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -2944,27 +2977,27 @@
       </c>
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A74" s="20"/>
-      <c r="D74" s="31"/>
+      <c r="A74" s="22"/>
+      <c r="D74" s="33"/>
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A75" s="20"/>
-      <c r="D75" s="31"/>
+      <c r="A75" s="22"/>
+      <c r="D75" s="33"/>
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A76" s="20"/>
-      <c r="D76" s="31"/>
+      <c r="A76" s="22"/>
+      <c r="D76" s="33"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A77" s="20"/>
-      <c r="D77" s="31"/>
+      <c r="A77" s="22"/>
+      <c r="D77" s="33"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A78" s="20"/>
-      <c r="D78" s="31"/>
+      <c r="A78" s="22"/>
+      <c r="D78" s="33"/>
     </row>
     <row r="79" s="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A79" s="34">
+      <c r="A79" s="36">
         <v>60</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -2975,7 +3008,7 @@
       </c>
     </row>
     <row r="80" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A80" s="20">
+      <c r="A80" s="22">
         <v>61</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -2989,7 +3022,7 @@
       </c>
     </row>
     <row r="81" s="9" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A81" s="36">
+      <c r="A81" s="38">
         <v>62</v>
       </c>
       <c r="B81" s="9" t="s">
@@ -3003,7 +3036,7 @@
       </c>
     </row>
     <row r="82" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A82" s="20">
+      <c r="A82" s="22">
         <v>63</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -3012,7 +3045,7 @@
       <c r="C82" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D82" s="31" t="s">
+      <c r="D82" s="33" t="s">
         <v>136</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3023,7 +3056,7 @@
       </c>
     </row>
     <row r="83" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A83" s="20">
+      <c r="A83" s="22">
         <v>64</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -3032,7 +3065,7 @@
       <c r="C83" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="30" t="s">
+      <c r="D83" s="32" t="s">
         <v>139</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3043,7 +3076,7 @@
       </c>
     </row>
     <row r="84" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A84" s="37">
+      <c r="A84" s="39">
         <v>65</v>
       </c>
       <c r="B84" s="10" t="s">
@@ -3052,7 +3085,7 @@
       <c r="C84" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="38" t="s">
+      <c r="D84" s="40" t="s">
         <v>141</v>
       </c>
       <c r="E84" s="10" t="s">
@@ -3060,7 +3093,7 @@
       </c>
     </row>
     <row r="85" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A85" s="37">
+      <c r="A85" s="39">
         <v>66</v>
       </c>
       <c r="B85" s="10" t="s">
@@ -3074,7 +3107,7 @@
       </c>
     </row>
     <row r="86" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A86" s="20">
+      <c r="A86" s="22">
         <v>67</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -3088,7 +3121,7 @@
       </c>
     </row>
     <row r="87" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A87" s="20">
+      <c r="A87" s="22">
         <v>68</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -3097,7 +3130,7 @@
       <c r="C87" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D87" s="31" t="s">
+      <c r="D87" s="33" t="s">
         <v>147</v>
       </c>
       <c r="F87" s="3" t="s">
@@ -3105,7 +3138,7 @@
       </c>
     </row>
     <row r="88" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A88" s="20">
+      <c r="A88" s="22">
         <v>69</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -3114,7 +3147,7 @@
       <c r="C88" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D88" s="30" t="s">
+      <c r="D88" s="32" t="s">
         <v>150</v>
       </c>
       <c r="E88" s="3" t="s">
@@ -3125,7 +3158,7 @@
       </c>
     </row>
     <row r="89" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A89" s="20">
+      <c r="A89" s="22">
         <v>70</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -3142,7 +3175,7 @@
       </c>
     </row>
     <row r="90" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A90" s="20">
+      <c r="A90" s="22">
         <v>71</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -3151,7 +3184,7 @@
       <c r="C90" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D90" s="31" t="s">
+      <c r="D90" s="33" t="s">
         <v>156</v>
       </c>
       <c r="F90" s="3" t="s">
@@ -3159,7 +3192,7 @@
       </c>
     </row>
     <row r="91" s="11" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A91" s="39">
+      <c r="A91" s="41">
         <v>72</v>
       </c>
       <c r="B91" s="11" t="s">
@@ -3168,7 +3201,7 @@
       <c r="C91" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D91" s="40" t="s">
+      <c r="D91" s="42" t="s">
         <v>158</v>
       </c>
       <c r="E91" s="11" t="s">
@@ -3176,152 +3209,206 @@
       </c>
     </row>
     <row r="92" s="3" customFormat="1" spans="1:6">
-      <c r="A92" s="41">
+      <c r="A92" s="43">
         <v>73</v>
       </c>
-      <c r="B92" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" s="41" t="s">
+      <c r="B92" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="43" t="s">
         <v>160</v>
       </c>
-      <c r="D92" s="42" t="s">
+      <c r="D92" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="E92" s="41"/>
+      <c r="E92" s="43"/>
       <c r="F92" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="93" s="3" customFormat="1" spans="1:6">
-      <c r="A93" s="41">
+      <c r="A93" s="43">
         <v>74</v>
       </c>
-      <c r="B93" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="41" t="s">
+      <c r="B93" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="D93" s="22" t="s">
+      <c r="D93" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="E93" s="41"/>
+      <c r="E93" s="43"/>
       <c r="F93" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="94" s="3" customFormat="1" spans="1:6">
-      <c r="A94" s="43">
+      <c r="A94" s="45">
         <v>75</v>
       </c>
-      <c r="B94" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="43" t="s">
+      <c r="B94" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="45" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="44" t="s">
+      <c r="D94" s="46" t="s">
         <v>165</v>
       </c>
-      <c r="E94" s="43"/>
+      <c r="E94" s="45"/>
       <c r="F94" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="A95" s="45">
+    <row r="95" s="3" customFormat="1" spans="1:5">
+      <c r="A95" s="45"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="45"/>
+      <c r="D95" s="46"/>
+      <c r="E95" s="45"/>
+    </row>
+    <row r="96" s="3" customFormat="1" spans="1:5">
+      <c r="A96" s="45"/>
+      <c r="B96" s="45"/>
+      <c r="C96" s="45"/>
+      <c r="D96" s="46"/>
+      <c r="E96" s="45"/>
+    </row>
+    <row r="97" s="3" customFormat="1" spans="1:5">
+      <c r="A97" s="45"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="45"/>
+      <c r="D97" s="46"/>
+      <c r="E97" s="45"/>
+    </row>
+    <row r="98" s="3" customFormat="1" spans="1:5">
+      <c r="A98" s="45"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="45"/>
+      <c r="D98" s="46"/>
+      <c r="E98" s="45"/>
+    </row>
+    <row r="99" s="3" customFormat="1" spans="1:5">
+      <c r="A99" s="45"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="45"/>
+      <c r="D99" s="46"/>
+      <c r="E99" s="45"/>
+    </row>
+    <row r="100" s="3" customFormat="1" spans="1:5">
+      <c r="A100" s="45"/>
+      <c r="B100" s="45"/>
+      <c r="C100" s="45"/>
+      <c r="D100" s="46"/>
+      <c r="E100" s="45"/>
+    </row>
+    <row r="101" s="3" customFormat="1" spans="1:6">
+      <c r="A101" s="43">
         <v>76</v>
       </c>
-      <c r="B95" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="45" t="s">
+      <c r="B101" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="43" t="s">
         <v>166</v>
       </c>
-      <c r="D95" s="17" t="s">
+      <c r="D101" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="E95" s="45"/>
-      <c r="F95" s="45"/>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96" s="45">
+      <c r="E101" s="43"/>
+      <c r="F101" s="43" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="102" s="12" customFormat="1" spans="1:6">
+      <c r="A102" s="47">
         <v>77</v>
       </c>
-      <c r="B96" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C96" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="D96" s="17" t="s">
+      <c r="B102" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="E96" s="45"/>
-      <c r="F96" s="45"/>
-    </row>
-    <row r="97" ht="54" spans="1:6">
-      <c r="A97" s="45">
+      <c r="D102" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="E102" s="47"/>
+      <c r="F102" s="47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="103" s="3" customFormat="1" ht="54" spans="1:6">
+      <c r="A103" s="43">
         <v>78</v>
       </c>
-      <c r="B97" s="45" t="s">
+      <c r="B103" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C97" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="D97" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="E97" s="45"/>
-      <c r="F97" s="45"/>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98" s="45">
+      <c r="C103" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="D103" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="E103" s="43"/>
+      <c r="F103" s="43" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="104" s="3" customFormat="1" spans="1:6">
+      <c r="A104" s="43">
         <v>79</v>
       </c>
-      <c r="B98" s="45" t="s">
+      <c r="B104" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C98" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="D98" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="E98" s="45"/>
-      <c r="F98" s="45"/>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99" s="45">
+      <c r="C104" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" s="43"/>
+      <c r="F104" s="43" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="105" s="13" customFormat="1" spans="1:6">
+      <c r="A105" s="50">
         <v>80</v>
       </c>
-      <c r="B99" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="47" t="s">
-        <v>174</v>
-      </c>
-      <c r="D99" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="E99" s="47"/>
-      <c r="F99" s="47"/>
-    </row>
-    <row r="100" ht="94.5" spans="1:6">
-      <c r="A100" s="45">
+      <c r="B105" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="D105" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E105" s="50"/>
+      <c r="F105" s="50" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="106" s="3" customFormat="1" ht="94.5" spans="1:6">
+      <c r="A106" s="43">
         <v>81</v>
       </c>
-      <c r="B100" s="47" t="s">
+      <c r="B106" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C100" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="47"/>
+      <c r="C106" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="D106" s="43"/>
+      <c r="E106" s="43"/>
+      <c r="F106" s="43" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3373,11 +3460,11 @@
     <hyperlink ref="D92" r:id="rId41" display="问题图片\73.jpg"/>
     <hyperlink ref="D93" r:id="rId42" display="问题图片\74.jpg"/>
     <hyperlink ref="D94" r:id="rId43" display="问题图片\75.jpg"/>
-    <hyperlink ref="D95" r:id="rId44" display="问题图片\76.png"/>
-    <hyperlink ref="D96" r:id="rId45" display="问题图片\77.png"/>
-    <hyperlink ref="D97" r:id="rId46" display="问题图片\78.jpg"/>
-    <hyperlink ref="D98" r:id="rId47" display="问题图片\79-1.jpg"/>
-    <hyperlink ref="D99" r:id="rId48" display="问题图片\80.png"/>
+    <hyperlink ref="D101" r:id="rId44" display="问题图片\76.png"/>
+    <hyperlink ref="D102" r:id="rId45" display="问题图片\77.png"/>
+    <hyperlink ref="D103" r:id="rId46" display="问题图片\78.jpg"/>
+    <hyperlink ref="D104" r:id="rId47" display="问题图片\79-1.jpg"/>
+    <hyperlink ref="D105" r:id="rId48" display="问题图片\80.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="187">
   <si>
     <t>编号</t>
   </si>
@@ -626,6 +626,21 @@
   </si>
   <si>
     <t>合成的属性检测不太好加，其他都加了</t>
+  </si>
+  <si>
+    <t>感叹号按钮中有提示：VIP奖励，但是点击跳转到免费vip界面之后并没有任何奖励可以领取</t>
+  </si>
+  <si>
+    <t>问题图片\82-1.jpg</t>
+  </si>
+  <si>
+    <t>问题图片\82-2.jpg</t>
+  </si>
+  <si>
+    <t>自动开箱会出现开出来高战力装备没有停留直接关闭的情况，复现方法：先开启自动开箱，此时打开宝箱升级界面，点击升级，补足提示框停留一会儿就会出现</t>
+  </si>
+  <si>
+    <t>问题图片\83.jpg</t>
   </si>
 </sst>
 </file>
@@ -1354,7 +1369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1509,6 +1524,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1575,13 +1596,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1834,10 +1848,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="121.258333333333" customWidth="1"/>
+    <col min="3" max="3" width="132" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="31.875" customWidth="1"/>
     <col min="6" max="6" width="104.258333333333" customWidth="1"/>
@@ -3408,6 +3422,37 @@
       <c r="E106" s="43"/>
       <c r="F106" s="43" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107">
+        <v>82</v>
+      </c>
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>182</v>
+      </c>
+      <c r="D107" s="52" t="s">
+        <v>183</v>
+      </c>
+      <c r="E107" s="53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108">
+        <v>83</v>
+      </c>
+      <c r="B108" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" t="s">
+        <v>185</v>
+      </c>
+      <c r="D108" s="52" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3465,6 +3510,9 @@
     <hyperlink ref="D103" r:id="rId46" display="问题图片\78.jpg"/>
     <hyperlink ref="D104" r:id="rId47" display="问题图片\79-1.jpg"/>
     <hyperlink ref="D105" r:id="rId48" display="问题图片\80.png"/>
+    <hyperlink ref="D107" r:id="rId49" display="问题图片\82-1.jpg"/>
+    <hyperlink ref="E107" r:id="rId50" display="问题图片\82-2.jpg"/>
+    <hyperlink ref="D108" r:id="rId51" display="问题图片\83.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="188">
   <si>
     <t>编号</t>
   </si>
@@ -635,6 +635,9 @@
   </si>
   <si>
     <t>问题图片\82-2.jpg</t>
+  </si>
+  <si>
+    <t>已修正，主要是0级的问题</t>
   </si>
   <si>
     <t>自动开箱会出现开出来高战力装备没有停留直接关闭的情况，复现方法：先开启自动开箱，此时打开宝箱升级界面，点击升级，补足提示框停留一会儿就会出现</t>
@@ -1369,7 +1372,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1525,6 +1528,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
@@ -1848,7 +1854,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3424,40 +3430,55 @@
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="A107">
+    <row r="107" s="3" customFormat="1" spans="3:3">
+      <c r="C107" s="52"/>
+    </row>
+    <row r="108" s="3" customFormat="1" spans="3:3">
+      <c r="C108" s="52"/>
+    </row>
+    <row r="109" s="3" customFormat="1" spans="3:3">
+      <c r="C109" s="52"/>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110">
         <v>82</v>
       </c>
-      <c r="B107" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" t="s">
+      <c r="B110" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" t="s">
         <v>182</v>
       </c>
-      <c r="D107" s="52" t="s">
+      <c r="D110" s="53" t="s">
         <v>183</v>
       </c>
-      <c r="E107" s="53" t="s">
+      <c r="E110" s="54" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108">
+      <c r="F110" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111">
         <v>83</v>
       </c>
-      <c r="B108" t="s">
-        <v>10</v>
-      </c>
-      <c r="C108" t="s">
-        <v>185</v>
-      </c>
-      <c r="D108" s="52" t="s">
+      <c r="B111" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" t="s">
         <v>186</v>
+      </c>
+      <c r="D111" s="54" t="s">
+        <v>187</v>
+      </c>
+      <c r="F111" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B107 B108 B109 B1:B106 B110:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3510,9 +3531,9 @@
     <hyperlink ref="D103" r:id="rId46" display="问题图片\78.jpg"/>
     <hyperlink ref="D104" r:id="rId47" display="问题图片\79-1.jpg"/>
     <hyperlink ref="D105" r:id="rId48" display="问题图片\80.png"/>
-    <hyperlink ref="D107" r:id="rId49" display="问题图片\82-1.jpg"/>
-    <hyperlink ref="E107" r:id="rId50" display="问题图片\82-2.jpg"/>
-    <hyperlink ref="D108" r:id="rId51" display="问题图片\83.jpg"/>
+    <hyperlink ref="D110" r:id="rId49" display="问题图片\82-1.jpg"/>
+    <hyperlink ref="E110" r:id="rId50" display="问题图片\82-2.jpg"/>
+    <hyperlink ref="D111" r:id="rId51" display="问题图片\83.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="18240" windowHeight="17535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="194">
   <si>
     <t>编号</t>
   </si>
@@ -644,6 +644,24 @@
   </si>
   <si>
     <t>问题图片\83.jpg</t>
+  </si>
+  <si>
+    <t>经验获取的提示文字区域调整到红框所示区域</t>
+  </si>
+  <si>
+    <t>问题图片\84.png</t>
+  </si>
+  <si>
+    <t>月光宝盒按钮移动到右上角小地图旁边，如图所示按钮位置</t>
+  </si>
+  <si>
+    <t>问题图片\85.png</t>
+  </si>
+  <si>
+    <t>常驻的属性显示区域，按照如图所示位置摆放</t>
+  </si>
+  <si>
+    <t>问题图片\86.png</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3476,9 +3494,51 @@
         <v>9</v>
       </c>
     </row>
+    <row r="112" spans="1:4">
+      <c r="A112">
+        <v>84</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>188</v>
+      </c>
+      <c r="D112" s="53" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113">
+        <v>85</v>
+      </c>
+      <c r="B113" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" t="s">
+        <v>190</v>
+      </c>
+      <c r="D113" s="53" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114">
+        <v>86</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>192</v>
+      </c>
+      <c r="D114" s="53" t="s">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B107 B108 B109 B1:B106 B110:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B111 B112:B114 B115:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3534,6 +3594,9 @@
     <hyperlink ref="D110" r:id="rId49" display="问题图片\82-1.jpg"/>
     <hyperlink ref="E110" r:id="rId50" display="问题图片\82-2.jpg"/>
     <hyperlink ref="D111" r:id="rId51" display="问题图片\83.jpg"/>
+    <hyperlink ref="D112" r:id="rId52" display="问题图片\84.png"/>
+    <hyperlink ref="D113" r:id="rId53" display="问题图片\85.png"/>
+    <hyperlink ref="D114" r:id="rId54" display="问题图片\86.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="196">
   <si>
     <t>编号</t>
   </si>
@@ -662,6 +662,12 @@
   </si>
   <si>
     <t>问题图片\86.png</t>
+  </si>
+  <si>
+    <t>如图所示主线任务，任务描述上会多一个称号“0”的显示，但是任务中没有配置“0”；其次点击改任务没有弹出称号升级的界面</t>
+  </si>
+  <si>
+    <t>问题图片\87.jpg</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1878,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3536,9 +3542,23 @@
         <v>193</v>
       </c>
     </row>
+    <row r="115" spans="1:4">
+      <c r="A115">
+        <v>87</v>
+      </c>
+      <c r="B115" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" t="s">
+        <v>194</v>
+      </c>
+      <c r="D115" s="53" t="s">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B111 B112:B114 B115:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3597,6 +3617,7 @@
     <hyperlink ref="D112" r:id="rId52" display="问题图片\84.png"/>
     <hyperlink ref="D113" r:id="rId53" display="问题图片\85.png"/>
     <hyperlink ref="D114" r:id="rId54" display="问题图片\86.png"/>
+    <hyperlink ref="D115" r:id="rId55" display="问题图片\87.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18240" windowHeight="17535"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="198">
   <si>
     <t>编号</t>
   </si>
@@ -652,6 +652,9 @@
     <t>问题图片\84.png</t>
   </si>
   <si>
+    <t>经验获取已经移动，   道具的获取和消耗没能控制</t>
+  </si>
+  <si>
     <t>月光宝盒按钮移动到右上角小地图旁边，如图所示按钮位置</t>
   </si>
   <si>
@@ -668,6 +671,9 @@
   </si>
   <si>
     <t>问题图片\87.jpg</t>
+  </si>
+  <si>
+    <t>任务描述的地方你带参数了。已修正</t>
   </si>
 </sst>
 </file>
@@ -1878,12 +1884,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="31.875" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="104.258333333333" customWidth="1"/>
     <col min="7" max="7" width="36.2583333333333" customWidth="1"/>
   </cols>
@@ -3500,65 +3506,86 @@
         <v>9</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112">
+    <row r="112" spans="4:4">
+      <c r="D112" s="54"/>
+    </row>
+    <row r="113" spans="4:4">
+      <c r="D113" s="54"/>
+    </row>
+    <row r="114" spans="4:4">
+      <c r="D114" s="54"/>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115">
         <v>84</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B115" t="s">
         <v>6</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C115" t="s">
         <v>188</v>
       </c>
-      <c r="D112" s="53" t="s">
+      <c r="D115" s="54" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113">
+      <c r="F115" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116">
         <v>85</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B116" t="s">
         <v>6</v>
       </c>
-      <c r="C113" t="s">
-        <v>190</v>
-      </c>
-      <c r="D113" s="53" t="s">
+      <c r="C116" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114">
+      <c r="D116" s="54" t="s">
+        <v>192</v>
+      </c>
+      <c r="F116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117">
         <v>86</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B117" t="s">
         <v>6</v>
       </c>
-      <c r="C114" t="s">
-        <v>192</v>
-      </c>
-      <c r="D114" s="53" t="s">
+      <c r="C117" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115">
+      <c r="D117" s="54" t="s">
+        <v>194</v>
+      </c>
+      <c r="F117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118">
         <v>87</v>
       </c>
-      <c r="B115" t="s">
-        <v>10</v>
-      </c>
-      <c r="C115" t="s">
-        <v>194</v>
-      </c>
-      <c r="D115" s="53" t="s">
+      <c r="B118" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" t="s">
         <v>195</v>
+      </c>
+      <c r="D118" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="F118" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B112 B113 B114 B1:B111 B115:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3614,10 +3641,10 @@
     <hyperlink ref="D110" r:id="rId49" display="问题图片\82-1.jpg"/>
     <hyperlink ref="E110" r:id="rId50" display="问题图片\82-2.jpg"/>
     <hyperlink ref="D111" r:id="rId51" display="问题图片\83.jpg"/>
-    <hyperlink ref="D112" r:id="rId52" display="问题图片\84.png"/>
-    <hyperlink ref="D113" r:id="rId53" display="问题图片\85.png"/>
-    <hyperlink ref="D114" r:id="rId54" display="问题图片\86.png"/>
-    <hyperlink ref="D115" r:id="rId55" display="问题图片\87.jpg"/>
+    <hyperlink ref="D115" r:id="rId52" display="问题图片\84.png"/>
+    <hyperlink ref="D116" r:id="rId53" display="问题图片\85.png"/>
+    <hyperlink ref="D117" r:id="rId54" display="问题图片\86.png"/>
+    <hyperlink ref="D118" r:id="rId55" display="问题图片\87.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="204">
   <si>
     <t>编号</t>
   </si>
@@ -674,6 +674,24 @@
   </si>
   <si>
     <t>任务描述的地方你带参数了。已修正</t>
+  </si>
+  <si>
+    <t>主线任务，击杀个人首领跳转错误，应该跳转到个人首领界面，不是战力首领界面</t>
+  </si>
+  <si>
+    <t>问题图片\88.jpg</t>
+  </si>
+  <si>
+    <t>绑元道具掉在地面上无法获取，也不会弹出快捷使用弹框</t>
+  </si>
+  <si>
+    <t>问题图片\89.jpg</t>
+  </si>
+  <si>
+    <t>属性面板的“展开”、“隐藏”按钮放在属性面板的同一层级，把怪物头像血条显示的区域露出来，如参考图所示；掉落物品的飘字位置放在屏幕的右下方，如参考图所示</t>
+  </si>
+  <si>
+    <t>问题图片\90.png</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1902,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3583,9 +3601,51 @@
         <v>197</v>
       </c>
     </row>
+    <row r="119" spans="1:4">
+      <c r="A119">
+        <v>88</v>
+      </c>
+      <c r="B119" t="s">
+        <v>10</v>
+      </c>
+      <c r="C119" t="s">
+        <v>198</v>
+      </c>
+      <c r="D119" s="54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120">
+        <v>89</v>
+      </c>
+      <c r="B120" t="s">
+        <v>10</v>
+      </c>
+      <c r="C120" t="s">
+        <v>200</v>
+      </c>
+      <c r="D120" s="54" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121">
+        <v>90</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>202</v>
+      </c>
+      <c r="D121" s="54" t="s">
+        <v>203</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B112 B113 B114 B1:B111 B115:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3645,6 +3705,9 @@
     <hyperlink ref="D116" r:id="rId53" display="问题图片\85.png"/>
     <hyperlink ref="D117" r:id="rId54" display="问题图片\86.png"/>
     <hyperlink ref="D118" r:id="rId55" display="问题图片\87.jpg"/>
+    <hyperlink ref="D119" r:id="rId56" display="问题图片\88.jpg"/>
+    <hyperlink ref="D120" r:id="rId57" display="问题图片\89.jpg"/>
+    <hyperlink ref="D121" r:id="rId58" display="问题图片\90.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="206">
   <si>
     <t>编号</t>
   </si>
@@ -688,10 +688,16 @@
     <t>问题图片\89.jpg</t>
   </si>
   <si>
+    <t>道具表没有配置内挂，所以无法拾取</t>
+  </si>
+  <si>
     <t>属性面板的“展开”、“隐藏”按钮放在属性面板的同一层级，把怪物头像血条显示的区域露出来，如参考图所示；掉落物品的飘字位置放在屏幕的右下方，如参考图所示</t>
   </si>
   <si>
     <t>问题图片\90.png</t>
+  </si>
+  <si>
+    <t>属性位置改了，道具飘字还没找到可以方法修改</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1908,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3601,51 +3607,66 @@
         <v>197</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
-      <c r="A119">
+    <row r="119" spans="4:4">
+      <c r="D119" s="54"/>
+    </row>
+    <row r="120" spans="4:4">
+      <c r="D120" s="54"/>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121">
         <v>88</v>
       </c>
-      <c r="B119" t="s">
-        <v>10</v>
-      </c>
-      <c r="C119" t="s">
+      <c r="B121" t="s">
+        <v>10</v>
+      </c>
+      <c r="C121" t="s">
         <v>198</v>
       </c>
-      <c r="D119" s="54" t="s">
+      <c r="D121" s="54" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120">
+      <c r="F121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122">
         <v>89</v>
       </c>
-      <c r="B120" t="s">
-        <v>10</v>
-      </c>
-      <c r="C120" t="s">
+      <c r="B122" t="s">
+        <v>10</v>
+      </c>
+      <c r="C122" t="s">
         <v>200</v>
       </c>
-      <c r="D120" s="54" t="s">
+      <c r="D122" s="54" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121">
+      <c r="F122" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123">
         <v>90</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B123" t="s">
         <v>6</v>
       </c>
-      <c r="C121" t="s">
-        <v>202</v>
-      </c>
-      <c r="D121" s="54" t="s">
+      <c r="C123" t="s">
         <v>203</v>
+      </c>
+      <c r="D123" s="54" t="s">
+        <v>204</v>
+      </c>
+      <c r="F123" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B119 B120 B1:B118 B121:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3705,9 +3726,9 @@
     <hyperlink ref="D116" r:id="rId53" display="问题图片\85.png"/>
     <hyperlink ref="D117" r:id="rId54" display="问题图片\86.png"/>
     <hyperlink ref="D118" r:id="rId55" display="问题图片\87.jpg"/>
-    <hyperlink ref="D119" r:id="rId56" display="问题图片\88.jpg"/>
-    <hyperlink ref="D120" r:id="rId57" display="问题图片\89.jpg"/>
-    <hyperlink ref="D121" r:id="rId58" display="问题图片\90.png"/>
+    <hyperlink ref="D121" r:id="rId56" display="问题图片\88.jpg"/>
+    <hyperlink ref="D122" r:id="rId57" display="问题图片\89.jpg"/>
+    <hyperlink ref="D123" r:id="rId58" display="问题图片\90.png"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="231">
   <si>
     <t>编号</t>
   </si>
@@ -698,6 +698,84 @@
   </si>
   <si>
     <t>属性位置改了，道具飘字还没找到可以方法修改</t>
+  </si>
+  <si>
+    <t>新增加的属性展示框中，风雨雷电属性里面目前都显示的是固定值，但应该除了攻速其他的都是百分比的显示</t>
+  </si>
+  <si>
+    <t>问题图片\91.jpg</t>
+  </si>
+  <si>
+    <t>开箱设置里面保留天赋属性装备和极品属性装备的勾选项没有生效，带有天赋属性的装备还是会被分解掉</t>
+  </si>
+  <si>
+    <t>问题图片\92.jpg</t>
+  </si>
+  <si>
+    <t>开箱的序列帧动画需要添加一下，现在开箱的间隔有点长，会以为是卡顿</t>
+  </si>
+  <si>
+    <t>问题图片\93.jpg</t>
+  </si>
+  <si>
+    <t>每日必做里面的开箱换装点击前往没有打开新增的月光宝盒界面</t>
+  </si>
+  <si>
+    <t>问题图片\94.jpg</t>
+  </si>
+  <si>
+    <t>月光宝盒按钮下方没有月光宝盒的文字</t>
+  </si>
+  <si>
+    <t>问题图片\95.jpg</t>
+  </si>
+  <si>
+    <t>战力首领的结算弹框会被带出副本，操作是在战力首领副本中提前打开了包裹界面</t>
+  </si>
+  <si>
+    <t>问题图片\96.jpg</t>
+  </si>
+  <si>
+    <t>强化，魂石，官职，护卫功能按钮上没有小红点，但是界面内有小红点</t>
+  </si>
+  <si>
+    <t>问题图片\97.jpg</t>
+  </si>
+  <si>
+    <t>同样是可叠加可使用的道具，筛子道具可以在包裹中一次性使用掉格子中的所有数量，但是红包和强化原石就不行，另外筛子多个叠加也能弹出快捷使用，红包和强化原石也不行</t>
+  </si>
+  <si>
+    <t>强化按钮的状态是不是反了?不点击是红色，点击会变灰吧？</t>
+  </si>
+  <si>
+    <t>问题图片\99.jpg</t>
+  </si>
+  <si>
+    <t>掉落装备拾取后的快捷穿戴弹出框上的装备名字颜色没有匹配其品质颜色</t>
+  </si>
+  <si>
+    <t>问题图片\100.jpg</t>
+  </si>
+  <si>
+    <t>免费VIP功能有可领取奖励时界面内按钮和功能按钮上均未出现小红点</t>
+  </si>
+  <si>
+    <t>问题图片\101.jpg</t>
+  </si>
+  <si>
+    <t>魂石五行属性的属性描述要分两行，现在一行显示不完全</t>
+  </si>
+  <si>
+    <t>问题图片\102.jpg</t>
+  </si>
+  <si>
+    <t>白嫖礼包规则说明缺失，规则说明内容为：
+1、白嫖礼包分为多种类别的礼包，每一类礼包分为多个档次。
+2、每一类礼包只能选择一个档次进行种草，种草期结束后即可免费领取礼包。
+3、每一类礼包均可以通过元宝直接购买，且随着购买次数的增加，礼包折扣力度也会增加。</t>
+  </si>
+  <si>
+    <t>问题图片\103.jpg</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1504,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1591,6 +1669,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1908,7 +1992,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3664,9 +3748,188 @@
         <v>205</v>
       </c>
     </row>
+    <row r="124" spans="1:4">
+      <c r="A124">
+        <v>91</v>
+      </c>
+      <c r="B124" t="s">
+        <v>10</v>
+      </c>
+      <c r="C124" t="s">
+        <v>206</v>
+      </c>
+      <c r="D124" s="53" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125">
+        <v>92</v>
+      </c>
+      <c r="B125" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125" t="s">
+        <v>208</v>
+      </c>
+      <c r="D125" s="53" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126">
+        <v>93</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>210</v>
+      </c>
+      <c r="D126" s="53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127">
+        <v>94</v>
+      </c>
+      <c r="B127" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" t="s">
+        <v>212</v>
+      </c>
+      <c r="D127" s="53" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128">
+        <v>95</v>
+      </c>
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="D128" s="53" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129">
+        <v>96</v>
+      </c>
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" t="s">
+        <v>216</v>
+      </c>
+      <c r="D129" s="53" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130">
+        <v>97</v>
+      </c>
+      <c r="B130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" t="s">
+        <v>218</v>
+      </c>
+      <c r="D130" s="53" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
+        <v>98</v>
+      </c>
+      <c r="B131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132">
+        <v>99</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>221</v>
+      </c>
+      <c r="D132" s="53" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133">
+        <v>100</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" t="s">
+        <v>223</v>
+      </c>
+      <c r="D133" s="53" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134">
+        <v>101</v>
+      </c>
+      <c r="B134" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" t="s">
+        <v>225</v>
+      </c>
+      <c r="D134" s="53" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135">
+        <v>102</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>227</v>
+      </c>
+      <c r="D135" s="53" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="136" ht="54" spans="1:4">
+      <c r="A136">
+        <v>103</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="56" t="s">
+        <v>229</v>
+      </c>
+      <c r="D136" s="53" t="s">
+        <v>230</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B119 B120 B1:B118 B121:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B136 B137:B1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3729,6 +3992,18 @@
     <hyperlink ref="D121" r:id="rId56" display="问题图片\88.jpg"/>
     <hyperlink ref="D122" r:id="rId57" display="问题图片\89.jpg"/>
     <hyperlink ref="D123" r:id="rId58" display="问题图片\90.png"/>
+    <hyperlink ref="D124" r:id="rId59" display="问题图片\91.jpg"/>
+    <hyperlink ref="D125" r:id="rId60" display="问题图片\92.jpg"/>
+    <hyperlink ref="D126" r:id="rId61" display="问题图片\93.jpg"/>
+    <hyperlink ref="D127" r:id="rId62" display="问题图片\94.jpg"/>
+    <hyperlink ref="D128" r:id="rId63" display="问题图片\95.jpg"/>
+    <hyperlink ref="D129" r:id="rId64" display="问题图片\96.jpg"/>
+    <hyperlink ref="D130" r:id="rId65" display="问题图片\97.jpg"/>
+    <hyperlink ref="D132" r:id="rId66" display="问题图片\99.jpg"/>
+    <hyperlink ref="D133" r:id="rId67" display="问题图片\100.jpg"/>
+    <hyperlink ref="D134" r:id="rId68" display="问题图片\101.jpg"/>
+    <hyperlink ref="D135" r:id="rId69" display="问题图片\102.jpg"/>
+    <hyperlink ref="D136" r:id="rId70" display="问题图片\103.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="237">
   <si>
     <t>编号</t>
   </si>
@@ -712,12 +712,21 @@
     <t>问题图片\92.jpg</t>
   </si>
   <si>
+    <t>都是会停下来的</t>
+  </si>
+  <si>
     <t>开箱的序列帧动画需要添加一下，现在开箱的间隔有点长，会以为是卡顿</t>
   </si>
   <si>
     <t>问题图片\93.jpg</t>
   </si>
   <si>
+    <t>单开有动画，自动无动画</t>
+  </si>
+  <si>
+    <t>已修正 ，降低间隔</t>
+  </si>
+  <si>
     <t>每日必做里面的开箱换装点击前往没有打开新增的月光宝盒界面</t>
   </si>
   <si>
@@ -742,6 +751,9 @@
     <t>问题图片\97.jpg</t>
   </si>
   <si>
+    <t>界面的主icon小红点有的，就是有延时</t>
+  </si>
+  <si>
     <t>同样是可叠加可使用的道具，筛子道具可以在包裹中一次性使用掉格子中的所有数量，但是红包和强化原石就不行，另外筛子多个叠加也能弹出快捷使用，红包和强化原石也不行</t>
   </si>
   <si>
@@ -751,10 +763,16 @@
     <t>问题图片\99.jpg</t>
   </si>
   <si>
+    <t>已调换资源修正</t>
+  </si>
+  <si>
     <t>掉落装备拾取后的快捷穿戴弹出框上的装备名字颜色没有匹配其品质颜色</t>
   </si>
   <si>
     <t>问题图片\100.jpg</t>
+  </si>
+  <si>
+    <t>客户端不支持功能。。。后面有时间再改客户端代码</t>
   </si>
   <si>
     <t>免费VIP功能有可领取奖励时界面内按钮和功能按钮上均未出现小红点</t>
@@ -1504,7 +1522,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1669,9 +1687,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1992,7 +2007,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -3748,188 +3763,239 @@
         <v>205</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
-      <c r="A124">
+    <row r="124" spans="4:4">
+      <c r="D124" s="54"/>
+    </row>
+    <row r="125" spans="4:4">
+      <c r="D125" s="54"/>
+    </row>
+    <row r="126" spans="4:4">
+      <c r="D126" s="54"/>
+    </row>
+    <row r="127" spans="4:4">
+      <c r="D127" s="54"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128">
         <v>91</v>
       </c>
-      <c r="B124" t="s">
-        <v>10</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" t="s">
         <v>206</v>
       </c>
-      <c r="D124" s="53" t="s">
+      <c r="D128" s="54" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125">
+      <c r="F128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129">
         <v>92</v>
       </c>
-      <c r="B125" t="s">
-        <v>10</v>
-      </c>
-      <c r="C125" t="s">
+      <c r="B129" t="s">
+        <v>10</v>
+      </c>
+      <c r="C129" t="s">
         <v>208</v>
       </c>
-      <c r="D125" s="53" t="s">
+      <c r="D129" s="54" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126">
+      <c r="E129" t="s">
+        <v>210</v>
+      </c>
+      <c r="F129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130">
         <v>93</v>
-      </c>
-      <c r="B126" t="s">
-        <v>6</v>
-      </c>
-      <c r="C126" t="s">
-        <v>210</v>
-      </c>
-      <c r="D126" s="53" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127">
-        <v>94</v>
-      </c>
-      <c r="B127" t="s">
-        <v>10</v>
-      </c>
-      <c r="C127" t="s">
-        <v>212</v>
-      </c>
-      <c r="D127" s="53" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128">
-        <v>95</v>
-      </c>
-      <c r="B128" t="s">
-        <v>10</v>
-      </c>
-      <c r="C128" s="55" t="s">
-        <v>214</v>
-      </c>
-      <c r="D128" s="53" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129">
-        <v>96</v>
-      </c>
-      <c r="B129" t="s">
-        <v>10</v>
-      </c>
-      <c r="C129" t="s">
-        <v>216</v>
-      </c>
-      <c r="D129" s="53" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130">
-        <v>97</v>
       </c>
       <c r="B130" t="s">
         <v>6</v>
       </c>
       <c r="C130" t="s">
+        <v>211</v>
+      </c>
+      <c r="D130" s="54" t="s">
+        <v>212</v>
+      </c>
+      <c r="E130" t="s">
+        <v>213</v>
+      </c>
+      <c r="F130" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131">
+        <v>94</v>
+      </c>
+      <c r="B131" t="s">
+        <v>10</v>
+      </c>
+      <c r="C131" t="s">
+        <v>215</v>
+      </c>
+      <c r="D131" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="F131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132">
+        <v>95</v>
+      </c>
+      <c r="B132" t="s">
+        <v>10</v>
+      </c>
+      <c r="C132" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="D132" s="53" t="s">
         <v>218</v>
       </c>
-      <c r="D130" s="53" t="s">
+      <c r="F132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133">
+        <v>96</v>
+      </c>
+      <c r="B133" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="131" spans="1:3">
-      <c r="A131">
+      <c r="D133" s="54" t="s">
+        <v>220</v>
+      </c>
+      <c r="F133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134">
+        <v>97</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>221</v>
+      </c>
+      <c r="D134" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="F134" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="135" s="3" customFormat="1" spans="1:3">
+      <c r="A135" s="3">
         <v>98</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B135" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C131" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132">
+      <c r="C135" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136">
         <v>99</v>
-      </c>
-      <c r="B132" t="s">
-        <v>6</v>
-      </c>
-      <c r="C132" t="s">
-        <v>221</v>
-      </c>
-      <c r="D132" s="53" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133">
-        <v>100</v>
-      </c>
-      <c r="B133" t="s">
-        <v>10</v>
-      </c>
-      <c r="C133" t="s">
-        <v>223</v>
-      </c>
-      <c r="D133" s="53" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134">
-        <v>101</v>
-      </c>
-      <c r="B134" t="s">
-        <v>10</v>
-      </c>
-      <c r="C134" t="s">
-        <v>225</v>
-      </c>
-      <c r="D134" s="53" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135">
-        <v>102</v>
-      </c>
-      <c r="B135" t="s">
-        <v>6</v>
-      </c>
-      <c r="C135" t="s">
-        <v>227</v>
-      </c>
-      <c r="D135" s="53" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="136" ht="54" spans="1:4">
-      <c r="A136">
-        <v>103</v>
       </c>
       <c r="B136" t="s">
         <v>6</v>
       </c>
-      <c r="C136" s="56" t="s">
+      <c r="C136" t="s">
+        <v>225</v>
+      </c>
+      <c r="D136" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="F136" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="137" s="3" customFormat="1" spans="1:6">
+      <c r="A137" s="3">
+        <v>100</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D137" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="D136" s="53" t="s">
+      <c r="F137" s="3" t="s">
         <v>230</v>
+      </c>
+    </row>
+    <row r="138" s="3" customFormat="1" spans="1:4">
+      <c r="A138" s="3">
+        <v>101</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D138" s="33" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139">
+        <v>102</v>
+      </c>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>233</v>
+      </c>
+      <c r="D139" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="F139" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="140" ht="54" spans="1:6">
+      <c r="A140">
+        <v>103</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="D140" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="F140" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B136 B137:B1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"BUG,优化"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3992,18 +4058,18 @@
     <hyperlink ref="D121" r:id="rId56" display="问题图片\88.jpg"/>
     <hyperlink ref="D122" r:id="rId57" display="问题图片\89.jpg"/>
     <hyperlink ref="D123" r:id="rId58" display="问题图片\90.png"/>
-    <hyperlink ref="D124" r:id="rId59" display="问题图片\91.jpg"/>
-    <hyperlink ref="D125" r:id="rId60" display="问题图片\92.jpg"/>
-    <hyperlink ref="D126" r:id="rId61" display="问题图片\93.jpg"/>
-    <hyperlink ref="D127" r:id="rId62" display="问题图片\94.jpg"/>
-    <hyperlink ref="D128" r:id="rId63" display="问题图片\95.jpg"/>
-    <hyperlink ref="D129" r:id="rId64" display="问题图片\96.jpg"/>
-    <hyperlink ref="D130" r:id="rId65" display="问题图片\97.jpg"/>
-    <hyperlink ref="D132" r:id="rId66" display="问题图片\99.jpg"/>
-    <hyperlink ref="D133" r:id="rId67" display="问题图片\100.jpg"/>
-    <hyperlink ref="D134" r:id="rId68" display="问题图片\101.jpg"/>
-    <hyperlink ref="D135" r:id="rId69" display="问题图片\102.jpg"/>
-    <hyperlink ref="D136" r:id="rId70" display="问题图片\103.jpg"/>
+    <hyperlink ref="D128" r:id="rId59" display="问题图片\91.jpg"/>
+    <hyperlink ref="D129" r:id="rId60" display="问题图片\92.jpg"/>
+    <hyperlink ref="D130" r:id="rId61" display="问题图片\93.jpg"/>
+    <hyperlink ref="D131" r:id="rId62" display="问题图片\94.jpg"/>
+    <hyperlink ref="D132" r:id="rId63" display="问题图片\95.jpg"/>
+    <hyperlink ref="D133" r:id="rId64" display="问题图片\96.jpg"/>
+    <hyperlink ref="D134" r:id="rId65" display="问题图片\97.jpg"/>
+    <hyperlink ref="D136" r:id="rId66" display="问题图片\99.jpg"/>
+    <hyperlink ref="D137" r:id="rId67" display="问题图片\100.jpg"/>
+    <hyperlink ref="D138" r:id="rId68" display="问题图片\101.jpg"/>
+    <hyperlink ref="D139" r:id="rId69" display="问题图片\102.jpg"/>
+    <hyperlink ref="D140" r:id="rId70" display="问题图片\103.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="238">
   <si>
     <t>编号</t>
   </si>
@@ -751,10 +751,13 @@
     <t>问题图片\97.jpg</t>
   </si>
   <si>
-    <t>界面的主icon小红点有的，就是有延时</t>
+    <t>界面的主icon之前登录后有延时，现在登录就刷</t>
   </si>
   <si>
     <t>同样是可叠加可使用的道具，筛子道具可以在包裹中一次性使用掉格子中的所有数量，但是红包和强化原石就不行，另外筛子多个叠加也能弹出快捷使用，红包和强化原石也不行</t>
+  </si>
+  <si>
+    <t>背包里面没有该道具，则拾取后可弹框。。。有该道具，则产生叠加，无法弹框</t>
   </si>
   <si>
     <t>强化按钮的状态是不是反了?不点击是红色，点击会变灰吧？</t>
@@ -1522,7 +1525,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1563,6 +1566,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
@@ -1690,6 +1696,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2018,19 +2027,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:6">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
@@ -2038,206 +2047,206 @@
       </c>
     </row>
     <row r="2" ht="66" spans="1:6">
-      <c r="A2" s="14">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="14"/>
+      <c r="E2" s="15"/>
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A3" s="17">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="17" t="s">
+      <c r="B3" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="17"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A5" s="20">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <v>6</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="14" t="s">
+      <c r="B7" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <v>7</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="14" t="s">
+      <c r="B8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="14"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="9" ht="82.5" spans="1:6">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:6">
-      <c r="A10" s="14">
-        <v>9</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="15">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
       <c r="F10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:6">
-      <c r="A11" s="14">
-        <v>10</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:6">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>11</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="15"/>
       <c r="F12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:7">
-      <c r="A13" s="14">
+      <c r="A13" s="15">
         <v>12</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="2" t="s">
         <v>9</v>
       </c>
@@ -2246,19 +2255,19 @@
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:7">
-      <c r="A14" s="14">
+      <c r="A14" s="15">
         <v>13</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="14" t="s">
+      <c r="B14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="15"/>
       <c r="F14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2267,19 +2276,19 @@
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:7">
-      <c r="A15" s="14">
+      <c r="A15" s="15">
         <v>14</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="14" t="s">
+      <c r="B15" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="14"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="2" t="s">
         <v>9</v>
       </c>
@@ -2288,19 +2297,19 @@
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:7">
-      <c r="A16" s="14">
+      <c r="A16" s="15">
         <v>15</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="2" t="s">
         <v>9</v>
       </c>
@@ -2309,17 +2318,17 @@
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:7">
-      <c r="A17" s="14">
+      <c r="A17" s="15">
         <v>16</v>
       </c>
-      <c r="B17" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="B17" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
       <c r="F17" t="s">
         <v>41</v>
       </c>
@@ -2328,644 +2337,644 @@
       </c>
     </row>
     <row r="18" ht="66" spans="1:6">
-      <c r="A18" s="14">
+      <c r="A18" s="15">
         <v>17</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
       <c r="F18" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:6">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>18</v>
       </c>
-      <c r="B19" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="14" t="s">
+      <c r="B19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="14"/>
+      <c r="E19" s="15"/>
       <c r="F19" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A20" s="22">
+      <c r="A20" s="23">
         <v>19</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="22" t="s">
+      <c r="B20" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:6">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <v>20</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="14" t="s">
+      <c r="B21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
       <c r="F21" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:6">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>21</v>
       </c>
-      <c r="B22" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="14" t="s">
+      <c r="B22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
       <c r="F22" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:6">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <v>22</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:6">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <v>23</v>
       </c>
-      <c r="B24" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
       <c r="F24" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:6">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <v>24</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
       <c r="F25" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="26" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A26" s="22">
+      <c r="A26" s="23">
         <v>25</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
       <c r="F26" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A27" s="22">
+      <c r="A27" s="23">
         <v>26</v>
       </c>
-      <c r="B27" s="22" t="s">
+      <c r="B27" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="3" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:5">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <v>27</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
     </row>
     <row r="29" ht="16.5" spans="1:5">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
     </row>
     <row r="30" ht="16.5" spans="1:5">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
     </row>
     <row r="31" ht="16.5" spans="1:5">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
     </row>
     <row r="32" ht="16.5" spans="1:5">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
     </row>
     <row r="33" ht="16.5" spans="1:5">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A34" s="22">
+      <c r="A34" s="23">
         <v>28</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="22" t="s">
+      <c r="B34" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="23" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A35" s="22">
+      <c r="A35" s="23">
         <v>29</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="23" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="36" s="4" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A36" s="25">
+      <c r="A36" s="26">
         <v>30</v>
       </c>
-      <c r="B36" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="25" t="s">
+      <c r="B36" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="37" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A37" s="26">
+      <c r="A37" s="27">
         <v>31</v>
       </c>
-      <c r="B37" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="26" t="s">
+      <c r="B37" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="E37" s="26"/>
+      <c r="E37" s="27"/>
       <c r="F37" s="5" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="38" s="5" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A38" s="26">
+      <c r="A38" s="27">
         <v>32</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="26" t="s">
+      <c r="B38" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="E38" s="26"/>
+      <c r="E38" s="27"/>
       <c r="F38" s="5" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A39" s="22">
+      <c r="A39" s="23">
         <v>33</v>
       </c>
-      <c r="B39" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="22" t="s">
+      <c r="B39" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D39" s="24" t="s">
+      <c r="D39" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="E39" s="22"/>
-      <c r="F39" s="29" t="s">
+      <c r="E39" s="23"/>
+      <c r="F39" s="30" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" ht="99" spans="1:6">
-      <c r="A40" s="22">
+      <c r="A40" s="23">
         <v>34</v>
       </c>
-      <c r="B40" s="22" t="s">
+      <c r="B40" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C40" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
       <c r="F40" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A41" s="22">
+      <c r="A41" s="23">
         <v>35</v>
       </c>
-      <c r="B41" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="22" t="s">
+      <c r="B41" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A42" s="22">
+      <c r="A42" s="23">
         <v>36</v>
       </c>
-      <c r="B42" s="22" t="s">
+      <c r="B42" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="24" t="s">
+      <c r="D42" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="22"/>
+      <c r="E42" s="23"/>
       <c r="F42" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A43" s="22">
+      <c r="A43" s="23">
         <v>37</v>
       </c>
-      <c r="B43" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="22" t="s">
+      <c r="B43" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="24" t="s">
+      <c r="D43" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="22"/>
+      <c r="E43" s="23"/>
       <c r="F43" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:6">
-      <c r="A44" s="14">
+      <c r="A44" s="15">
         <v>38</v>
       </c>
-      <c r="B44" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="14" t="s">
+      <c r="B44" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="16" t="s">
+      <c r="D44" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="14"/>
+      <c r="E44" s="15"/>
       <c r="F44" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="45" s="6" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A45" s="30">
+      <c r="A45" s="31">
         <v>39</v>
       </c>
-      <c r="B45" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="30" t="s">
+      <c r="B45" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
       <c r="F45" s="6" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A46" s="22">
+      <c r="A46" s="23">
         <v>40</v>
       </c>
-      <c r="B46" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="22" t="s">
+      <c r="B46" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="24" t="s">
+      <c r="D46" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="22"/>
+      <c r="E46" s="23"/>
       <c r="F46" s="3" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A47" s="22">
+      <c r="A47" s="23">
         <v>41</v>
       </c>
-      <c r="B47" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="22" t="s">
+      <c r="B47" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="24" t="s">
+      <c r="D47" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E47" s="22"/>
+      <c r="E47" s="23"/>
       <c r="F47" s="3" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A48" s="22"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="22"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="22"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="23"/>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A49" s="22"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="22"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="23"/>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A50" s="22"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="22"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="22"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="23"/>
     </row>
     <row r="51" ht="16.5" spans="1:5">
-      <c r="A51" s="14">
+      <c r="A51" s="15">
         <v>42</v>
       </c>
-      <c r="B51" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C51" s="14" t="s">
+      <c r="B51" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E51" s="14"/>
+      <c r="E51" s="15"/>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A52" s="22">
+      <c r="A52" s="23">
         <v>43</v>
       </c>
-      <c r="B52" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="22" t="s">
+      <c r="B52" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="E52" s="22"/>
+      <c r="E52" s="23"/>
       <c r="F52" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A53" s="22">
+      <c r="A53" s="23">
         <v>44</v>
       </c>
-      <c r="B53" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C53" s="22" t="s">
+      <c r="B53" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="23"/>
       <c r="F53" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A54" s="22">
+      <c r="A54" s="23">
         <v>45</v>
       </c>
-      <c r="B54" s="22" t="s">
+      <c r="B54" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C54" s="22" t="s">
+      <c r="C54" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
       <c r="F54" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A55" s="22">
+      <c r="A55" s="23">
         <v>46</v>
       </c>
-      <c r="B55" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="22" t="s">
+      <c r="B55" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="23"/>
       <c r="F55" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A56" s="22">
+      <c r="A56" s="23">
         <v>47</v>
       </c>
-      <c r="B56" s="22" t="s">
+      <c r="B56" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C56" s="22" t="s">
+      <c r="C56" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
       <c r="F56" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A57" s="22">
+      <c r="A57" s="23">
         <v>48</v>
       </c>
-      <c r="B57" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="22" t="s">
+      <c r="B57" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="23"/>
       <c r="F57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A58" s="22">
+      <c r="A58" s="23">
         <v>49</v>
       </c>
-      <c r="B58" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="22" t="s">
+      <c r="B58" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
+      <c r="D58" s="23"/>
+      <c r="E58" s="23"/>
       <c r="F58" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A59" s="22"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A60" s="22"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A61" s="22"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A62" s="22"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A63" s="22"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A64" s="22">
+      <c r="A64" s="23">
         <v>50</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -2974,7 +2983,7 @@
       <c r="C64" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D64" s="32" t="s">
+      <c r="D64" s="33" t="s">
         <v>105</v>
       </c>
       <c r="E64" s="3" t="s">
@@ -2985,7 +2994,7 @@
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A65" s="22">
+      <c r="A65" s="23">
         <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -2994,7 +3003,7 @@
       <c r="C65" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="33" t="s">
+      <c r="D65" s="34" t="s">
         <v>108</v>
       </c>
       <c r="E65" s="3" t="s">
@@ -3005,7 +3014,7 @@
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A66" s="22">
+      <c r="A66" s="23">
         <v>52</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -3014,7 +3023,7 @@
       <c r="C66" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D66" s="33" t="s">
+      <c r="D66" s="34" t="s">
         <v>111</v>
       </c>
       <c r="E66" s="3" t="s">
@@ -3025,7 +3034,7 @@
       </c>
     </row>
     <row r="67" s="7" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A67" s="34">
+      <c r="A67" s="35">
         <v>53</v>
       </c>
       <c r="B67" s="7" t="s">
@@ -3034,7 +3043,7 @@
       <c r="C67" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="D67" s="35" t="s">
+      <c r="D67" s="36" t="s">
         <v>114</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -3042,7 +3051,7 @@
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A68" s="22">
+      <c r="A68" s="23">
         <v>54</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -3051,7 +3060,7 @@
       <c r="C68" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D68" s="32" t="s">
+      <c r="D68" s="33" t="s">
         <v>117</v>
       </c>
       <c r="E68" s="3" t="s">
@@ -3062,7 +3071,7 @@
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A69" s="22">
+      <c r="A69" s="23">
         <v>55</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -3071,7 +3080,7 @@
       <c r="C69" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D69" s="32" t="s">
+      <c r="D69" s="33" t="s">
         <v>120</v>
       </c>
       <c r="E69" s="3" t="s">
@@ -3082,7 +3091,7 @@
       </c>
     </row>
     <row r="70" s="8" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A70" s="36">
+      <c r="A70" s="37">
         <v>56</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -3091,7 +3100,7 @@
       <c r="C70" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D70" s="37" t="s">
+      <c r="D70" s="38" t="s">
         <v>123</v>
       </c>
       <c r="E70" s="8" t="s">
@@ -3099,7 +3108,7 @@
       </c>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A71" s="22">
+      <c r="A71" s="23">
         <v>57</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -3108,7 +3117,7 @@
       <c r="C71" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D71" s="32" t="s">
+      <c r="D71" s="33" t="s">
         <v>126</v>
       </c>
       <c r="F71" s="3" t="s">
@@ -3116,7 +3125,7 @@
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A72" s="22">
+      <c r="A72" s="23">
         <v>58</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -3125,7 +3134,7 @@
       <c r="C72" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="32" t="s">
+      <c r="D72" s="33" t="s">
         <v>128</v>
       </c>
       <c r="F72" s="3" t="s">
@@ -3133,7 +3142,7 @@
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A73" s="22">
+      <c r="A73" s="23">
         <v>59</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -3142,7 +3151,7 @@
       <c r="C73" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D73" s="33" t="s">
+      <c r="D73" s="34" t="s">
         <v>130</v>
       </c>
       <c r="F73" s="3" t="s">
@@ -3150,27 +3159,27 @@
       </c>
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A74" s="22"/>
-      <c r="D74" s="33"/>
+      <c r="A74" s="23"/>
+      <c r="D74" s="34"/>
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A75" s="22"/>
-      <c r="D75" s="33"/>
+      <c r="A75" s="23"/>
+      <c r="D75" s="34"/>
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A76" s="22"/>
-      <c r="D76" s="33"/>
+      <c r="A76" s="23"/>
+      <c r="D76" s="34"/>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A77" s="22"/>
-      <c r="D77" s="33"/>
+      <c r="A77" s="23"/>
+      <c r="D77" s="34"/>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:4">
-      <c r="A78" s="22"/>
-      <c r="D78" s="33"/>
+      <c r="A78" s="23"/>
+      <c r="D78" s="34"/>
     </row>
     <row r="79" s="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A79" s="36">
+      <c r="A79" s="37">
         <v>60</v>
       </c>
       <c r="B79" s="8" t="s">
@@ -3181,7 +3190,7 @@
       </c>
     </row>
     <row r="80" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A80" s="22">
+      <c r="A80" s="23">
         <v>61</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -3195,7 +3204,7 @@
       </c>
     </row>
     <row r="81" s="9" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A81" s="38">
+      <c r="A81" s="39">
         <v>62</v>
       </c>
       <c r="B81" s="9" t="s">
@@ -3209,7 +3218,7 @@
       </c>
     </row>
     <row r="82" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A82" s="22">
+      <c r="A82" s="23">
         <v>63</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -3218,7 +3227,7 @@
       <c r="C82" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D82" s="33" t="s">
+      <c r="D82" s="34" t="s">
         <v>136</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3229,7 +3238,7 @@
       </c>
     </row>
     <row r="83" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A83" s="22">
+      <c r="A83" s="23">
         <v>64</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -3238,7 +3247,7 @@
       <c r="C83" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D83" s="32" t="s">
+      <c r="D83" s="33" t="s">
         <v>139</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3249,7 +3258,7 @@
       </c>
     </row>
     <row r="84" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A84" s="39">
+      <c r="A84" s="40">
         <v>65</v>
       </c>
       <c r="B84" s="10" t="s">
@@ -3258,7 +3267,7 @@
       <c r="C84" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="D84" s="40" t="s">
+      <c r="D84" s="41" t="s">
         <v>141</v>
       </c>
       <c r="E84" s="10" t="s">
@@ -3266,7 +3275,7 @@
       </c>
     </row>
     <row r="85" s="10" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A85" s="39">
+      <c r="A85" s="40">
         <v>66</v>
       </c>
       <c r="B85" s="10" t="s">
@@ -3280,7 +3289,7 @@
       </c>
     </row>
     <row r="86" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A86" s="22">
+      <c r="A86" s="23">
         <v>67</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -3294,7 +3303,7 @@
       </c>
     </row>
     <row r="87" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A87" s="22">
+      <c r="A87" s="23">
         <v>68</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -3303,7 +3312,7 @@
       <c r="C87" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D87" s="33" t="s">
+      <c r="D87" s="34" t="s">
         <v>147</v>
       </c>
       <c r="F87" s="3" t="s">
@@ -3311,7 +3320,7 @@
       </c>
     </row>
     <row r="88" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A88" s="22">
+      <c r="A88" s="23">
         <v>69</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -3320,7 +3329,7 @@
       <c r="C88" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D88" s="32" t="s">
+      <c r="D88" s="33" t="s">
         <v>150</v>
       </c>
       <c r="E88" s="3" t="s">
@@ -3331,7 +3340,7 @@
       </c>
     </row>
     <row r="89" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A89" s="22">
+      <c r="A89" s="23">
         <v>70</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -3348,7 +3357,7 @@
       </c>
     </row>
     <row r="90" s="3" customFormat="1" ht="16.5" spans="1:6">
-      <c r="A90" s="22">
+      <c r="A90" s="23">
         <v>71</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -3357,7 +3366,7 @@
       <c r="C90" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D90" s="33" t="s">
+      <c r="D90" s="34" t="s">
         <v>156</v>
       </c>
       <c r="F90" s="3" t="s">
@@ -3365,7 +3374,7 @@
       </c>
     </row>
     <row r="91" s="11" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A91" s="41">
+      <c r="A91" s="42">
         <v>72</v>
       </c>
       <c r="B91" s="11" t="s">
@@ -3374,7 +3383,7 @@
       <c r="C91" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D91" s="42" t="s">
+      <c r="D91" s="43" t="s">
         <v>158</v>
       </c>
       <c r="E91" s="11" t="s">
@@ -3382,215 +3391,215 @@
       </c>
     </row>
     <row r="92" s="3" customFormat="1" spans="1:6">
-      <c r="A92" s="43">
+      <c r="A92" s="44">
         <v>73</v>
       </c>
-      <c r="B92" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" s="43" t="s">
+      <c r="B92" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="D92" s="44" t="s">
+      <c r="D92" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="E92" s="43"/>
+      <c r="E92" s="44"/>
       <c r="F92" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="93" s="3" customFormat="1" spans="1:6">
-      <c r="A93" s="43">
+      <c r="A93" s="44">
         <v>74</v>
       </c>
-      <c r="B93" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C93" s="43" t="s">
+      <c r="B93" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="D93" s="24" t="s">
+      <c r="D93" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="E93" s="43"/>
+      <c r="E93" s="44"/>
       <c r="F93" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="94" s="3" customFormat="1" spans="1:6">
-      <c r="A94" s="45">
+      <c r="A94" s="46">
         <v>75</v>
       </c>
-      <c r="B94" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="45" t="s">
+      <c r="B94" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="46" t="s">
         <v>164</v>
       </c>
-      <c r="D94" s="46" t="s">
+      <c r="D94" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="E94" s="45"/>
+      <c r="E94" s="46"/>
       <c r="F94" s="3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="95" s="3" customFormat="1" spans="1:5">
-      <c r="A95" s="45"/>
-      <c r="B95" s="45"/>
-      <c r="C95" s="45"/>
-      <c r="D95" s="46"/>
-      <c r="E95" s="45"/>
+      <c r="A95" s="46"/>
+      <c r="B95" s="46"/>
+      <c r="C95" s="46"/>
+      <c r="D95" s="47"/>
+      <c r="E95" s="46"/>
     </row>
     <row r="96" s="3" customFormat="1" spans="1:5">
-      <c r="A96" s="45"/>
-      <c r="B96" s="45"/>
-      <c r="C96" s="45"/>
-      <c r="D96" s="46"/>
-      <c r="E96" s="45"/>
+      <c r="A96" s="46"/>
+      <c r="B96" s="46"/>
+      <c r="C96" s="46"/>
+      <c r="D96" s="47"/>
+      <c r="E96" s="46"/>
     </row>
     <row r="97" s="3" customFormat="1" spans="1:5">
-      <c r="A97" s="45"/>
-      <c r="B97" s="45"/>
-      <c r="C97" s="45"/>
-      <c r="D97" s="46"/>
-      <c r="E97" s="45"/>
+      <c r="A97" s="46"/>
+      <c r="B97" s="46"/>
+      <c r="C97" s="46"/>
+      <c r="D97" s="47"/>
+      <c r="E97" s="46"/>
     </row>
     <row r="98" s="3" customFormat="1" spans="1:5">
-      <c r="A98" s="45"/>
-      <c r="B98" s="45"/>
-      <c r="C98" s="45"/>
-      <c r="D98" s="46"/>
-      <c r="E98" s="45"/>
+      <c r="A98" s="46"/>
+      <c r="B98" s="46"/>
+      <c r="C98" s="46"/>
+      <c r="D98" s="47"/>
+      <c r="E98" s="46"/>
     </row>
     <row r="99" s="3" customFormat="1" spans="1:5">
-      <c r="A99" s="45"/>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
-      <c r="D99" s="46"/>
-      <c r="E99" s="45"/>
+      <c r="A99" s="46"/>
+      <c r="B99" s="46"/>
+      <c r="C99" s="46"/>
+      <c r="D99" s="47"/>
+      <c r="E99" s="46"/>
     </row>
     <row r="100" s="3" customFormat="1" spans="1:5">
-      <c r="A100" s="45"/>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="46"/>
-      <c r="E100" s="45"/>
+      <c r="A100" s="46"/>
+      <c r="B100" s="46"/>
+      <c r="C100" s="46"/>
+      <c r="D100" s="47"/>
+      <c r="E100" s="46"/>
     </row>
     <row r="101" s="3" customFormat="1" spans="1:6">
-      <c r="A101" s="43">
+      <c r="A101" s="44">
         <v>76</v>
       </c>
-      <c r="B101" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="43" t="s">
+      <c r="B101" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="D101" s="44" t="s">
+      <c r="D101" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43" t="s">
+      <c r="E101" s="44"/>
+      <c r="F101" s="44" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="102" s="12" customFormat="1" spans="1:6">
-      <c r="A102" s="47">
+      <c r="A102" s="48">
         <v>77</v>
       </c>
-      <c r="B102" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C102" s="47" t="s">
+      <c r="B102" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="D102" s="48" t="s">
+      <c r="D102" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="E102" s="47"/>
-      <c r="F102" s="47" t="s">
+      <c r="E102" s="48"/>
+      <c r="F102" s="48" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="103" s="3" customFormat="1" ht="54" spans="1:6">
-      <c r="A103" s="43">
+      <c r="A103" s="44">
         <v>78</v>
       </c>
-      <c r="B103" s="43" t="s">
+      <c r="B103" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C103" s="49" t="s">
+      <c r="C103" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="D103" s="24" t="s">
+      <c r="D103" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="E103" s="43"/>
-      <c r="F103" s="43" t="s">
+      <c r="E103" s="44"/>
+      <c r="F103" s="44" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="104" s="3" customFormat="1" spans="1:6">
-      <c r="A104" s="43">
+      <c r="A104" s="44">
         <v>79</v>
       </c>
-      <c r="B104" s="43" t="s">
+      <c r="B104" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C104" s="43" t="s">
+      <c r="C104" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="25" t="s">
         <v>176</v>
       </c>
-      <c r="E104" s="43"/>
-      <c r="F104" s="43" t="s">
+      <c r="E104" s="44"/>
+      <c r="F104" s="44" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="105" s="13" customFormat="1" spans="1:6">
-      <c r="A105" s="50">
+      <c r="A105" s="51">
         <v>80</v>
       </c>
-      <c r="B105" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="50" t="s">
+      <c r="B105" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="D105" s="51" t="s">
+      <c r="D105" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="E105" s="50"/>
-      <c r="F105" s="50" t="s">
+      <c r="E105" s="51"/>
+      <c r="F105" s="51" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="106" s="3" customFormat="1" ht="94.5" spans="1:6">
-      <c r="A106" s="43">
+      <c r="A106" s="44">
         <v>81</v>
       </c>
-      <c r="B106" s="43" t="s">
+      <c r="B106" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="C106" s="49" t="s">
+      <c r="C106" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="D106" s="43"/>
-      <c r="E106" s="43"/>
-      <c r="F106" s="43" t="s">
+      <c r="D106" s="44"/>
+      <c r="E106" s="44"/>
+      <c r="F106" s="44" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="107" s="3" customFormat="1" spans="3:3">
-      <c r="C107" s="52"/>
+      <c r="C107" s="53"/>
     </row>
     <row r="108" s="3" customFormat="1" spans="3:3">
-      <c r="C108" s="52"/>
+      <c r="C108" s="53"/>
     </row>
     <row r="109" s="3" customFormat="1" spans="3:3">
-      <c r="C109" s="52"/>
+      <c r="C109" s="53"/>
     </row>
     <row r="110" spans="1:6">
       <c r="A110">
@@ -3602,10 +3611,10 @@
       <c r="C110" t="s">
         <v>182</v>
       </c>
-      <c r="D110" s="53" t="s">
+      <c r="D110" s="54" t="s">
         <v>183</v>
       </c>
-      <c r="E110" s="54" t="s">
+      <c r="E110" s="55" t="s">
         <v>184</v>
       </c>
       <c r="F110" t="s">
@@ -3622,7 +3631,7 @@
       <c r="C111" t="s">
         <v>186</v>
       </c>
-      <c r="D111" s="54" t="s">
+      <c r="D111" s="55" t="s">
         <v>187</v>
       </c>
       <c r="F111" t="s">
@@ -3630,13 +3639,13 @@
       </c>
     </row>
     <row r="112" spans="4:4">
-      <c r="D112" s="54"/>
+      <c r="D112" s="55"/>
     </row>
     <row r="113" spans="4:4">
-      <c r="D113" s="54"/>
+      <c r="D113" s="55"/>
     </row>
     <row r="114" spans="4:4">
-      <c r="D114" s="54"/>
+      <c r="D114" s="55"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115">
@@ -3648,7 +3657,7 @@
       <c r="C115" t="s">
         <v>188</v>
       </c>
-      <c r="D115" s="54" t="s">
+      <c r="D115" s="55" t="s">
         <v>189</v>
       </c>
       <c r="F115" t="s">
@@ -3665,7 +3674,7 @@
       <c r="C116" t="s">
         <v>191</v>
       </c>
-      <c r="D116" s="54" t="s">
+      <c r="D116" s="55" t="s">
         <v>192</v>
       </c>
       <c r="F116" t="s">
@@ -3682,7 +3691,7 @@
       <c r="C117" t="s">
         <v>193</v>
       </c>
-      <c r="D117" s="54" t="s">
+      <c r="D117" s="55" t="s">
         <v>194</v>
       </c>
       <c r="F117" t="s">
@@ -3699,7 +3708,7 @@
       <c r="C118" t="s">
         <v>195</v>
       </c>
-      <c r="D118" s="54" t="s">
+      <c r="D118" s="55" t="s">
         <v>196</v>
       </c>
       <c r="F118" t="s">
@@ -3707,10 +3716,10 @@
       </c>
     </row>
     <row r="119" spans="4:4">
-      <c r="D119" s="54"/>
+      <c r="D119" s="55"/>
     </row>
     <row r="120" spans="4:4">
-      <c r="D120" s="54"/>
+      <c r="D120" s="55"/>
     </row>
     <row r="121" spans="1:6">
       <c r="A121">
@@ -3722,7 +3731,7 @@
       <c r="C121" t="s">
         <v>198</v>
       </c>
-      <c r="D121" s="54" t="s">
+      <c r="D121" s="55" t="s">
         <v>199</v>
       </c>
       <c r="F121" t="s">
@@ -3739,7 +3748,7 @@
       <c r="C122" t="s">
         <v>200</v>
       </c>
-      <c r="D122" s="54" t="s">
+      <c r="D122" s="55" t="s">
         <v>201</v>
       </c>
       <c r="F122" t="s">
@@ -3756,7 +3765,7 @@
       <c r="C123" t="s">
         <v>203</v>
       </c>
-      <c r="D123" s="54" t="s">
+      <c r="D123" s="55" t="s">
         <v>204</v>
       </c>
       <c r="F123" t="s">
@@ -3764,16 +3773,16 @@
       </c>
     </row>
     <row r="124" spans="4:4">
-      <c r="D124" s="54"/>
+      <c r="D124" s="55"/>
     </row>
     <row r="125" spans="4:4">
-      <c r="D125" s="54"/>
+      <c r="D125" s="55"/>
     </row>
     <row r="126" spans="4:4">
-      <c r="D126" s="54"/>
+      <c r="D126" s="55"/>
     </row>
     <row r="127" spans="4:4">
-      <c r="D127" s="54"/>
+      <c r="D127" s="55"/>
     </row>
     <row r="128" spans="1:6">
       <c r="A128">
@@ -3785,7 +3794,7 @@
       <c r="C128" t="s">
         <v>206</v>
       </c>
-      <c r="D128" s="54" t="s">
+      <c r="D128" s="55" t="s">
         <v>207</v>
       </c>
       <c r="F128" t="s">
@@ -3802,7 +3811,7 @@
       <c r="C129" t="s">
         <v>208</v>
       </c>
-      <c r="D129" s="54" t="s">
+      <c r="D129" s="55" t="s">
         <v>209</v>
       </c>
       <c r="E129" t="s">
@@ -3822,7 +3831,7 @@
       <c r="C130" t="s">
         <v>211</v>
       </c>
-      <c r="D130" s="54" t="s">
+      <c r="D130" s="55" t="s">
         <v>212</v>
       </c>
       <c r="E130" t="s">
@@ -3842,7 +3851,7 @@
       <c r="C131" t="s">
         <v>215</v>
       </c>
-      <c r="D131" s="53" t="s">
+      <c r="D131" s="54" t="s">
         <v>216</v>
       </c>
       <c r="F131" t="s">
@@ -3856,10 +3865,10 @@
       <c r="B132" t="s">
         <v>10</v>
       </c>
-      <c r="C132" s="55" t="s">
+      <c r="C132" s="56" t="s">
         <v>217</v>
       </c>
-      <c r="D132" s="53" t="s">
+      <c r="D132" s="54" t="s">
         <v>218</v>
       </c>
       <c r="F132" t="s">
@@ -3876,7 +3885,7 @@
       <c r="C133" t="s">
         <v>219</v>
       </c>
-      <c r="D133" s="54" t="s">
+      <c r="D133" s="55" t="s">
         <v>220</v>
       </c>
       <c r="F133" t="s">
@@ -3893,14 +3902,14 @@
       <c r="C134" t="s">
         <v>221</v>
       </c>
-      <c r="D134" s="54" t="s">
+      <c r="D134" s="55" t="s">
         <v>222</v>
       </c>
       <c r="F134" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="135" s="3" customFormat="1" spans="1:3">
+    <row r="135" s="3" customFormat="1" spans="1:6">
       <c r="A135" s="3">
         <v>98</v>
       </c>
@@ -3909,6 +3918,9 @@
       </c>
       <c r="C135" s="3" t="s">
         <v>224</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -3919,13 +3931,13 @@
         <v>6</v>
       </c>
       <c r="C136" t="s">
-        <v>225</v>
-      </c>
-      <c r="D136" s="53" t="s">
         <v>226</v>
       </c>
+      <c r="D136" s="54" t="s">
+        <v>227</v>
+      </c>
       <c r="F136" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="137" s="3" customFormat="1" spans="1:6">
@@ -3936,27 +3948,30 @@
         <v>10</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D137" s="32" t="s">
         <v>229</v>
       </c>
+      <c r="D137" s="33" t="s">
+        <v>230</v>
+      </c>
       <c r="F137" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="138" s="3" customFormat="1" spans="1:4">
-      <c r="A138" s="3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="138" s="14" customFormat="1" spans="1:6">
+      <c r="A138" s="14">
         <v>101</v>
       </c>
-      <c r="B138" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C138" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="D138" s="33" t="s">
+      <c r="B138" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C138" s="14" t="s">
         <v>232</v>
+      </c>
+      <c r="D138" s="57" t="s">
+        <v>233</v>
+      </c>
+      <c r="F138" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -3967,10 +3982,10 @@
         <v>6</v>
       </c>
       <c r="C139" t="s">
-        <v>233</v>
-      </c>
-      <c r="D139" s="54" t="s">
         <v>234</v>
+      </c>
+      <c r="D139" s="55" t="s">
+        <v>235</v>
       </c>
       <c r="F139" t="s">
         <v>63</v>
@@ -3983,11 +3998,11 @@
       <c r="B140" t="s">
         <v>6</v>
       </c>
-      <c r="C140" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="D140" s="53" t="s">
+      <c r="C140" s="56" t="s">
         <v>236</v>
+      </c>
+      <c r="D140" s="54" t="s">
+        <v>237</v>
       </c>
       <c r="F140" t="s">
         <v>63</v>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="245">
   <si>
     <t>编号</t>
   </si>
@@ -797,6 +797,29 @@
   </si>
   <si>
     <t>问题图片\103.jpg</t>
+  </si>
+  <si>
+    <t>感叹号按钮里面点击“获取箱子”打开的界面会把回收界面一起弹出来造成界面卡死，怀疑问题出在装备回收界面前期手动打开过</t>
+  </si>
+  <si>
+    <t>问题图片\104.jpg</t>
+  </si>
+  <si>
+    <t>月光宝盒按钮上添加小红点提示，显示规则为：仅在今日还有可开启次数（未达到今日开箱上限）且当前持有开箱次数不为0时显示小红点</t>
+  </si>
+  <si>
+    <t>问题图片\105.jpg</t>
+  </si>
+  <si>
+    <t>回收界面在包裹满之后如果又持续获取装备，则界面点关闭没有反应，界面会一直打开无法关闭</t>
+  </si>
+  <si>
+    <t>问题图片\106.jpg</t>
+  </si>
+  <si>
+    <t>红包道具和强化石原石道具目前有两个问题：
+1、虽然弹出来了快捷使用，但是点击使用无法正常打开，仍然是会回到包裹中。
+2、在包裹中点击使用，仍然是一次只能用一个，没有像筛子道具那样可以把一个格子里面的道具全部用掉</t>
   </si>
 </sst>
 </file>
@@ -1525,7 +1548,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1699,6 +1722,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2016,7 +2042,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="132" customWidth="1"/>
@@ -4006,6 +4032,59 @@
       </c>
       <c r="F140" t="s">
         <v>63</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141">
+        <v>104</v>
+      </c>
+      <c r="B141" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" t="s">
+        <v>238</v>
+      </c>
+      <c r="D141" s="54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142">
+        <v>105</v>
+      </c>
+      <c r="B142" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>240</v>
+      </c>
+      <c r="D142" s="54" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143">
+        <v>106</v>
+      </c>
+      <c r="B143" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" t="s">
+        <v>242</v>
+      </c>
+      <c r="D143" s="54" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="144" ht="40.5" spans="1:3">
+      <c r="A144">
+        <v>107</v>
+      </c>
+      <c r="B144" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="58" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -4085,6 +4164,9 @@
     <hyperlink ref="D138" r:id="rId68" display="问题图片\101.jpg"/>
     <hyperlink ref="D139" r:id="rId69" display="问题图片\102.jpg"/>
     <hyperlink ref="D140" r:id="rId70" display="问题图片\103.jpg"/>
+    <hyperlink ref="D141" r:id="rId71" display="问题图片\104.jpg"/>
+    <hyperlink ref="D142" r:id="rId72" display="问题图片\105.jpg"/>
+    <hyperlink ref="D143" r:id="rId73" display="问题图片\106.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/策划文档/问题汇总列表.xlsx
+++ b/策划文档/问题汇总列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="246">
   <si>
     <t>编号</t>
   </si>
@@ -815,6 +815,9 @@
   </si>
   <si>
     <t>问题图片\106.jpg</t>
+  </si>
+  <si>
+    <t>未能复现！！！！</t>
   </si>
   <si>
     <t>红包道具和强化石原石道具目前有两个问题：
@@ -1548,7 +1551,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1722,9 +1725,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4034,7 +4034,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:6">
       <c r="A141">
         <v>104</v>
       </c>
@@ -4044,11 +4044,14 @@
       <c r="C141" t="s">
         <v>238</v>
       </c>
-      <c r="D141" s="54" t="s">
+      <c r="D141" s="55" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="142" spans="1:4">
+      <c r="F141" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142">
         <v>105</v>
       </c>
@@ -4061,8 +4064,11 @@
       <c r="D142" s="54" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="143" spans="1:4">
+      <c r="F142" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143">
         <v>106</v>
       </c>
@@ -4072,19 +4078,25 @@
       <c r="C143" t="s">
         <v>242</v>
       </c>
-      <c r="D143" s="54" t="s">
+      <c r="D143" s="55" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="144" ht="40.5" spans="1:3">
+      <c r="F143" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="144" ht="40.5" spans="1:6">
       <c r="A144">
         <v>107</v>
       </c>
       <c r="B144" t="s">
         <v>10</v>
       </c>
-      <c r="C144" s="58" t="s">
-        <v>244</v>
+      <c r="C144" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="F144" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
